--- a/LocCodes.xlsx
+++ b/LocCodes.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bertling-my.sharepoint.com/personal/erik_stahl_bertling_com/Documents/Skrivbordet/LocCodes py script/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erik.stahl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_4701D0A8D320DC6EC520DDF0505ED87656C75FBA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D596910-15E7-4805-B8B2-39799A9B49E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA120FF-3BFC-4AB0-8A61-FEFC179F8446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$5036</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$5035</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -3232,12 +3232,6 @@
     <t>Nansha New Port</t>
   </si>
   <si>
-    <t>CNNOP</t>
-  </si>
-  <si>
-    <t>Nansha</t>
-  </si>
-  <si>
     <t>CNNSA</t>
   </si>
   <si>
@@ -29366,6 +29360,12 @@
   </si>
   <si>
     <t>Port Klang</t>
+  </si>
+  <si>
+    <t>SEHED</t>
+  </si>
+  <si>
+    <t>Hedemora</t>
   </si>
 </sst>
 </file>
@@ -34149,15 +34149,15 @@
         <v>1085</v>
       </c>
       <c r="B555" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B556" t="s">
         <v>1087</v>
-      </c>
-      <c r="B556" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.25">
@@ -34173,15 +34173,15 @@
         <v>1090</v>
       </c>
       <c r="B558" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B559" t="s">
         <v>1092</v>
-      </c>
-      <c r="B559" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.25">
@@ -34221,15 +34221,15 @@
         <v>1101</v>
       </c>
       <c r="B564" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B565" t="s">
         <v>1103</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.25">
@@ -34317,15 +34317,15 @@
         <v>1124</v>
       </c>
       <c r="B576" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B577" t="s">
         <v>1126</v>
-      </c>
-      <c r="B577" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.25">
@@ -34341,15 +34341,15 @@
         <v>1129</v>
       </c>
       <c r="B579" t="s">
-        <v>1130</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B580" t="s">
         <v>1131</v>
-      </c>
-      <c r="B580" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.25">
@@ -34357,15 +34357,15 @@
         <v>1132</v>
       </c>
       <c r="B581" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B582" t="s">
         <v>1134</v>
-      </c>
-      <c r="B582" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.25">
@@ -34373,15 +34373,15 @@
         <v>1135</v>
       </c>
       <c r="B583" t="s">
-        <v>1136</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B584" t="s">
         <v>1137</v>
-      </c>
-      <c r="B584" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.25">
@@ -34397,15 +34397,15 @@
         <v>1140</v>
       </c>
       <c r="B586" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B587" t="s">
         <v>1142</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.25">
@@ -34421,15 +34421,15 @@
         <v>1145</v>
       </c>
       <c r="B589" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B590" t="s">
         <v>1147</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.25">
@@ -34477,31 +34477,31 @@
         <v>1158</v>
       </c>
       <c r="B596" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B597" t="s">
-        <v>1153</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B598" t="s">
-        <v>1061</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B599" t="s">
         <v>1162</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
@@ -34517,15 +34517,15 @@
         <v>1165</v>
       </c>
       <c r="B601" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B602" t="s">
         <v>1167</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
@@ -34549,15 +34549,15 @@
         <v>1172</v>
       </c>
       <c r="B605" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B606" t="s">
         <v>1174</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
@@ -34565,15 +34565,15 @@
         <v>1175</v>
       </c>
       <c r="B607" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B608" t="s">
         <v>1177</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.25">
@@ -34581,15 +34581,15 @@
         <v>1178</v>
       </c>
       <c r="B609" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B610" t="s">
         <v>1180</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.25">
@@ -34597,15 +34597,15 @@
         <v>1181</v>
       </c>
       <c r="B611" t="s">
-        <v>1182</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B612" t="s">
         <v>1183</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.25">
@@ -34621,23 +34621,23 @@
         <v>1186</v>
       </c>
       <c r="B614" t="s">
-        <v>1187</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B615" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B616" t="s">
         <v>1189</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.25">
@@ -34693,15 +34693,15 @@
         <v>1202</v>
       </c>
       <c r="B623" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B624" t="s">
         <v>1204</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.25">
@@ -34717,15 +34717,15 @@
         <v>1207</v>
       </c>
       <c r="B626" t="s">
-        <v>1208</v>
+        <v>77</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B627" t="s">
         <v>1209</v>
-      </c>
-      <c r="B627" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.25">
@@ -34757,15 +34757,15 @@
         <v>1216</v>
       </c>
       <c r="B631" t="s">
-        <v>1217</v>
+        <v>77</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B632" t="s">
         <v>1218</v>
-      </c>
-      <c r="B632" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.25">
@@ -34821,15 +34821,15 @@
         <v>1231</v>
       </c>
       <c r="B639" t="s">
-        <v>1232</v>
+        <v>884</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B640" t="s">
         <v>1233</v>
-      </c>
-      <c r="B640" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
@@ -34853,15 +34853,15 @@
         <v>1238</v>
       </c>
       <c r="B643" t="s">
-        <v>1239</v>
+        <v>432</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B644" t="s">
         <v>1240</v>
-      </c>
-      <c r="B644" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.25">
@@ -34941,15 +34941,15 @@
         <v>1259</v>
       </c>
       <c r="B654" t="s">
-        <v>1260</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B655" t="s">
         <v>1261</v>
-      </c>
-      <c r="B655" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.25">
@@ -35005,15 +35005,15 @@
         <v>1274</v>
       </c>
       <c r="B662" t="s">
-        <v>1275</v>
+        <v>956</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B663" t="s">
         <v>1276</v>
-      </c>
-      <c r="B663" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.25">
@@ -35397,15 +35397,15 @@
         <v>1371</v>
       </c>
       <c r="B711" t="s">
-        <v>1372</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B712" t="s">
         <v>1373</v>
-      </c>
-      <c r="B712" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.25">
@@ -36037,15 +36037,15 @@
         <v>1530</v>
       </c>
       <c r="B791" t="s">
-        <v>1531</v>
+        <v>494</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B792" t="s">
         <v>1532</v>
-      </c>
-      <c r="B792" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.25">
@@ -36061,15 +36061,15 @@
         <v>1535</v>
       </c>
       <c r="B794" t="s">
-        <v>1536</v>
+        <v>585</v>
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B795" t="s">
         <v>1537</v>
-      </c>
-      <c r="B795" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.25">
@@ -37117,15 +37117,15 @@
         <v>1798</v>
       </c>
       <c r="B926" t="s">
-        <v>1799</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B927" t="s">
         <v>1800</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.25">
@@ -37821,15 +37821,15 @@
         <v>1973</v>
       </c>
       <c r="B1014" t="s">
-        <v>1974</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1975</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.25">
@@ -38693,15 +38693,15 @@
         <v>2190</v>
       </c>
       <c r="B1123" t="s">
-        <v>2191</v>
+        <v>442</v>
       </c>
     </row>
     <row r="1124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1124" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="1125" spans="1:2" x14ac:dyDescent="0.25">
@@ -39261,23 +39261,23 @@
         <v>2331</v>
       </c>
       <c r="B1194" t="s">
-        <v>2332</v>
+        <v>924</v>
       </c>
     </row>
     <row r="1195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="B1195" t="s">
-        <v>924</v>
+        <v>972</v>
       </c>
     </row>
     <row r="1196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1196" t="s">
         <v>2334</v>
-      </c>
-      <c r="B1196" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.25">
@@ -39405,15 +39405,15 @@
         <v>2365</v>
       </c>
       <c r="B1212" t="s">
-        <v>2366</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B1213" t="s">
         <v>2367</v>
-      </c>
-      <c r="B1213" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="1214" spans="1:2" x14ac:dyDescent="0.25">
@@ -39973,15 +39973,15 @@
         <v>2506</v>
       </c>
       <c r="B1283" t="s">
-        <v>2507</v>
+        <v>474</v>
       </c>
     </row>
     <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B1284" t="s">
         <v>2508</v>
-      </c>
-      <c r="B1284" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
@@ -40429,15 +40429,15 @@
         <v>2619</v>
       </c>
       <c r="B1340" t="s">
-        <v>2620</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1341" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B1341" t="s">
         <v>2621</v>
-      </c>
-      <c r="B1341" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
@@ -41253,15 +41253,15 @@
         <v>2824</v>
       </c>
       <c r="B1443" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1444" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B1444" t="s">
         <v>2826</v>
-      </c>
-      <c r="B1444" t="s">
-        <v>2825</v>
       </c>
     </row>
     <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
@@ -41301,15 +41301,15 @@
         <v>2835</v>
       </c>
       <c r="B1449" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1450" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B1450" t="s">
         <v>2837</v>
-      </c>
-      <c r="B1450" t="s">
-        <v>2836</v>
       </c>
     </row>
     <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
@@ -42013,15 +42013,15 @@
         <v>3012</v>
       </c>
       <c r="B1538" t="s">
-        <v>3013</v>
+        <v>976</v>
       </c>
     </row>
     <row r="1539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1539" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B1539" t="s">
         <v>3014</v>
-      </c>
-      <c r="B1539" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="1540" spans="1:2" x14ac:dyDescent="0.25">
@@ -42253,15 +42253,15 @@
         <v>3071</v>
       </c>
       <c r="B1568" t="s">
-        <v>3072</v>
+        <v>679</v>
       </c>
     </row>
     <row r="1569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1569" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B1569" t="s">
         <v>3073</v>
-      </c>
-      <c r="B1569" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="1570" spans="1:2" x14ac:dyDescent="0.25">
@@ -42309,15 +42309,15 @@
         <v>3084</v>
       </c>
       <c r="B1575" t="s">
-        <v>3085</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1576" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B1576" t="s">
         <v>3086</v>
-      </c>
-      <c r="B1576" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="1577" spans="1:2" x14ac:dyDescent="0.25">
@@ -42741,15 +42741,15 @@
         <v>3191</v>
       </c>
       <c r="B1629" t="s">
-        <v>3192</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="1630" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1630" t="s">
+        <v>3192</v>
+      </c>
+      <c r="B1630" t="s">
         <v>3193</v>
-      </c>
-      <c r="B1630" t="s">
-        <v>3190</v>
       </c>
     </row>
     <row r="1631" spans="1:2" x14ac:dyDescent="0.25">
@@ -43013,15 +43013,15 @@
         <v>3258</v>
       </c>
       <c r="B1663" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="1664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1664" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B1664" t="s">
         <v>3260</v>
-      </c>
-      <c r="B1664" t="s">
-        <v>3257</v>
       </c>
     </row>
     <row r="1665" spans="1:2" x14ac:dyDescent="0.25">
@@ -43189,15 +43189,15 @@
         <v>3301</v>
       </c>
       <c r="B1685" t="s">
-        <v>3302</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="1686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1686" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1686" t="s">
         <v>3303</v>
-      </c>
-      <c r="B1686" t="s">
-        <v>3184</v>
       </c>
     </row>
     <row r="1687" spans="1:2" x14ac:dyDescent="0.25">
@@ -44213,15 +44213,15 @@
         <v>3556</v>
       </c>
       <c r="B1813" t="s">
-        <v>3557</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1814" t="s">
+        <v>3557</v>
+      </c>
+      <c r="B1814" t="s">
         <v>3558</v>
-      </c>
-      <c r="B1814" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="1815" spans="1:2" x14ac:dyDescent="0.25">
@@ -44541,15 +44541,15 @@
         <v>3637</v>
       </c>
       <c r="B1854" t="s">
-        <v>3638</v>
+        <v>623</v>
       </c>
     </row>
     <row r="1855" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1855" t="s">
+        <v>3638</v>
+      </c>
+      <c r="B1855" t="s">
         <v>3639</v>
-      </c>
-      <c r="B1855" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="1856" spans="1:2" x14ac:dyDescent="0.25">
@@ -44693,15 +44693,15 @@
         <v>3674</v>
       </c>
       <c r="B1873" t="s">
-        <v>3675</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1874" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1874" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B1874" t="s">
         <v>3676</v>
-      </c>
-      <c r="B1874" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="1875" spans="1:2" x14ac:dyDescent="0.25">
@@ -44877,15 +44877,15 @@
         <v>3719</v>
       </c>
       <c r="B1896" t="s">
-        <v>3720</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="1897" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1897" t="s">
+        <v>3720</v>
+      </c>
+      <c r="B1897" t="s">
         <v>3721</v>
-      </c>
-      <c r="B1897" t="s">
-        <v>3692</v>
       </c>
     </row>
     <row r="1898" spans="1:2" x14ac:dyDescent="0.25">
@@ -44973,15 +44973,15 @@
         <v>3742</v>
       </c>
       <c r="B1908" t="s">
-        <v>3743</v>
+        <v>650</v>
       </c>
     </row>
     <row r="1909" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1909" t="s">
+        <v>3743</v>
+      </c>
+      <c r="B1909" t="s">
         <v>3744</v>
-      </c>
-      <c r="B1909" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="1910" spans="1:2" x14ac:dyDescent="0.25">
@@ -45173,15 +45173,15 @@
         <v>3791</v>
       </c>
       <c r="B1933" t="s">
-        <v>3792</v>
+        <v>663</v>
       </c>
     </row>
     <row r="1934" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1934" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B1934" t="s">
         <v>3793</v>
-      </c>
-      <c r="B1934" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="1935" spans="1:2" x14ac:dyDescent="0.25">
@@ -45309,15 +45309,15 @@
         <v>3824</v>
       </c>
       <c r="B1950" t="s">
-        <v>3825</v>
+        <v>663</v>
       </c>
     </row>
     <row r="1951" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1951" t="s">
+        <v>3825</v>
+      </c>
+      <c r="B1951" t="s">
         <v>3826</v>
-      </c>
-      <c r="B1951" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="1952" spans="1:2" x14ac:dyDescent="0.25">
@@ -45557,15 +45557,15 @@
         <v>3885</v>
       </c>
       <c r="B1981" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="1982" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1982" t="s">
+        <v>3886</v>
+      </c>
+      <c r="B1982" t="s">
         <v>3887</v>
-      </c>
-      <c r="B1982" t="s">
-        <v>3886</v>
       </c>
     </row>
     <row r="1983" spans="1:2" x14ac:dyDescent="0.25">
@@ -45621,15 +45621,15 @@
         <v>3900</v>
       </c>
       <c r="B1989" t="s">
-        <v>3901</v>
+        <v>696</v>
       </c>
     </row>
     <row r="1990" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1990" t="s">
+        <v>3901</v>
+      </c>
+      <c r="B1990" t="s">
         <v>3902</v>
-      </c>
-      <c r="B1990" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="1991" spans="1:2" x14ac:dyDescent="0.25">
@@ -46149,15 +46149,15 @@
         <v>4031</v>
       </c>
       <c r="B2055" t="s">
-        <v>4032</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2056" t="s">
+        <v>4032</v>
+      </c>
+      <c r="B2056" t="s">
         <v>4033</v>
-      </c>
-      <c r="B2056" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2057" spans="1:2" x14ac:dyDescent="0.25">
@@ -46285,15 +46285,15 @@
         <v>4064</v>
       </c>
       <c r="B2072" t="s">
-        <v>4065</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2073" t="s">
+        <v>4065</v>
+      </c>
+      <c r="B2073" t="s">
         <v>4066</v>
-      </c>
-      <c r="B2073" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2074" spans="1:2" x14ac:dyDescent="0.25">
@@ -46325,12 +46325,12 @@
         <v>4073</v>
       </c>
       <c r="B2077" t="s">
-        <v>4074</v>
+        <v>879</v>
       </c>
     </row>
     <row r="2078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2078" t="s">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="B2078" t="s">
         <v>879</v>
@@ -46338,10 +46338,10 @@
     </row>
     <row r="2079" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2079" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B2079" t="s">
         <v>4076</v>
-      </c>
-      <c r="B2079" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="2080" spans="1:2" x14ac:dyDescent="0.25">
@@ -46661,15 +46661,15 @@
         <v>4155</v>
       </c>
       <c r="B2119" t="s">
-        <v>4156</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="2120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2120" t="s">
+        <v>4156</v>
+      </c>
+      <c r="B2120" t="s">
         <v>4157</v>
-      </c>
-      <c r="B2120" t="s">
-        <v>4090</v>
       </c>
     </row>
     <row r="2121" spans="1:2" x14ac:dyDescent="0.25">
@@ -47189,15 +47189,15 @@
         <v>4286</v>
       </c>
       <c r="B2185" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="2186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2186" t="s">
+        <v>4287</v>
+      </c>
+      <c r="B2186" t="s">
         <v>4288</v>
-      </c>
-      <c r="B2186" t="s">
-        <v>4287</v>
       </c>
     </row>
     <row r="2187" spans="1:2" x14ac:dyDescent="0.25">
@@ -47261,15 +47261,15 @@
         <v>4303</v>
       </c>
       <c r="B2194" t="s">
-        <v>4304</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="2195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2195" t="s">
+        <v>4304</v>
+      </c>
+      <c r="B2195" t="s">
         <v>4305</v>
-      </c>
-      <c r="B2195" t="s">
-        <v>2393</v>
       </c>
     </row>
     <row r="2196" spans="1:2" x14ac:dyDescent="0.25">
@@ -47341,15 +47341,15 @@
         <v>4322</v>
       </c>
       <c r="B2204" t="s">
-        <v>4323</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="2205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2205" t="s">
+        <v>4323</v>
+      </c>
+      <c r="B2205" t="s">
         <v>4324</v>
-      </c>
-      <c r="B2205" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="2206" spans="1:2" x14ac:dyDescent="0.25">
@@ -47357,15 +47357,15 @@
         <v>4325</v>
       </c>
       <c r="B2206" t="s">
-        <v>4326</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="2207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2207" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B2207" t="s">
         <v>4327</v>
-      </c>
-      <c r="B2207" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="2208" spans="1:2" x14ac:dyDescent="0.25">
@@ -47925,15 +47925,15 @@
         <v>4466</v>
       </c>
       <c r="B2277" t="s">
-        <v>4467</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="2278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2278" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B2278" t="s">
         <v>4468</v>
-      </c>
-      <c r="B2278" t="s">
-        <v>4463</v>
       </c>
     </row>
     <row r="2279" spans="1:2" x14ac:dyDescent="0.25">
@@ -48029,15 +48029,15 @@
         <v>4491</v>
       </c>
       <c r="B2290" t="s">
-        <v>4492</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="2291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2291" t="s">
+        <v>4492</v>
+      </c>
+      <c r="B2291" t="s">
         <v>4493</v>
-      </c>
-      <c r="B2291" t="s">
-        <v>3557</v>
       </c>
     </row>
     <row r="2292" spans="1:2" x14ac:dyDescent="0.25">
@@ -48069,15 +48069,15 @@
         <v>4500</v>
       </c>
       <c r="B2295" t="s">
-        <v>4501</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="2296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2296" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B2296" t="s">
         <v>4502</v>
-      </c>
-      <c r="B2296" t="s">
-        <v>2356</v>
       </c>
     </row>
     <row r="2297" spans="1:2" x14ac:dyDescent="0.25">
@@ -48285,15 +48285,15 @@
         <v>4553</v>
       </c>
       <c r="B2322" t="s">
-        <v>4554</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2323" t="s">
+        <v>4554</v>
+      </c>
+      <c r="B2323" t="s">
         <v>4555</v>
-      </c>
-      <c r="B2323" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2324" spans="1:2" x14ac:dyDescent="0.25">
@@ -48437,15 +48437,15 @@
         <v>4590</v>
       </c>
       <c r="B2341" t="s">
-        <v>4591</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="2342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2342" t="s">
+        <v>4591</v>
+      </c>
+      <c r="B2342" t="s">
         <v>4592</v>
-      </c>
-      <c r="B2342" t="s">
-        <v>4591</v>
       </c>
     </row>
     <row r="2343" spans="1:2" x14ac:dyDescent="0.25">
@@ -48469,15 +48469,15 @@
         <v>4597</v>
       </c>
       <c r="B2345" t="s">
-        <v>4598</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="2346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2346" t="s">
+        <v>4598</v>
+      </c>
+      <c r="B2346" t="s">
         <v>4599</v>
-      </c>
-      <c r="B2346" t="s">
-        <v>4594</v>
       </c>
     </row>
     <row r="2347" spans="1:2" x14ac:dyDescent="0.25">
@@ -48709,15 +48709,15 @@
         <v>4656</v>
       </c>
       <c r="B2375" t="s">
-        <v>4657</v>
+        <v>9777</v>
       </c>
     </row>
     <row r="2376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2376" t="s">
+        <v>4657</v>
+      </c>
+      <c r="B2376" t="s">
         <v>4658</v>
-      </c>
-      <c r="B2376" t="s">
-        <v>9779</v>
       </c>
     </row>
     <row r="2377" spans="1:2" x14ac:dyDescent="0.25">
@@ -48749,15 +48749,15 @@
         <v>4665</v>
       </c>
       <c r="B2380" t="s">
-        <v>4666</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="2381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2381" t="s">
+        <v>4666</v>
+      </c>
+      <c r="B2381" t="s">
         <v>4667</v>
-      </c>
-      <c r="B2381" t="s">
-        <v>4660</v>
       </c>
     </row>
     <row r="2382" spans="1:2" x14ac:dyDescent="0.25">
@@ -49213,15 +49213,15 @@
         <v>4780</v>
       </c>
       <c r="B2438" t="s">
-        <v>4781</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="2439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2439" t="s">
+        <v>4781</v>
+      </c>
+      <c r="B2439" t="s">
         <v>4782</v>
-      </c>
-      <c r="B2439" t="s">
-        <v>4761</v>
       </c>
     </row>
     <row r="2440" spans="1:2" x14ac:dyDescent="0.25">
@@ -50645,15 +50645,15 @@
         <v>5137</v>
       </c>
       <c r="B2617" t="s">
-        <v>5138</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="2618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2618" t="s">
+        <v>5138</v>
+      </c>
+      <c r="B2618" t="s">
         <v>5139</v>
-      </c>
-      <c r="B2618" t="s">
-        <v>5126</v>
       </c>
     </row>
     <row r="2619" spans="1:2" x14ac:dyDescent="0.25">
@@ -50661,15 +50661,15 @@
         <v>5140</v>
       </c>
       <c r="B2619" t="s">
-        <v>5141</v>
+        <v>4763</v>
       </c>
     </row>
     <row r="2620" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2620" t="s">
+        <v>5141</v>
+      </c>
+      <c r="B2620" t="s">
         <v>5142</v>
-      </c>
-      <c r="B2620" t="s">
-        <v>4765</v>
       </c>
     </row>
     <row r="2621" spans="1:2" x14ac:dyDescent="0.25">
@@ -50973,15 +50973,15 @@
         <v>5217</v>
       </c>
       <c r="B2658" t="s">
-        <v>5218</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="2659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2659" t="s">
+        <v>5218</v>
+      </c>
+      <c r="B2659" t="s">
         <v>5219</v>
-      </c>
-      <c r="B2659" t="s">
-        <v>3517</v>
       </c>
     </row>
     <row r="2660" spans="1:2" x14ac:dyDescent="0.25">
@@ -51421,15 +51421,15 @@
         <v>5328</v>
       </c>
       <c r="B2714" t="s">
-        <v>5329</v>
+        <v>5325</v>
       </c>
     </row>
     <row r="2715" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2715" t="s">
+        <v>5329</v>
+      </c>
+      <c r="B2715" t="s">
         <v>5330</v>
-      </c>
-      <c r="B2715" t="s">
-        <v>5327</v>
       </c>
     </row>
     <row r="2716" spans="1:2" x14ac:dyDescent="0.25">
@@ -51605,15 +51605,15 @@
         <v>5373</v>
       </c>
       <c r="B2737" t="s">
-        <v>5374</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2738" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2738" t="s">
+        <v>5374</v>
+      </c>
+      <c r="B2738" t="s">
         <v>5375</v>
-      </c>
-      <c r="B2738" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="2739" spans="1:2" x14ac:dyDescent="0.25">
@@ -51773,15 +51773,15 @@
         <v>5414</v>
       </c>
       <c r="B2758" t="s">
-        <v>5415</v>
+        <v>5413</v>
       </c>
     </row>
     <row r="2759" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2759" t="s">
+        <v>5415</v>
+      </c>
+      <c r="B2759" t="s">
         <v>5416</v>
-      </c>
-      <c r="B2759" t="s">
-        <v>5415</v>
       </c>
     </row>
     <row r="2760" spans="1:2" x14ac:dyDescent="0.25">
@@ -51957,15 +51957,15 @@
         <v>5459</v>
       </c>
       <c r="B2781" t="s">
-        <v>5460</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="2782" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2782" t="s">
+        <v>5460</v>
+      </c>
+      <c r="B2782" t="s">
         <v>5461</v>
-      </c>
-      <c r="B2782" t="s">
-        <v>5352</v>
       </c>
     </row>
     <row r="2783" spans="1:2" x14ac:dyDescent="0.25">
@@ -52005,15 +52005,15 @@
         <v>5470</v>
       </c>
       <c r="B2787" t="s">
-        <v>5471</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="2788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2788" t="s">
+        <v>5471</v>
+      </c>
+      <c r="B2788" t="s">
         <v>5472</v>
-      </c>
-      <c r="B2788" t="s">
-        <v>3850</v>
       </c>
     </row>
     <row r="2789" spans="1:2" x14ac:dyDescent="0.25">
@@ -52277,15 +52277,15 @@
         <v>5537</v>
       </c>
       <c r="B2821" t="s">
-        <v>5538</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2822" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2822" t="s">
+        <v>5538</v>
+      </c>
+      <c r="B2822" t="s">
         <v>5539</v>
-      </c>
-      <c r="B2822" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="2823" spans="1:2" x14ac:dyDescent="0.25">
@@ -52517,15 +52517,15 @@
         <v>5596</v>
       </c>
       <c r="B2851" t="s">
-        <v>5597</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="2852" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2852" t="s">
+        <v>5597</v>
+      </c>
+      <c r="B2852" t="s">
         <v>5598</v>
-      </c>
-      <c r="B2852" t="s">
-        <v>2574</v>
       </c>
     </row>
     <row r="2853" spans="1:2" x14ac:dyDescent="0.25">
@@ -52861,15 +52861,15 @@
         <v>5681</v>
       </c>
       <c r="B2894" t="s">
-        <v>5682</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="2895" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2895" t="s">
+        <v>5682</v>
+      </c>
+      <c r="B2895" t="s">
         <v>5683</v>
-      </c>
-      <c r="B2895" t="s">
-        <v>9780</v>
       </c>
     </row>
     <row r="2896" spans="1:2" x14ac:dyDescent="0.25">
@@ -53013,15 +53013,15 @@
         <v>5718</v>
       </c>
       <c r="B2913" t="s">
-        <v>5719</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="2914" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2914" t="s">
+        <v>5719</v>
+      </c>
+      <c r="B2914" t="s">
         <v>5720</v>
-      </c>
-      <c r="B2914" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="2915" spans="1:2" x14ac:dyDescent="0.25">
@@ -53085,23 +53085,23 @@
         <v>5735</v>
       </c>
       <c r="B2922" t="s">
-        <v>5736</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="2923" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2923" t="s">
-        <v>5737</v>
+        <v>5736</v>
       </c>
       <c r="B2923" t="s">
-        <v>4351</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="2924" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2924" t="s">
+        <v>5737</v>
+      </c>
+      <c r="B2924" t="s">
         <v>5738</v>
-      </c>
-      <c r="B2924" t="s">
-        <v>5717</v>
       </c>
     </row>
     <row r="2925" spans="1:2" x14ac:dyDescent="0.25">
@@ -53109,15 +53109,15 @@
         <v>5739</v>
       </c>
       <c r="B2925" t="s">
-        <v>5740</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="2926" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2926" t="s">
+        <v>5740</v>
+      </c>
+      <c r="B2926" t="s">
         <v>5741</v>
-      </c>
-      <c r="B2926" t="s">
-        <v>5559</v>
       </c>
     </row>
     <row r="2927" spans="1:2" x14ac:dyDescent="0.25">
@@ -53389,15 +53389,15 @@
         <v>5808</v>
       </c>
       <c r="B2960" t="s">
-        <v>5809</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2961" t="s">
+        <v>5809</v>
+      </c>
+      <c r="B2961" t="s">
         <v>5810</v>
-      </c>
-      <c r="B2961" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="2962" spans="1:2" x14ac:dyDescent="0.25">
@@ -54061,15 +54061,15 @@
         <v>5975</v>
       </c>
       <c r="B3044" t="s">
-        <v>5976</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3045" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3045" t="s">
+        <v>5976</v>
+      </c>
+      <c r="B3045" t="s">
         <v>5977</v>
-      </c>
-      <c r="B3045" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="3046" spans="1:2" x14ac:dyDescent="0.25">
@@ -54933,15 +54933,15 @@
         <v>6192</v>
       </c>
       <c r="B3153" t="s">
-        <v>6193</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="3154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3154" t="s">
+        <v>6193</v>
+      </c>
+      <c r="B3154" t="s">
         <v>6194</v>
-      </c>
-      <c r="B3154" t="s">
-        <v>5890</v>
       </c>
     </row>
     <row r="3155" spans="1:2" x14ac:dyDescent="0.25">
@@ -55117,15 +55117,15 @@
         <v>6237</v>
       </c>
       <c r="B3176" t="s">
-        <v>6238</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="3177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3177" t="s">
+        <v>6238</v>
+      </c>
+      <c r="B3177" t="s">
         <v>6239</v>
-      </c>
-      <c r="B3177" t="s">
-        <v>5989</v>
       </c>
     </row>
     <row r="3178" spans="1:2" x14ac:dyDescent="0.25">
@@ -55197,15 +55197,15 @@
         <v>6256</v>
       </c>
       <c r="B3186" t="s">
-        <v>6257</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="3187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3187" t="s">
+        <v>6257</v>
+      </c>
+      <c r="B3187" t="s">
         <v>6258</v>
-      </c>
-      <c r="B3187" t="s">
-        <v>3634</v>
       </c>
     </row>
     <row r="3188" spans="1:2" x14ac:dyDescent="0.25">
@@ -55317,15 +55317,15 @@
         <v>6285</v>
       </c>
       <c r="B3201" t="s">
-        <v>6286</v>
+        <v>5488</v>
       </c>
     </row>
     <row r="3202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3202" t="s">
+        <v>6286</v>
+      </c>
+      <c r="B3202" t="s">
         <v>6287</v>
-      </c>
-      <c r="B3202" t="s">
-        <v>5490</v>
       </c>
     </row>
     <row r="3203" spans="1:2" x14ac:dyDescent="0.25">
@@ -55413,15 +55413,15 @@
         <v>6308</v>
       </c>
       <c r="B3213" t="s">
-        <v>6309</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3214" t="s">
+        <v>6309</v>
+      </c>
+      <c r="B3214" t="s">
         <v>6310</v>
-      </c>
-      <c r="B3214" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="3215" spans="1:2" x14ac:dyDescent="0.25">
@@ -55613,15 +55613,15 @@
         <v>6357</v>
       </c>
       <c r="B3238" t="s">
-        <v>6358</v>
+        <v>5732</v>
       </c>
     </row>
     <row r="3239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3239" t="s">
+        <v>6358</v>
+      </c>
+      <c r="B3239" t="s">
         <v>6359</v>
-      </c>
-      <c r="B3239" t="s">
-        <v>5734</v>
       </c>
     </row>
     <row r="3240" spans="1:2" x14ac:dyDescent="0.25">
@@ -56541,15 +56541,15 @@
         <v>6588</v>
       </c>
       <c r="B3354" t="s">
-        <v>6589</v>
+        <v>6505</v>
       </c>
     </row>
     <row r="3355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3355" t="s">
+        <v>6589</v>
+      </c>
+      <c r="B3355" t="s">
         <v>6590</v>
-      </c>
-      <c r="B3355" t="s">
-        <v>6507</v>
       </c>
     </row>
     <row r="3356" spans="1:2" x14ac:dyDescent="0.25">
@@ -56669,15 +56669,15 @@
         <v>6619</v>
       </c>
       <c r="B3370" t="s">
-        <v>6620</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="3371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3371" t="s">
+        <v>6620</v>
+      </c>
+      <c r="B3371" t="s">
         <v>6621</v>
-      </c>
-      <c r="B3371" t="s">
-        <v>6443</v>
       </c>
     </row>
     <row r="3372" spans="1:2" x14ac:dyDescent="0.25">
@@ -56733,15 +56733,15 @@
         <v>6634</v>
       </c>
       <c r="B3378" t="s">
-        <v>6635</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="3379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3379" t="s">
+        <v>6635</v>
+      </c>
+      <c r="B3379" t="s">
         <v>6636</v>
-      </c>
-      <c r="B3379" t="s">
-        <v>6620</v>
       </c>
     </row>
     <row r="3380" spans="1:2" x14ac:dyDescent="0.25">
@@ -56821,15 +56821,15 @@
         <v>6655</v>
       </c>
       <c r="B3389" t="s">
-        <v>6656</v>
+        <v>6654</v>
       </c>
     </row>
     <row r="3390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3390" t="s">
+        <v>6656</v>
+      </c>
+      <c r="B3390" t="s">
         <v>6657</v>
-      </c>
-      <c r="B3390" t="s">
-        <v>6656</v>
       </c>
     </row>
     <row r="3391" spans="1:2" x14ac:dyDescent="0.25">
@@ -57333,15 +57333,15 @@
         <v>6782</v>
       </c>
       <c r="B3453" t="s">
-        <v>6783</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="3454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3454" t="s">
+        <v>6783</v>
+      </c>
+      <c r="B3454" t="s">
         <v>6784</v>
-      </c>
-      <c r="B3454" t="s">
-        <v>2344</v>
       </c>
     </row>
     <row r="3455" spans="1:2" x14ac:dyDescent="0.25">
@@ -57589,15 +57589,15 @@
         <v>6845</v>
       </c>
       <c r="B3485" t="s">
-        <v>6846</v>
+        <v>6838</v>
       </c>
     </row>
     <row r="3486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3486" t="s">
+        <v>6846</v>
+      </c>
+      <c r="B3486" t="s">
         <v>6847</v>
-      </c>
-      <c r="B3486" t="s">
-        <v>6840</v>
       </c>
     </row>
     <row r="3487" spans="1:2" x14ac:dyDescent="0.25">
@@ -58181,15 +58181,15 @@
         <v>6992</v>
       </c>
       <c r="B3559" t="s">
-        <v>6993</v>
+        <v>5964</v>
       </c>
     </row>
     <row r="3560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3560" t="s">
+        <v>6993</v>
+      </c>
+      <c r="B3560" t="s">
         <v>6994</v>
-      </c>
-      <c r="B3560" t="s">
-        <v>5966</v>
       </c>
     </row>
     <row r="3561" spans="1:2" x14ac:dyDescent="0.25">
@@ -58365,15 +58365,15 @@
         <v>7037</v>
       </c>
       <c r="B3582" t="s">
-        <v>7038</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="3583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3583" t="s">
+        <v>7038</v>
+      </c>
+      <c r="B3583" t="s">
         <v>7039</v>
-      </c>
-      <c r="B3583" t="s">
-        <v>5972</v>
       </c>
     </row>
     <row r="3584" spans="1:2" x14ac:dyDescent="0.25">
@@ -59637,15 +59637,15 @@
         <v>7354</v>
       </c>
       <c r="B3741" t="s">
-        <v>7355</v>
+        <v>7353</v>
       </c>
     </row>
     <row r="3742" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3742" t="s">
+        <v>7355</v>
+      </c>
+      <c r="B3742" t="s">
         <v>7356</v>
-      </c>
-      <c r="B3742" t="s">
-        <v>7355</v>
       </c>
     </row>
     <row r="3743" spans="1:2" x14ac:dyDescent="0.25">
@@ -59693,15 +59693,15 @@
         <v>7367</v>
       </c>
       <c r="B3748" t="s">
-        <v>7368</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="3749" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3749" t="s">
+        <v>7368</v>
+      </c>
+      <c r="B3749" t="s">
         <v>7369</v>
-      </c>
-      <c r="B3749" t="s">
-        <v>7366</v>
       </c>
     </row>
     <row r="3750" spans="1:2" x14ac:dyDescent="0.25">
@@ -60101,15 +60101,15 @@
         <v>7468</v>
       </c>
       <c r="B3799" t="s">
-        <v>7469</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="3800" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3800" t="s">
+        <v>7469</v>
+      </c>
+      <c r="B3800" t="s">
         <v>7470</v>
-      </c>
-      <c r="B3800" t="s">
-        <v>6249</v>
       </c>
     </row>
     <row r="3801" spans="1:2" x14ac:dyDescent="0.25">
@@ -60197,15 +60197,15 @@
         <v>7491</v>
       </c>
       <c r="B3811" t="s">
-        <v>7492</v>
+        <v>5319</v>
       </c>
     </row>
     <row r="3812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3812" t="s">
+        <v>7492</v>
+      </c>
+      <c r="B3812" t="s">
         <v>7493</v>
-      </c>
-      <c r="B3812" t="s">
-        <v>5321</v>
       </c>
     </row>
     <row r="3813" spans="1:2" x14ac:dyDescent="0.25">
@@ -60301,15 +60301,15 @@
         <v>7516</v>
       </c>
       <c r="B3824" t="s">
-        <v>7517</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="3825" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3825" t="s">
+        <v>7517</v>
+      </c>
+      <c r="B3825" t="s">
         <v>7518</v>
-      </c>
-      <c r="B3825" t="s">
-        <v>4082</v>
       </c>
     </row>
     <row r="3826" spans="1:2" x14ac:dyDescent="0.25">
@@ -60469,15 +60469,15 @@
         <v>7557</v>
       </c>
       <c r="B3845" t="s">
-        <v>7558</v>
+        <v>5385</v>
       </c>
     </row>
     <row r="3846" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3846" t="s">
+        <v>7558</v>
+      </c>
+      <c r="B3846" t="s">
         <v>7559</v>
-      </c>
-      <c r="B3846" t="s">
-        <v>5387</v>
       </c>
     </row>
     <row r="3847" spans="1:2" x14ac:dyDescent="0.25">
@@ -61021,15 +61021,15 @@
         <v>7694</v>
       </c>
       <c r="B3914" t="s">
-        <v>7695</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="3915" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3915" t="s">
+        <v>7695</v>
+      </c>
+      <c r="B3915" t="s">
         <v>7696</v>
-      </c>
-      <c r="B3915" t="s">
-        <v>6305</v>
       </c>
     </row>
     <row r="3916" spans="1:2" x14ac:dyDescent="0.25">
@@ -61285,15 +61285,15 @@
         <v>7759</v>
       </c>
       <c r="B3947" t="s">
-        <v>7760</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="3948" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3948" t="s">
+        <v>7760</v>
+      </c>
+      <c r="B3948" t="s">
         <v>7761</v>
-      </c>
-      <c r="B3948" t="s">
-        <v>4302</v>
       </c>
     </row>
     <row r="3949" spans="1:2" x14ac:dyDescent="0.25">
@@ -61453,15 +61453,15 @@
         <v>7800</v>
       </c>
       <c r="B3968" t="s">
-        <v>7801</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="3969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3969" t="s">
+        <v>7801</v>
+      </c>
+      <c r="B3969" t="s">
         <v>7802</v>
-      </c>
-      <c r="B3969" t="s">
-        <v>7771</v>
       </c>
     </row>
     <row r="3970" spans="1:2" x14ac:dyDescent="0.25">
@@ -61613,15 +61613,15 @@
         <v>7839</v>
       </c>
       <c r="B3988" t="s">
-        <v>7840</v>
+        <v>7401</v>
       </c>
     </row>
     <row r="3989" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3989" t="s">
+        <v>7840</v>
+      </c>
+      <c r="B3989" t="s">
         <v>7841</v>
-      </c>
-      <c r="B3989" t="s">
-        <v>7403</v>
       </c>
     </row>
     <row r="3990" spans="1:2" x14ac:dyDescent="0.25">
@@ -61773,15 +61773,15 @@
         <v>7878</v>
       </c>
       <c r="B4008" t="s">
-        <v>7879</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="4009" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4009" t="s">
+        <v>7879</v>
+      </c>
+      <c r="B4009" t="s">
         <v>7880</v>
-      </c>
-      <c r="B4009" t="s">
-        <v>6356</v>
       </c>
     </row>
     <row r="4010" spans="1:2" x14ac:dyDescent="0.25">
@@ -61869,15 +61869,15 @@
         <v>7901</v>
       </c>
       <c r="B4020" t="s">
-        <v>7902</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="4021" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4021" t="s">
+        <v>7902</v>
+      </c>
+      <c r="B4021" t="s">
         <v>7903</v>
-      </c>
-      <c r="B4021" t="s">
-        <v>6212</v>
       </c>
     </row>
     <row r="4022" spans="1:2" x14ac:dyDescent="0.25">
@@ -62301,15 +62301,15 @@
         <v>8008</v>
       </c>
       <c r="B4074" t="s">
-        <v>8009</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="4075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4075" t="s">
+        <v>8009</v>
+      </c>
+      <c r="B4075" t="s">
         <v>8010</v>
-      </c>
-      <c r="B4075" t="s">
-        <v>6234</v>
       </c>
     </row>
     <row r="4076" spans="1:2" x14ac:dyDescent="0.25">
@@ -62701,15 +62701,15 @@
         <v>8107</v>
       </c>
       <c r="B4124" t="s">
-        <v>8108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4125" t="s">
+        <v>8108</v>
+      </c>
+      <c r="B4125" t="s">
         <v>8109</v>
-      </c>
-      <c r="B4125" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4126" spans="1:2" x14ac:dyDescent="0.25">
@@ -62765,15 +62765,15 @@
         <v>8122</v>
       </c>
       <c r="B4132" t="s">
-        <v>8123</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="4133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4133" t="s">
+        <v>8123</v>
+      </c>
+      <c r="B4133" t="s">
         <v>8124</v>
-      </c>
-      <c r="B4133" t="s">
-        <v>8111</v>
       </c>
     </row>
     <row r="4134" spans="1:2" x14ac:dyDescent="0.25">
@@ -62797,15 +62797,15 @@
         <v>8129</v>
       </c>
       <c r="B4136" t="s">
-        <v>8130</v>
+        <v>8102</v>
       </c>
     </row>
     <row r="4137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4137" t="s">
+        <v>8130</v>
+      </c>
+      <c r="B4137" t="s">
         <v>8131</v>
-      </c>
-      <c r="B4137" t="s">
-        <v>8104</v>
       </c>
     </row>
     <row r="4138" spans="1:2" x14ac:dyDescent="0.25">
@@ -63061,15 +63061,15 @@
         <v>8194</v>
       </c>
       <c r="B4169" t="s">
-        <v>8195</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="4170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4170" t="s">
+        <v>8195</v>
+      </c>
+      <c r="B4170" t="s">
         <v>8196</v>
-      </c>
-      <c r="B4170" t="s">
-        <v>6289</v>
       </c>
     </row>
     <row r="4171" spans="1:2" x14ac:dyDescent="0.25">
@@ -63085,15 +63085,15 @@
         <v>8199</v>
       </c>
       <c r="B4172" t="s">
-        <v>8200</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4173" t="s">
+        <v>8200</v>
+      </c>
+      <c r="B4173" t="s">
         <v>8201</v>
-      </c>
-      <c r="B4173" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="4174" spans="1:2" x14ac:dyDescent="0.25">
@@ -63173,15 +63173,15 @@
         <v>8220</v>
       </c>
       <c r="B4183" t="s">
-        <v>8221</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="4184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4184" t="s">
+        <v>8221</v>
+      </c>
+      <c r="B4184" t="s">
         <v>8222</v>
-      </c>
-      <c r="B4184" t="s">
-        <v>6183</v>
       </c>
     </row>
     <row r="4185" spans="1:2" x14ac:dyDescent="0.25">
@@ -63261,23 +63261,23 @@
         <v>8241</v>
       </c>
       <c r="B4194" t="s">
-        <v>8242</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="4195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4195" t="s">
-        <v>8243</v>
+        <v>8242</v>
       </c>
       <c r="B4195" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="4196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4196" t="s">
+        <v>8243</v>
+      </c>
+      <c r="B4196" t="s">
         <v>8244</v>
-      </c>
-      <c r="B4196" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="4197" spans="1:2" x14ac:dyDescent="0.25">
@@ -63317,15 +63317,15 @@
         <v>8253</v>
       </c>
       <c r="B4201" t="s">
-        <v>8254</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4202" t="s">
+        <v>8254</v>
+      </c>
+      <c r="B4202" t="s">
         <v>8255</v>
-      </c>
-      <c r="B4202" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="4203" spans="1:2" x14ac:dyDescent="0.25">
@@ -63445,15 +63445,15 @@
         <v>8284</v>
       </c>
       <c r="B4217" t="s">
-        <v>8285</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="4218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4218" t="s">
+        <v>8285</v>
+      </c>
+      <c r="B4218" t="s">
         <v>8286</v>
-      </c>
-      <c r="B4218" t="s">
-        <v>8285</v>
       </c>
     </row>
     <row r="4219" spans="1:2" x14ac:dyDescent="0.25">
@@ -63501,15 +63501,15 @@
         <v>8297</v>
       </c>
       <c r="B4224" t="s">
-        <v>8298</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4225" t="s">
+        <v>8298</v>
+      </c>
+      <c r="B4225" t="s">
         <v>8299</v>
-      </c>
-      <c r="B4225" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4226" spans="1:2" x14ac:dyDescent="0.25">
@@ -63597,15 +63597,15 @@
         <v>8320</v>
       </c>
       <c r="B4236" t="s">
-        <v>8321</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4237" t="s">
+        <v>8321</v>
+      </c>
+      <c r="B4237" t="s">
         <v>8322</v>
-      </c>
-      <c r="B4237" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4238" spans="1:2" x14ac:dyDescent="0.25">
@@ -63637,15 +63637,15 @@
         <v>8329</v>
       </c>
       <c r="B4241" t="s">
-        <v>8330</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="4242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4242" t="s">
+        <v>8330</v>
+      </c>
+      <c r="B4242" t="s">
         <v>8331</v>
-      </c>
-      <c r="B4242" t="s">
-        <v>8330</v>
       </c>
     </row>
     <row r="4243" spans="1:2" x14ac:dyDescent="0.25">
@@ -63677,15 +63677,15 @@
         <v>8338</v>
       </c>
       <c r="B4246" t="s">
-        <v>8339</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4247" t="s">
+        <v>8339</v>
+      </c>
+      <c r="B4247" t="s">
         <v>8340</v>
-      </c>
-      <c r="B4247" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="4248" spans="1:2" x14ac:dyDescent="0.25">
@@ -63829,15 +63829,15 @@
         <v>8375</v>
       </c>
       <c r="B4265" t="s">
-        <v>8376</v>
+        <v>8374</v>
       </c>
     </row>
     <row r="4266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4266" t="s">
+        <v>8376</v>
+      </c>
+      <c r="B4266" t="s">
         <v>8377</v>
-      </c>
-      <c r="B4266" t="s">
-        <v>8376</v>
       </c>
     </row>
     <row r="4267" spans="1:2" x14ac:dyDescent="0.25">
@@ -63901,15 +63901,15 @@
         <v>8392</v>
       </c>
       <c r="B4274" t="s">
-        <v>8393</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="4275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4275" t="s">
+        <v>8393</v>
+      </c>
+      <c r="B4275" t="s">
         <v>8394</v>
-      </c>
-      <c r="B4275" t="s">
-        <v>4309</v>
       </c>
     </row>
     <row r="4276" spans="1:2" x14ac:dyDescent="0.25">
@@ -63957,15 +63957,15 @@
         <v>8405</v>
       </c>
       <c r="B4281" t="s">
-        <v>8406</v>
+        <v>8346</v>
       </c>
     </row>
     <row r="4282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4282" t="s">
+        <v>8406</v>
+      </c>
+      <c r="B4282" t="s">
         <v>8407</v>
-      </c>
-      <c r="B4282" t="s">
-        <v>8348</v>
       </c>
     </row>
     <row r="4283" spans="1:2" x14ac:dyDescent="0.25">
@@ -64093,15 +64093,15 @@
         <v>8438</v>
       </c>
       <c r="B4298" t="s">
-        <v>8439</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="4299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4299" t="s">
+        <v>8439</v>
+      </c>
+      <c r="B4299" t="s">
         <v>8440</v>
-      </c>
-      <c r="B4299" t="s">
-        <v>8330</v>
       </c>
     </row>
     <row r="4300" spans="1:2" x14ac:dyDescent="0.25">
@@ -64581,15 +64581,15 @@
         <v>8559</v>
       </c>
       <c r="B4359" t="s">
-        <v>8560</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="4360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4360" t="s">
+        <v>8560</v>
+      </c>
+      <c r="B4360" t="s">
         <v>8561</v>
-      </c>
-      <c r="B4360" t="s">
-        <v>2389</v>
       </c>
     </row>
     <row r="4361" spans="1:2" x14ac:dyDescent="0.25">
@@ -64645,23 +64645,23 @@
         <v>8574</v>
       </c>
       <c r="B4367" t="s">
-        <v>8575</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="4368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4368" t="s">
-        <v>8576</v>
+        <v>8575</v>
       </c>
       <c r="B4368" t="s">
-        <v>6255</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="4369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4369" t="s">
+        <v>8576</v>
+      </c>
+      <c r="B4369" t="s">
         <v>8577</v>
-      </c>
-      <c r="B4369" t="s">
-        <v>4014</v>
       </c>
     </row>
     <row r="4370" spans="1:2" x14ac:dyDescent="0.25">
@@ -64701,15 +64701,15 @@
         <v>8586</v>
       </c>
       <c r="B4374" t="s">
-        <v>8587</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="4375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4375" t="s">
+        <v>8587</v>
+      </c>
+      <c r="B4375" t="s">
         <v>8588</v>
-      </c>
-      <c r="B4375" t="s">
-        <v>3525</v>
       </c>
     </row>
     <row r="4376" spans="1:2" x14ac:dyDescent="0.25">
@@ -64741,15 +64741,15 @@
         <v>8595</v>
       </c>
       <c r="B4379" t="s">
-        <v>8596</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="4380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4380" t="s">
+        <v>8596</v>
+      </c>
+      <c r="B4380" t="s">
         <v>8597</v>
-      </c>
-      <c r="B4380" t="s">
-        <v>4786</v>
       </c>
     </row>
     <row r="4381" spans="1:2" x14ac:dyDescent="0.25">
@@ -64821,15 +64821,15 @@
         <v>8614</v>
       </c>
       <c r="B4389" t="s">
-        <v>8615</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="4390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4390" t="s">
+        <v>8615</v>
+      </c>
+      <c r="B4390" t="s">
         <v>8616</v>
-      </c>
-      <c r="B4390" t="s">
-        <v>3850</v>
       </c>
     </row>
     <row r="4391" spans="1:2" x14ac:dyDescent="0.25">
@@ -64853,23 +64853,23 @@
         <v>8621</v>
       </c>
       <c r="B4393" t="s">
-        <v>8622</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="4394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4394" t="s">
-        <v>8623</v>
+        <v>8622</v>
       </c>
       <c r="B4394" t="s">
-        <v>8585</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="4395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4395" t="s">
+        <v>8623</v>
+      </c>
+      <c r="B4395" t="s">
         <v>8624</v>
-      </c>
-      <c r="B4395" t="s">
-        <v>8583</v>
       </c>
     </row>
     <row r="4396" spans="1:2" x14ac:dyDescent="0.25">
@@ -64989,15 +64989,15 @@
         <v>8653</v>
       </c>
       <c r="B4410" t="s">
-        <v>8654</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="4411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4411" t="s">
+        <v>8654</v>
+      </c>
+      <c r="B4411" t="s">
         <v>8655</v>
-      </c>
-      <c r="B4411" t="s">
-        <v>3557</v>
       </c>
     </row>
     <row r="4412" spans="1:2" x14ac:dyDescent="0.25">
@@ -65013,15 +65013,15 @@
         <v>8658</v>
       </c>
       <c r="B4413" t="s">
-        <v>8659</v>
+        <v>8655</v>
       </c>
     </row>
     <row r="4414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4414" t="s">
+        <v>8659</v>
+      </c>
+      <c r="B4414" t="s">
         <v>8660</v>
-      </c>
-      <c r="B4414" t="s">
-        <v>8657</v>
       </c>
     </row>
     <row r="4415" spans="1:2" x14ac:dyDescent="0.25">
@@ -65061,15 +65061,15 @@
         <v>8669</v>
       </c>
       <c r="B4419" t="s">
-        <v>8670</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4420" t="s">
+        <v>8670</v>
+      </c>
+      <c r="B4420" t="s">
         <v>8671</v>
-      </c>
-      <c r="B4420" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="4421" spans="1:2" x14ac:dyDescent="0.25">
@@ -65085,23 +65085,23 @@
         <v>8674</v>
       </c>
       <c r="B4422" t="s">
-        <v>8675</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4423" t="s">
-        <v>8676</v>
+        <v>8675</v>
       </c>
       <c r="B4423" t="s">
-        <v>190</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="4424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4424" t="s">
+        <v>8676</v>
+      </c>
+      <c r="B4424" t="s">
         <v>8677</v>
-      </c>
-      <c r="B4424" t="s">
-        <v>3592</v>
       </c>
     </row>
     <row r="4425" spans="1:2" x14ac:dyDescent="0.25">
@@ -65133,15 +65133,15 @@
         <v>8684</v>
       </c>
       <c r="B4428" t="s">
-        <v>8685</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="4429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4429" t="s">
+        <v>8685</v>
+      </c>
+      <c r="B4429" t="s">
         <v>8686</v>
-      </c>
-      <c r="B4429" t="s">
-        <v>8659</v>
       </c>
     </row>
     <row r="4430" spans="1:2" x14ac:dyDescent="0.25">
@@ -65149,15 +65149,15 @@
         <v>8687</v>
       </c>
       <c r="B4430" t="s">
-        <v>8688</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="4431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4431" t="s">
+        <v>8688</v>
+      </c>
+      <c r="B4431" t="s">
         <v>8689</v>
-      </c>
-      <c r="B4431" t="s">
-        <v>8685</v>
       </c>
     </row>
     <row r="4432" spans="1:2" x14ac:dyDescent="0.25">
@@ -65197,31 +65197,31 @@
         <v>8698</v>
       </c>
       <c r="B4436" t="s">
-        <v>8699</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="4437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4437" t="s">
-        <v>8700</v>
+        <v>8699</v>
       </c>
       <c r="B4437" t="s">
-        <v>8648</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4438" t="s">
-        <v>8701</v>
+        <v>8700</v>
       </c>
       <c r="B4438" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4439" t="s">
+        <v>8701</v>
+      </c>
+      <c r="B4439" t="s">
         <v>8702</v>
-      </c>
-      <c r="B4439" t="s">
-        <v>3612</v>
       </c>
     </row>
     <row r="4440" spans="1:2" x14ac:dyDescent="0.25">
@@ -65293,15 +65293,15 @@
         <v>8719</v>
       </c>
       <c r="B4448" t="s">
-        <v>8720</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="4449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4449" t="s">
+        <v>8720</v>
+      </c>
+      <c r="B4449" t="s">
         <v>8721</v>
-      </c>
-      <c r="B4449" t="s">
-        <v>3622</v>
       </c>
     </row>
     <row r="4450" spans="1:2" x14ac:dyDescent="0.25">
@@ -65373,31 +65373,31 @@
         <v>8738</v>
       </c>
       <c r="B4458" t="s">
-        <v>8739</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="4459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4459" t="s">
-        <v>8740</v>
+        <v>8739</v>
       </c>
       <c r="B4459" t="s">
-        <v>8733</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4460" t="s">
-        <v>8741</v>
+        <v>8740</v>
       </c>
       <c r="B4460" t="s">
-        <v>3612</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="4461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4461" t="s">
+        <v>8741</v>
+      </c>
+      <c r="B4461" t="s">
         <v>8742</v>
-      </c>
-      <c r="B4461" t="s">
-        <v>8712</v>
       </c>
     </row>
     <row r="4462" spans="1:2" x14ac:dyDescent="0.25">
@@ -65405,15 +65405,15 @@
         <v>8743</v>
       </c>
       <c r="B4462" t="s">
-        <v>8744</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="4463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4463" t="s">
+        <v>8744</v>
+      </c>
+      <c r="B4463" t="s">
         <v>8745</v>
-      </c>
-      <c r="B4463" t="s">
-        <v>8718</v>
       </c>
     </row>
     <row r="4464" spans="1:2" x14ac:dyDescent="0.25">
@@ -65429,15 +65429,15 @@
         <v>8748</v>
       </c>
       <c r="B4465" t="s">
-        <v>8749</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="4466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4466" t="s">
+        <v>8749</v>
+      </c>
+      <c r="B4466" t="s">
         <v>8750</v>
-      </c>
-      <c r="B4466" t="s">
-        <v>8718</v>
       </c>
     </row>
     <row r="4467" spans="1:2" x14ac:dyDescent="0.25">
@@ -65469,15 +65469,15 @@
         <v>8757</v>
       </c>
       <c r="B4470" t="s">
-        <v>8758</v>
+        <v>8742</v>
       </c>
     </row>
     <row r="4471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4471" t="s">
+        <v>8758</v>
+      </c>
+      <c r="B4471" t="s">
         <v>8759</v>
-      </c>
-      <c r="B4471" t="s">
-        <v>8744</v>
       </c>
     </row>
     <row r="4472" spans="1:2" x14ac:dyDescent="0.25">
@@ -65501,23 +65501,23 @@
         <v>8764</v>
       </c>
       <c r="B4474" t="s">
-        <v>8765</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4475" t="s">
-        <v>8766</v>
+        <v>8765</v>
       </c>
       <c r="B4475" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4476" t="s">
+        <v>8766</v>
+      </c>
+      <c r="B4476" t="s">
         <v>8767</v>
-      </c>
-      <c r="B4476" t="s">
-        <v>3612</v>
       </c>
     </row>
     <row r="4477" spans="1:2" x14ac:dyDescent="0.25">
@@ -65525,15 +65525,15 @@
         <v>8768</v>
       </c>
       <c r="B4477" t="s">
-        <v>8769</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="4478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4478" t="s">
+        <v>8769</v>
+      </c>
+      <c r="B4478" t="s">
         <v>8770</v>
-      </c>
-      <c r="B4478" t="s">
-        <v>8712</v>
       </c>
     </row>
     <row r="4479" spans="1:2" x14ac:dyDescent="0.25">
@@ -65645,15 +65645,15 @@
         <v>8797</v>
       </c>
       <c r="B4492" t="s">
-        <v>8798</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="4493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4493" t="s">
+        <v>8798</v>
+      </c>
+      <c r="B4493" t="s">
         <v>8799</v>
-      </c>
-      <c r="B4493" t="s">
-        <v>3649</v>
       </c>
     </row>
     <row r="4494" spans="1:2" x14ac:dyDescent="0.25">
@@ -65669,15 +65669,15 @@
         <v>8802</v>
       </c>
       <c r="B4495" t="s">
-        <v>8803</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="4496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4496" t="s">
+        <v>8803</v>
+      </c>
+      <c r="B4496" t="s">
         <v>8804</v>
-      </c>
-      <c r="B4496" t="s">
-        <v>3657</v>
       </c>
     </row>
     <row r="4497" spans="1:2" x14ac:dyDescent="0.25">
@@ -65693,15 +65693,15 @@
         <v>8807</v>
       </c>
       <c r="B4498" t="s">
-        <v>8808</v>
+        <v>8796</v>
       </c>
     </row>
     <row r="4499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4499" t="s">
+        <v>8808</v>
+      </c>
+      <c r="B4499" t="s">
         <v>8809</v>
-      </c>
-      <c r="B4499" t="s">
-        <v>8798</v>
       </c>
     </row>
     <row r="4500" spans="1:2" x14ac:dyDescent="0.25">
@@ -65709,31 +65709,31 @@
         <v>8810</v>
       </c>
       <c r="B4500" t="s">
-        <v>8811</v>
+        <v>8796</v>
       </c>
     </row>
     <row r="4501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4501" t="s">
-        <v>8812</v>
+        <v>8811</v>
       </c>
       <c r="B4501" t="s">
-        <v>8798</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="4502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4502" t="s">
-        <v>8813</v>
+        <v>8812</v>
       </c>
       <c r="B4502" t="s">
-        <v>3649</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="4503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4503" t="s">
+        <v>8813</v>
+      </c>
+      <c r="B4503" t="s">
         <v>8814</v>
-      </c>
-      <c r="B4503" t="s">
-        <v>3653</v>
       </c>
     </row>
     <row r="4504" spans="1:2" x14ac:dyDescent="0.25">
@@ -65797,15 +65797,15 @@
         <v>8829</v>
       </c>
       <c r="B4511" t="s">
-        <v>8830</v>
+        <v>8826</v>
       </c>
     </row>
     <row r="4512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4512" t="s">
+        <v>8830</v>
+      </c>
+      <c r="B4512" t="s">
         <v>8831</v>
-      </c>
-      <c r="B4512" t="s">
-        <v>8828</v>
       </c>
     </row>
     <row r="4513" spans="1:2" x14ac:dyDescent="0.25">
@@ -65909,15 +65909,15 @@
         <v>8856</v>
       </c>
       <c r="B4525" t="s">
-        <v>8857</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="4526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4526" t="s">
+        <v>8857</v>
+      </c>
+      <c r="B4526" t="s">
         <v>8858</v>
-      </c>
-      <c r="B4526" t="s">
-        <v>3686</v>
       </c>
     </row>
     <row r="4527" spans="1:2" x14ac:dyDescent="0.25">
@@ -66045,15 +66045,15 @@
         <v>8889</v>
       </c>
       <c r="B4542" t="s">
-        <v>8890</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="4543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4543" t="s">
+        <v>8890</v>
+      </c>
+      <c r="B4543" t="s">
         <v>8891</v>
-      </c>
-      <c r="B4543" t="s">
-        <v>3566</v>
       </c>
     </row>
     <row r="4544" spans="1:2" x14ac:dyDescent="0.25">
@@ -66117,15 +66117,15 @@
         <v>8906</v>
       </c>
       <c r="B4551" t="s">
-        <v>8907</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="4552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4552" t="s">
+        <v>8907</v>
+      </c>
+      <c r="B4552" t="s">
         <v>8908</v>
-      </c>
-      <c r="B4552" t="s">
-        <v>3714</v>
       </c>
     </row>
     <row r="4553" spans="1:2" x14ac:dyDescent="0.25">
@@ -66269,15 +66269,15 @@
         <v>8943</v>
       </c>
       <c r="B4570" t="s">
-        <v>8944</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4571" t="s">
+        <v>8944</v>
+      </c>
+      <c r="B4571" t="s">
         <v>8945</v>
-      </c>
-      <c r="B4571" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="4572" spans="1:2" x14ac:dyDescent="0.25">
@@ -66341,15 +66341,15 @@
         <v>8960</v>
       </c>
       <c r="B4579" t="s">
-        <v>8961</v>
+        <v>8924</v>
       </c>
     </row>
     <row r="4580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4580" t="s">
+        <v>8961</v>
+      </c>
+      <c r="B4580" t="s">
         <v>8962</v>
-      </c>
-      <c r="B4580" t="s">
-        <v>8926</v>
       </c>
     </row>
     <row r="4581" spans="1:2" x14ac:dyDescent="0.25">
@@ -66357,15 +66357,15 @@
         <v>8963</v>
       </c>
       <c r="B4581" t="s">
-        <v>8964</v>
+        <v>8924</v>
       </c>
     </row>
     <row r="4582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4582" t="s">
+        <v>8964</v>
+      </c>
+      <c r="B4582" t="s">
         <v>8965</v>
-      </c>
-      <c r="B4582" t="s">
-        <v>8926</v>
       </c>
     </row>
     <row r="4583" spans="1:2" x14ac:dyDescent="0.25">
@@ -66373,15 +66373,15 @@
         <v>8966</v>
       </c>
       <c r="B4583" t="s">
-        <v>8967</v>
+        <v>8924</v>
       </c>
     </row>
     <row r="4584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4584" t="s">
+        <v>8967</v>
+      </c>
+      <c r="B4584" t="s">
         <v>8968</v>
-      </c>
-      <c r="B4584" t="s">
-        <v>8926</v>
       </c>
     </row>
     <row r="4585" spans="1:2" x14ac:dyDescent="0.25">
@@ -66485,23 +66485,23 @@
         <v>8993</v>
       </c>
       <c r="B4597" t="s">
-        <v>8994</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4598" t="s">
-        <v>8995</v>
+        <v>8994</v>
       </c>
       <c r="B4598" t="s">
-        <v>650</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4599" t="s">
+        <v>8995</v>
+      </c>
+      <c r="B4599" t="s">
         <v>8996</v>
-      </c>
-      <c r="B4599" t="s">
-        <v>3612</v>
       </c>
     </row>
     <row r="4600" spans="1:2" x14ac:dyDescent="0.25">
@@ -66541,15 +66541,15 @@
         <v>9005</v>
       </c>
       <c r="B4604" t="s">
-        <v>9006</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="4605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4605" t="s">
+        <v>9006</v>
+      </c>
+      <c r="B4605" t="s">
         <v>9007</v>
-      </c>
-      <c r="B4605" t="s">
-        <v>3772</v>
       </c>
     </row>
     <row r="4606" spans="1:2" x14ac:dyDescent="0.25">
@@ -66557,23 +66557,23 @@
         <v>9008</v>
       </c>
       <c r="B4606" t="s">
-        <v>9009</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4607" t="s">
-        <v>9010</v>
+        <v>9009</v>
       </c>
       <c r="B4607" t="s">
-        <v>5192</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4608" t="s">
+        <v>9010</v>
+      </c>
+      <c r="B4608" t="s">
         <v>9011</v>
-      </c>
-      <c r="B4608" t="s">
-        <v>5192</v>
       </c>
     </row>
     <row r="4609" spans="1:2" x14ac:dyDescent="0.25">
@@ -66581,15 +66581,15 @@
         <v>9012</v>
       </c>
       <c r="B4609" t="s">
-        <v>9013</v>
+        <v>9011</v>
       </c>
     </row>
     <row r="4610" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4610" t="s">
+        <v>9013</v>
+      </c>
+      <c r="B4610" t="s">
         <v>9014</v>
-      </c>
-      <c r="B4610" t="s">
-        <v>9013</v>
       </c>
     </row>
     <row r="4611" spans="1:2" x14ac:dyDescent="0.25">
@@ -66613,23 +66613,23 @@
         <v>9019</v>
       </c>
       <c r="B4613" t="s">
-        <v>9020</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4614" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4614" t="s">
-        <v>9021</v>
+        <v>9020</v>
       </c>
       <c r="B4614" t="s">
-        <v>5192</v>
+        <v>6687</v>
       </c>
     </row>
     <row r="4615" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4615" t="s">
+        <v>9021</v>
+      </c>
+      <c r="B4615" t="s">
         <v>9022</v>
-      </c>
-      <c r="B4615" t="s">
-        <v>6689</v>
       </c>
     </row>
     <row r="4616" spans="1:2" x14ac:dyDescent="0.25">
@@ -66645,15 +66645,15 @@
         <v>9025</v>
       </c>
       <c r="B4617" t="s">
-        <v>9026</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="4618" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4618" t="s">
+        <v>9026</v>
+      </c>
+      <c r="B4618" t="s">
         <v>9027</v>
-      </c>
-      <c r="B4618" t="s">
-        <v>8747</v>
       </c>
     </row>
     <row r="4619" spans="1:2" x14ac:dyDescent="0.25">
@@ -66677,23 +66677,23 @@
         <v>9032</v>
       </c>
       <c r="B4621" t="s">
-        <v>9033</v>
+        <v>8759</v>
       </c>
     </row>
     <row r="4622" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4622" t="s">
-        <v>9034</v>
+        <v>9033</v>
       </c>
       <c r="B4622" t="s">
-        <v>8761</v>
+        <v>8801</v>
       </c>
     </row>
     <row r="4623" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4623" t="s">
+        <v>9034</v>
+      </c>
+      <c r="B4623" t="s">
         <v>9035</v>
-      </c>
-      <c r="B4623" t="s">
-        <v>8803</v>
       </c>
     </row>
     <row r="4624" spans="1:2" x14ac:dyDescent="0.25">
@@ -66701,23 +66701,23 @@
         <v>9036</v>
       </c>
       <c r="B4624" t="s">
-        <v>9037</v>
+        <v>9027</v>
       </c>
     </row>
     <row r="4625" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4625" t="s">
-        <v>9038</v>
+        <v>9037</v>
       </c>
       <c r="B4625" t="s">
-        <v>9029</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="4626" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4626" t="s">
+        <v>9038</v>
+      </c>
+      <c r="B4626" t="s">
         <v>9039</v>
-      </c>
-      <c r="B4626" t="s">
-        <v>5202</v>
       </c>
     </row>
     <row r="4627" spans="1:2" x14ac:dyDescent="0.25">
@@ -66749,15 +66749,15 @@
         <v>9046</v>
       </c>
       <c r="B4630" t="s">
-        <v>9047</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="4631" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4631" t="s">
+        <v>9047</v>
+      </c>
+      <c r="B4631" t="s">
         <v>9048</v>
-      </c>
-      <c r="B4631" t="s">
-        <v>3788</v>
       </c>
     </row>
     <row r="4632" spans="1:2" x14ac:dyDescent="0.25">
@@ -66781,15 +66781,15 @@
         <v>9053</v>
       </c>
       <c r="B4634" t="s">
-        <v>9054</v>
+        <v>896</v>
       </c>
     </row>
     <row r="4635" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4635" t="s">
+        <v>9054</v>
+      </c>
+      <c r="B4635" t="s">
         <v>9055</v>
-      </c>
-      <c r="B4635" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="4636" spans="1:2" x14ac:dyDescent="0.25">
@@ -66805,15 +66805,15 @@
         <v>9058</v>
       </c>
       <c r="B4637" t="s">
-        <v>9059</v>
+        <v>9055</v>
       </c>
     </row>
     <row r="4638" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4638" t="s">
+        <v>9059</v>
+      </c>
+      <c r="B4638" t="s">
         <v>9060</v>
-      </c>
-      <c r="B4638" t="s">
-        <v>9057</v>
       </c>
     </row>
     <row r="4639" spans="1:2" x14ac:dyDescent="0.25">
@@ -66821,15 +66821,15 @@
         <v>9061</v>
       </c>
       <c r="B4639" t="s">
-        <v>9062</v>
+        <v>9060</v>
       </c>
     </row>
     <row r="4640" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4640" t="s">
+        <v>9062</v>
+      </c>
+      <c r="B4640" t="s">
         <v>9063</v>
-      </c>
-      <c r="B4640" t="s">
-        <v>9062</v>
       </c>
     </row>
     <row r="4641" spans="1:2" x14ac:dyDescent="0.25">
@@ -66861,15 +66861,15 @@
         <v>9070</v>
       </c>
       <c r="B4644" t="s">
-        <v>9071</v>
+        <v>9055</v>
       </c>
     </row>
     <row r="4645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4645" t="s">
+        <v>9071</v>
+      </c>
+      <c r="B4645" t="s">
         <v>9072</v>
-      </c>
-      <c r="B4645" t="s">
-        <v>9057</v>
       </c>
     </row>
     <row r="4646" spans="1:2" x14ac:dyDescent="0.25">
@@ -66877,23 +66877,23 @@
         <v>9073</v>
       </c>
       <c r="B4646" t="s">
-        <v>9074</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="4647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4647" t="s">
-        <v>9075</v>
+        <v>9074</v>
       </c>
       <c r="B4647" t="s">
-        <v>4506</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="4648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4648" t="s">
+        <v>9075</v>
+      </c>
+      <c r="B4648" t="s">
         <v>9076</v>
-      </c>
-      <c r="B4648" t="s">
-        <v>3788</v>
       </c>
     </row>
     <row r="4649" spans="1:2" x14ac:dyDescent="0.25">
@@ -66925,15 +66925,15 @@
         <v>9083</v>
       </c>
       <c r="B4652" t="s">
-        <v>9084</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="4653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4653" t="s">
+        <v>9084</v>
+      </c>
+      <c r="B4653" t="s">
         <v>9085</v>
-      </c>
-      <c r="B4653" t="s">
-        <v>2598</v>
       </c>
     </row>
     <row r="4654" spans="1:2" x14ac:dyDescent="0.25">
@@ -66981,15 +66981,15 @@
         <v>9096</v>
       </c>
       <c r="B4659" t="s">
-        <v>9097</v>
+        <v>6727</v>
       </c>
     </row>
     <row r="4660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4660" t="s">
+        <v>9097</v>
+      </c>
+      <c r="B4660" t="s">
         <v>9098</v>
-      </c>
-      <c r="B4660" t="s">
-        <v>6729</v>
       </c>
     </row>
     <row r="4661" spans="1:2" x14ac:dyDescent="0.25">
@@ -67045,15 +67045,15 @@
         <v>9111</v>
       </c>
       <c r="B4667" t="s">
-        <v>9112</v>
+        <v>9098</v>
       </c>
     </row>
     <row r="4668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4668" t="s">
+        <v>9112</v>
+      </c>
+      <c r="B4668" t="s">
         <v>9113</v>
-      </c>
-      <c r="B4668" t="s">
-        <v>9100</v>
       </c>
     </row>
     <row r="4669" spans="1:2" x14ac:dyDescent="0.25">
@@ -67069,15 +67069,15 @@
         <v>9116</v>
       </c>
       <c r="B4670" t="s">
-        <v>9117</v>
+        <v>8828</v>
       </c>
     </row>
     <row r="4671" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4671" t="s">
+        <v>9117</v>
+      </c>
+      <c r="B4671" t="s">
         <v>9118</v>
-      </c>
-      <c r="B4671" t="s">
-        <v>8830</v>
       </c>
     </row>
     <row r="4672" spans="1:2" x14ac:dyDescent="0.25">
@@ -67133,15 +67133,15 @@
         <v>9131</v>
       </c>
       <c r="B4678" t="s">
-        <v>9132</v>
+        <v>8573</v>
       </c>
     </row>
     <row r="4679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4679" t="s">
+        <v>9132</v>
+      </c>
+      <c r="B4679" t="s">
         <v>9133</v>
-      </c>
-      <c r="B4679" t="s">
-        <v>8575</v>
       </c>
     </row>
     <row r="4680" spans="1:2" x14ac:dyDescent="0.25">
@@ -67157,15 +67157,15 @@
         <v>9136</v>
       </c>
       <c r="B4681" t="s">
-        <v>9137</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="4682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4682" t="s">
+        <v>9137</v>
+      </c>
+      <c r="B4682" t="s">
         <v>9138</v>
-      </c>
-      <c r="B4682" t="s">
-        <v>9009</v>
       </c>
     </row>
     <row r="4683" spans="1:2" x14ac:dyDescent="0.25">
@@ -67229,15 +67229,15 @@
         <v>9153</v>
       </c>
       <c r="B4690" t="s">
-        <v>9154</v>
+        <v>9106</v>
       </c>
     </row>
     <row r="4691" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4691" t="s">
+        <v>9154</v>
+      </c>
+      <c r="B4691" t="s">
         <v>9155</v>
-      </c>
-      <c r="B4691" t="s">
-        <v>9108</v>
       </c>
     </row>
     <row r="4692" spans="1:2" x14ac:dyDescent="0.25">
@@ -67261,15 +67261,15 @@
         <v>9160</v>
       </c>
       <c r="B4694" t="s">
-        <v>9161</v>
+        <v>9098</v>
       </c>
     </row>
     <row r="4695" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4695" t="s">
+        <v>9161</v>
+      </c>
+      <c r="B4695" t="s">
         <v>9162</v>
-      </c>
-      <c r="B4695" t="s">
-        <v>9100</v>
       </c>
     </row>
     <row r="4696" spans="1:2" x14ac:dyDescent="0.25">
@@ -67285,15 +67285,15 @@
         <v>9165</v>
       </c>
       <c r="B4697" t="s">
-        <v>9166</v>
+        <v>9102</v>
       </c>
     </row>
     <row r="4698" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4698" t="s">
+        <v>9166</v>
+      </c>
+      <c r="B4698" t="s">
         <v>9167</v>
-      </c>
-      <c r="B4698" t="s">
-        <v>9104</v>
       </c>
     </row>
     <row r="4699" spans="1:2" x14ac:dyDescent="0.25">
@@ -67357,15 +67357,15 @@
         <v>9182</v>
       </c>
       <c r="B4706" t="s">
-        <v>9183</v>
+        <v>9098</v>
       </c>
     </row>
     <row r="4707" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4707" t="s">
+        <v>9183</v>
+      </c>
+      <c r="B4707" t="s">
         <v>9184</v>
-      </c>
-      <c r="B4707" t="s">
-        <v>9100</v>
       </c>
     </row>
     <row r="4708" spans="1:2" x14ac:dyDescent="0.25">
@@ -67405,23 +67405,23 @@
         <v>9193</v>
       </c>
       <c r="B4712" t="s">
-        <v>9194</v>
+        <v>9192</v>
       </c>
     </row>
     <row r="4713" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4713" t="s">
-        <v>9195</v>
+        <v>9194</v>
       </c>
       <c r="B4713" t="s">
-        <v>9194</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="4714" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4714" t="s">
+        <v>9195</v>
+      </c>
+      <c r="B4714" t="s">
         <v>9196</v>
-      </c>
-      <c r="B4714" t="s">
-        <v>3612</v>
       </c>
     </row>
     <row r="4715" spans="1:2" x14ac:dyDescent="0.25">
@@ -67437,15 +67437,15 @@
         <v>9199</v>
       </c>
       <c r="B4716" t="s">
-        <v>9200</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="4717" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4717" t="s">
+        <v>9200</v>
+      </c>
+      <c r="B4717" t="s">
         <v>9201</v>
-      </c>
-      <c r="B4717" t="s">
-        <v>8857</v>
       </c>
     </row>
     <row r="4718" spans="1:2" x14ac:dyDescent="0.25">
@@ -67461,15 +67461,15 @@
         <v>9204</v>
       </c>
       <c r="B4719" t="s">
-        <v>9205</v>
+        <v>9201</v>
       </c>
     </row>
     <row r="4720" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4720" t="s">
+        <v>9205</v>
+      </c>
+      <c r="B4720" t="s">
         <v>9206</v>
-      </c>
-      <c r="B4720" t="s">
-        <v>9203</v>
       </c>
     </row>
     <row r="4721" spans="1:2" x14ac:dyDescent="0.25">
@@ -67485,15 +67485,15 @@
         <v>9209</v>
       </c>
       <c r="B4722" t="s">
-        <v>9210</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="4723" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4723" t="s">
+        <v>9210</v>
+      </c>
+      <c r="B4723" t="s">
         <v>9211</v>
-      </c>
-      <c r="B4723" t="s">
-        <v>8857</v>
       </c>
     </row>
     <row r="4724" spans="1:2" x14ac:dyDescent="0.25">
@@ -67525,15 +67525,15 @@
         <v>9218</v>
       </c>
       <c r="B4727" t="s">
-        <v>9219</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="4728" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4728" t="s">
+        <v>9219</v>
+      </c>
+      <c r="B4728" t="s">
         <v>9220</v>
-      </c>
-      <c r="B4728" t="s">
-        <v>8857</v>
       </c>
     </row>
     <row r="4729" spans="1:2" x14ac:dyDescent="0.25">
@@ -67557,39 +67557,39 @@
         <v>9225</v>
       </c>
       <c r="B4731" t="s">
-        <v>9226</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="4732" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4732" t="s">
-        <v>9227</v>
+        <v>9226</v>
       </c>
       <c r="B4732" t="s">
-        <v>8857</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="4733" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4733" t="s">
-        <v>9228</v>
+        <v>9227</v>
       </c>
       <c r="B4733" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="4734" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4734" t="s">
-        <v>9229</v>
+        <v>9228</v>
       </c>
       <c r="B4734" t="s">
-        <v>3889</v>
+        <v>8801</v>
       </c>
     </row>
     <row r="4735" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4735" t="s">
+        <v>9229</v>
+      </c>
+      <c r="B4735" t="s">
         <v>9230</v>
-      </c>
-      <c r="B4735" t="s">
-        <v>8803</v>
       </c>
     </row>
     <row r="4736" spans="1:2" x14ac:dyDescent="0.25">
@@ -67597,15 +67597,15 @@
         <v>9231</v>
       </c>
       <c r="B4736" t="s">
-        <v>9232</v>
+        <v>9201</v>
       </c>
     </row>
     <row r="4737" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4737" t="s">
+        <v>9232</v>
+      </c>
+      <c r="B4737" t="s">
         <v>9233</v>
-      </c>
-      <c r="B4737" t="s">
-        <v>9203</v>
       </c>
     </row>
     <row r="4738" spans="1:2" x14ac:dyDescent="0.25">
@@ -67653,15 +67653,15 @@
         <v>9244</v>
       </c>
       <c r="B4743" t="s">
-        <v>9245</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="4744" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4744" t="s">
+        <v>9245</v>
+      </c>
+      <c r="B4744" t="s">
         <v>9246</v>
-      </c>
-      <c r="B4744" t="s">
-        <v>8718</v>
       </c>
     </row>
     <row r="4745" spans="1:2" x14ac:dyDescent="0.25">
@@ -67709,15 +67709,15 @@
         <v>9257</v>
       </c>
       <c r="B4750" t="s">
-        <v>9258</v>
+        <v>9201</v>
       </c>
     </row>
     <row r="4751" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4751" t="s">
+        <v>9258</v>
+      </c>
+      <c r="B4751" t="s">
         <v>9259</v>
-      </c>
-      <c r="B4751" t="s">
-        <v>9203</v>
       </c>
     </row>
     <row r="4752" spans="1:2" x14ac:dyDescent="0.25">
@@ -67733,15 +67733,15 @@
         <v>9262</v>
       </c>
       <c r="B4753" t="s">
-        <v>9263</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="4754" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4754" t="s">
+        <v>9263</v>
+      </c>
+      <c r="B4754" t="s">
         <v>9264</v>
-      </c>
-      <c r="B4754" t="s">
-        <v>6137</v>
       </c>
     </row>
     <row r="4755" spans="1:2" x14ac:dyDescent="0.25">
@@ -67813,15 +67813,15 @@
         <v>9281</v>
       </c>
       <c r="B4763" t="s">
-        <v>9282</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="4764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4764" t="s">
+        <v>9282</v>
+      </c>
+      <c r="B4764" t="s">
         <v>9283</v>
-      </c>
-      <c r="B4764" t="s">
-        <v>8811</v>
       </c>
     </row>
     <row r="4765" spans="1:2" x14ac:dyDescent="0.25">
@@ -67853,15 +67853,15 @@
         <v>9290</v>
       </c>
       <c r="B4768" t="s">
-        <v>9291</v>
+        <v>9280</v>
       </c>
     </row>
     <row r="4769" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4769" t="s">
+        <v>9291</v>
+      </c>
+      <c r="B4769" t="s">
         <v>9292</v>
-      </c>
-      <c r="B4769" t="s">
-        <v>9282</v>
       </c>
     </row>
     <row r="4770" spans="1:2" x14ac:dyDescent="0.25">
@@ -67901,15 +67901,15 @@
         <v>9301</v>
       </c>
       <c r="B4774" t="s">
-        <v>9302</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="4775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4775" t="s">
+        <v>9302</v>
+      </c>
+      <c r="B4775" t="s">
         <v>9303</v>
-      </c>
-      <c r="B4775" t="s">
-        <v>3906</v>
       </c>
     </row>
     <row r="4776" spans="1:2" x14ac:dyDescent="0.25">
@@ -67949,15 +67949,15 @@
         <v>9312</v>
       </c>
       <c r="B4780" t="s">
-        <v>9313</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="4781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4781" t="s">
+        <v>9313</v>
+      </c>
+      <c r="B4781" t="s">
         <v>9314</v>
-      </c>
-      <c r="B4781" t="s">
-        <v>3906</v>
       </c>
     </row>
     <row r="4782" spans="1:2" x14ac:dyDescent="0.25">
@@ -67965,15 +67965,15 @@
         <v>9315</v>
       </c>
       <c r="B4782" t="s">
-        <v>9316</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="4783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4783" t="s">
+        <v>9316</v>
+      </c>
+      <c r="B4783" t="s">
         <v>9317</v>
-      </c>
-      <c r="B4783" t="s">
-        <v>8811</v>
       </c>
     </row>
     <row r="4784" spans="1:2" x14ac:dyDescent="0.25">
@@ -68037,15 +68037,15 @@
         <v>9332</v>
       </c>
       <c r="B4791" t="s">
-        <v>9333</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="4792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4792" t="s">
+        <v>9333</v>
+      </c>
+      <c r="B4792" t="s">
         <v>9334</v>
-      </c>
-      <c r="B4792" t="s">
-        <v>5874</v>
       </c>
     </row>
     <row r="4793" spans="1:2" x14ac:dyDescent="0.25">
@@ -68061,31 +68061,31 @@
         <v>9337</v>
       </c>
       <c r="B4794" t="s">
-        <v>9338</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4795" t="s">
-        <v>9339</v>
+        <v>9338</v>
       </c>
       <c r="B4795" t="s">
-        <v>704</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="4796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4796" t="s">
-        <v>9340</v>
+        <v>9339</v>
       </c>
       <c r="B4796" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="4797" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4797" t="s">
+        <v>9340</v>
+      </c>
+      <c r="B4797" t="s">
         <v>9341</v>
-      </c>
-      <c r="B4797" t="s">
-        <v>3922</v>
       </c>
     </row>
     <row r="4798" spans="1:2" x14ac:dyDescent="0.25">
@@ -68109,15 +68109,15 @@
         <v>9346</v>
       </c>
       <c r="B4800" t="s">
-        <v>9347</v>
+        <v>704</v>
       </c>
     </row>
     <row r="4801" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4801" t="s">
+        <v>9347</v>
+      </c>
+      <c r="B4801" t="s">
         <v>9348</v>
-      </c>
-      <c r="B4801" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="4802" spans="1:2" x14ac:dyDescent="0.25">
@@ -68181,15 +68181,15 @@
         <v>9363</v>
       </c>
       <c r="B4809" t="s">
-        <v>9364</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="4810" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4810" t="s">
+        <v>9364</v>
+      </c>
+      <c r="B4810" t="s">
         <v>9365</v>
-      </c>
-      <c r="B4810" t="s">
-        <v>9362</v>
       </c>
     </row>
     <row r="4811" spans="1:2" x14ac:dyDescent="0.25">
@@ -68237,15 +68237,15 @@
         <v>9376</v>
       </c>
       <c r="B4816" t="s">
-        <v>9377</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="4817" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4817" t="s">
+        <v>9377</v>
+      </c>
+      <c r="B4817" t="s">
         <v>9378</v>
-      </c>
-      <c r="B4817" t="s">
-        <v>9362</v>
       </c>
     </row>
     <row r="4818" spans="1:2" x14ac:dyDescent="0.25">
@@ -68293,15 +68293,15 @@
         <v>9389</v>
       </c>
       <c r="B4823" t="s">
-        <v>9390</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="4824" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4824" t="s">
+        <v>9390</v>
+      </c>
+      <c r="B4824" t="s">
         <v>9391</v>
-      </c>
-      <c r="B4824" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="4825" spans="1:2" x14ac:dyDescent="0.25">
@@ -68389,15 +68389,15 @@
         <v>9412</v>
       </c>
       <c r="B4835" t="s">
-        <v>9413</v>
+        <v>9384</v>
       </c>
     </row>
     <row r="4836" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4836" t="s">
+        <v>9413</v>
+      </c>
+      <c r="B4836" t="s">
         <v>9414</v>
-      </c>
-      <c r="B4836" t="s">
-        <v>9386</v>
       </c>
     </row>
     <row r="4837" spans="1:2" x14ac:dyDescent="0.25">
@@ -68453,15 +68453,15 @@
         <v>9427</v>
       </c>
       <c r="B4843" t="s">
-        <v>9428</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="4844" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4844" t="s">
+        <v>9428</v>
+      </c>
+      <c r="B4844" t="s">
         <v>9429</v>
-      </c>
-      <c r="B4844" t="s">
-        <v>3889</v>
       </c>
     </row>
     <row r="4845" spans="1:2" x14ac:dyDescent="0.25">
@@ -68493,15 +68493,15 @@
         <v>9436</v>
       </c>
       <c r="B4848" t="s">
-        <v>9437</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4849" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4849" t="s">
+        <v>9437</v>
+      </c>
+      <c r="B4849" t="s">
         <v>9438</v>
-      </c>
-      <c r="B4849" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="4850" spans="1:2" x14ac:dyDescent="0.25">
@@ -68533,15 +68533,15 @@
         <v>9445</v>
       </c>
       <c r="B4853" t="s">
-        <v>9446</v>
+        <v>9360</v>
       </c>
     </row>
     <row r="4854" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4854" t="s">
+        <v>9446</v>
+      </c>
+      <c r="B4854" t="s">
         <v>9447</v>
-      </c>
-      <c r="B4854" t="s">
-        <v>9362</v>
       </c>
     </row>
     <row r="4855" spans="1:2" x14ac:dyDescent="0.25">
@@ -68597,15 +68597,15 @@
         <v>9460</v>
       </c>
       <c r="B4861" t="s">
-        <v>9461</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="4862" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4862" t="s">
+        <v>9461</v>
+      </c>
+      <c r="B4862" t="s">
         <v>9462</v>
-      </c>
-      <c r="B4862" t="s">
-        <v>8712</v>
       </c>
     </row>
     <row r="4863" spans="1:2" x14ac:dyDescent="0.25">
@@ -68621,15 +68621,15 @@
         <v>9465</v>
       </c>
       <c r="B4864" t="s">
-        <v>9466</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="4865" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4865" t="s">
+        <v>9466</v>
+      </c>
+      <c r="B4865" t="s">
         <v>9467</v>
-      </c>
-      <c r="B4865" t="s">
-        <v>8607</v>
       </c>
     </row>
     <row r="4866" spans="1:2" x14ac:dyDescent="0.25">
@@ -68709,23 +68709,23 @@
         <v>9486</v>
       </c>
       <c r="B4875" t="s">
-        <v>9487</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="4876" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4876" t="s">
-        <v>9488</v>
+        <v>9487</v>
       </c>
       <c r="B4876" t="s">
-        <v>8648</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="4877" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4877" t="s">
+        <v>9488</v>
+      </c>
+      <c r="B4877" t="s">
         <v>9489</v>
-      </c>
-      <c r="B4877" t="s">
-        <v>8659</v>
       </c>
     </row>
     <row r="4878" spans="1:2" x14ac:dyDescent="0.25">
@@ -68789,15 +68789,15 @@
         <v>9504</v>
       </c>
       <c r="B4885" t="s">
-        <v>9505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4886" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4886" t="s">
+        <v>9505</v>
+      </c>
+      <c r="B4886" t="s">
         <v>9506</v>
-      </c>
-      <c r="B4886" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="4887" spans="1:2" x14ac:dyDescent="0.25">
@@ -68853,15 +68853,15 @@
         <v>9519</v>
       </c>
       <c r="B4893" t="s">
-        <v>9520</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="4894" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4894" t="s">
+        <v>9520</v>
+      </c>
+      <c r="B4894" t="s">
         <v>9521</v>
-      </c>
-      <c r="B4894" t="s">
-        <v>5162</v>
       </c>
     </row>
     <row r="4895" spans="1:2" x14ac:dyDescent="0.25">
@@ -68869,15 +68869,15 @@
         <v>9522</v>
       </c>
       <c r="B4895" t="s">
-        <v>9523</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="4896" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4896" t="s">
+        <v>9523</v>
+      </c>
+      <c r="B4896" t="s">
         <v>9524</v>
-      </c>
-      <c r="B4896" t="s">
-        <v>8747</v>
       </c>
     </row>
     <row r="4897" spans="1:2" x14ac:dyDescent="0.25">
@@ -68933,15 +68933,15 @@
         <v>9537</v>
       </c>
       <c r="B4903" t="s">
-        <v>9538</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="4904" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4904" t="s">
+        <v>9538</v>
+      </c>
+      <c r="B4904" t="s">
         <v>9539</v>
-      </c>
-      <c r="B4904" t="s">
-        <v>4014</v>
       </c>
     </row>
     <row r="4905" spans="1:2" x14ac:dyDescent="0.25">
@@ -68949,15 +68949,15 @@
         <v>9540</v>
       </c>
       <c r="B4905" t="s">
-        <v>9541</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="4906" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4906" t="s">
+        <v>9541</v>
+      </c>
+      <c r="B4906" t="s">
         <v>9542</v>
-      </c>
-      <c r="B4906" t="s">
-        <v>8599</v>
       </c>
     </row>
     <row r="4907" spans="1:2" x14ac:dyDescent="0.25">
@@ -68973,15 +68973,15 @@
         <v>9545</v>
       </c>
       <c r="B4908" t="s">
-        <v>9546</v>
+        <v>9532</v>
       </c>
     </row>
     <row r="4909" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4909" t="s">
+        <v>9546</v>
+      </c>
+      <c r="B4909" t="s">
         <v>9547</v>
-      </c>
-      <c r="B4909" t="s">
-        <v>9534</v>
       </c>
     </row>
     <row r="4910" spans="1:2" x14ac:dyDescent="0.25">
@@ -69021,15 +69021,15 @@
         <v>9556</v>
       </c>
       <c r="B4914" t="s">
-        <v>9557</v>
+        <v>9532</v>
       </c>
     </row>
     <row r="4915" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4915" t="s">
+        <v>9557</v>
+      </c>
+      <c r="B4915" t="s">
         <v>9558</v>
-      </c>
-      <c r="B4915" t="s">
-        <v>9534</v>
       </c>
     </row>
     <row r="4916" spans="1:2" x14ac:dyDescent="0.25">
@@ -69045,15 +69045,15 @@
         <v>9561</v>
       </c>
       <c r="B4917" t="s">
-        <v>9562</v>
+        <v>9528</v>
       </c>
     </row>
     <row r="4918" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4918" t="s">
+        <v>9562</v>
+      </c>
+      <c r="B4918" t="s">
         <v>9563</v>
-      </c>
-      <c r="B4918" t="s">
-        <v>9530</v>
       </c>
     </row>
     <row r="4919" spans="1:2" x14ac:dyDescent="0.25">
@@ -69085,15 +69085,15 @@
         <v>9570</v>
       </c>
       <c r="B4922" t="s">
-        <v>9571</v>
+        <v>9014</v>
       </c>
     </row>
     <row r="4923" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4923" t="s">
+        <v>9571</v>
+      </c>
+      <c r="B4923" t="s">
         <v>9572</v>
-      </c>
-      <c r="B4923" t="s">
-        <v>9016</v>
       </c>
     </row>
     <row r="4924" spans="1:2" x14ac:dyDescent="0.25">
@@ -69157,15 +69157,15 @@
         <v>9587</v>
       </c>
       <c r="B4931" t="s">
-        <v>9588</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="4932" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4932" t="s">
+        <v>9588</v>
+      </c>
+      <c r="B4932" t="s">
         <v>9589</v>
-      </c>
-      <c r="B4932" t="s">
-        <v>8811</v>
       </c>
     </row>
     <row r="4933" spans="1:2" x14ac:dyDescent="0.25">
@@ -69173,39 +69173,39 @@
         <v>9590</v>
       </c>
       <c r="B4933" t="s">
-        <v>9591</v>
+        <v>9055</v>
       </c>
     </row>
     <row r="4934" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4934" t="s">
-        <v>9592</v>
+        <v>9591</v>
       </c>
       <c r="B4934" t="s">
-        <v>9057</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="4935" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4935" t="s">
-        <v>9593</v>
+        <v>9592</v>
       </c>
       <c r="B4935" t="s">
-        <v>8673</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4936" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4936" t="s">
-        <v>9594</v>
+        <v>9593</v>
       </c>
       <c r="B4936" t="s">
-        <v>242</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4937" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4937" t="s">
+        <v>9594</v>
+      </c>
+      <c r="B4937" t="s">
         <v>9595</v>
-      </c>
-      <c r="B4937" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="4938" spans="1:2" x14ac:dyDescent="0.25">
@@ -69221,15 +69221,15 @@
         <v>9598</v>
       </c>
       <c r="B4939" t="s">
-        <v>9599</v>
+        <v>9171</v>
       </c>
     </row>
     <row r="4940" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4940" t="s">
+        <v>9599</v>
+      </c>
+      <c r="B4940" t="s">
         <v>9600</v>
-      </c>
-      <c r="B4940" t="s">
-        <v>9173</v>
       </c>
     </row>
     <row r="4941" spans="1:2" x14ac:dyDescent="0.25">
@@ -69269,15 +69269,15 @@
         <v>9609</v>
       </c>
       <c r="B4945" t="s">
-        <v>9610</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="4946" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4946" t="s">
+        <v>9610</v>
+      </c>
+      <c r="B4946" t="s">
         <v>9611</v>
-      </c>
-      <c r="B4946" t="s">
-        <v>8648</v>
       </c>
     </row>
     <row r="4947" spans="1:2" x14ac:dyDescent="0.25">
@@ -69309,15 +69309,15 @@
         <v>9618</v>
       </c>
       <c r="B4950" t="s">
-        <v>9619</v>
+        <v>8664</v>
       </c>
     </row>
     <row r="4951" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4951" t="s">
+        <v>9619</v>
+      </c>
+      <c r="B4951" t="s">
         <v>9620</v>
-      </c>
-      <c r="B4951" t="s">
-        <v>8666</v>
       </c>
     </row>
     <row r="4952" spans="1:2" x14ac:dyDescent="0.25">
@@ -69333,15 +69333,15 @@
         <v>9623</v>
       </c>
       <c r="B4953" t="s">
-        <v>9624</v>
+        <v>6933</v>
       </c>
     </row>
     <row r="4954" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4954" t="s">
+        <v>9624</v>
+      </c>
+      <c r="B4954" t="s">
         <v>9625</v>
-      </c>
-      <c r="B4954" t="s">
-        <v>6935</v>
       </c>
     </row>
     <row r="4955" spans="1:2" x14ac:dyDescent="0.25">
@@ -69461,15 +69461,15 @@
         <v>9654</v>
       </c>
       <c r="B4969" t="s">
-        <v>9655</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="4970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4970" t="s">
+        <v>9655</v>
+      </c>
+      <c r="B4970" t="s">
         <v>9656</v>
-      </c>
-      <c r="B4970" t="s">
-        <v>2771</v>
       </c>
     </row>
     <row r="4971" spans="1:2" x14ac:dyDescent="0.25">
@@ -69485,15 +69485,15 @@
         <v>9659</v>
       </c>
       <c r="B4972" t="s">
-        <v>9660</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="4973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4973" t="s">
+        <v>9660</v>
+      </c>
+      <c r="B4973" t="s">
         <v>9661</v>
-      </c>
-      <c r="B4973" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="4974" spans="1:2" x14ac:dyDescent="0.25">
@@ -69525,15 +69525,15 @@
         <v>9668</v>
       </c>
       <c r="B4977" t="s">
-        <v>9669</v>
+        <v>5413</v>
       </c>
     </row>
     <row r="4978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4978" t="s">
+        <v>9669</v>
+      </c>
+      <c r="B4978" t="s">
         <v>9670</v>
-      </c>
-      <c r="B4978" t="s">
-        <v>5415</v>
       </c>
     </row>
     <row r="4979" spans="1:2" x14ac:dyDescent="0.25">
@@ -69573,15 +69573,15 @@
         <v>9679</v>
       </c>
       <c r="B4983" t="s">
-        <v>9680</v>
+        <v>8076</v>
       </c>
     </row>
     <row r="4984" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4984" t="s">
+        <v>9680</v>
+      </c>
+      <c r="B4984" t="s">
         <v>9681</v>
-      </c>
-      <c r="B4984" t="s">
-        <v>8078</v>
       </c>
     </row>
     <row r="4985" spans="1:2" x14ac:dyDescent="0.25">
@@ -69597,15 +69597,15 @@
         <v>9684</v>
       </c>
       <c r="B4986" t="s">
-        <v>9685</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4987" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4987" t="s">
+        <v>9685</v>
+      </c>
+      <c r="B4987" t="s">
         <v>9686</v>
-      </c>
-      <c r="B4987" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="4988" spans="1:2" x14ac:dyDescent="0.25">
@@ -69645,15 +69645,15 @@
         <v>9695</v>
       </c>
       <c r="B4992" t="s">
-        <v>9696</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4993" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4993" t="s">
+        <v>9696</v>
+      </c>
+      <c r="B4993" t="s">
         <v>9697</v>
-      </c>
-      <c r="B4993" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="4994" spans="1:2" x14ac:dyDescent="0.25">
@@ -69693,15 +69693,15 @@
         <v>9706</v>
       </c>
       <c r="B4998" t="s">
-        <v>9707</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="4999" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4999" t="s">
+        <v>9707</v>
+      </c>
+      <c r="B4999" t="s">
         <v>9708</v>
-      </c>
-      <c r="B4999" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="5000" spans="1:2" x14ac:dyDescent="0.25">
@@ -69837,15 +69837,15 @@
         <v>9741</v>
       </c>
       <c r="B5016" t="s">
-        <v>9742</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="5017" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5017" t="s">
+        <v>9742</v>
+      </c>
+      <c r="B5017" t="s">
         <v>9743</v>
-      </c>
-      <c r="B5017" t="s">
-        <v>5206</v>
       </c>
     </row>
     <row r="5018" spans="1:2" x14ac:dyDescent="0.25">
@@ -69885,15 +69885,15 @@
         <v>9752</v>
       </c>
       <c r="B5022" t="s">
-        <v>9753</v>
+        <v>9283</v>
       </c>
     </row>
     <row r="5023" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5023" t="s">
+        <v>9753</v>
+      </c>
+      <c r="B5023" t="s">
         <v>9754</v>
-      </c>
-      <c r="B5023" t="s">
-        <v>9285</v>
       </c>
     </row>
     <row r="5024" spans="1:2" x14ac:dyDescent="0.25">
@@ -69933,15 +69933,15 @@
         <v>9763</v>
       </c>
       <c r="B5028" t="s">
-        <v>9764</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="5029" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5029" t="s">
+        <v>9764</v>
+      </c>
+      <c r="B5029" t="s">
         <v>9765</v>
-      </c>
-      <c r="B5029" t="s">
-        <v>4039</v>
       </c>
     </row>
     <row r="5030" spans="1:2" x14ac:dyDescent="0.25">
@@ -69989,19 +69989,19 @@
         <v>9776</v>
       </c>
       <c r="B5035" t="s">
-        <v>9777</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="5036" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5036" t="s">
-        <v>9778</v>
+        <v>9779</v>
       </c>
       <c r="B5036" t="s">
-        <v>4367</v>
+        <v>9780</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5036" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B5035" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/LocCodes.xlsx
+++ b/LocCodes.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$5061</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$B$5659</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5061"/>
+  <dimension ref="A1:B5659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -61153,8 +61153,7184 @@
         </is>
       </c>
     </row>
+    <row r="5062">
+      <c r="A5062" t="inlineStr">
+        <is>
+          <t>SE2SK</t>
+        </is>
+      </c>
+      <c r="B5062" t="inlineStr">
+        <is>
+          <t>Sankt Olof</t>
+        </is>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" t="inlineStr">
+        <is>
+          <t>SE6VG</t>
+        </is>
+      </c>
+      <c r="B5063" t="inlineStr">
+        <is>
+          <t>Vedum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5064">
+      <c r="A5064" t="inlineStr">
+        <is>
+          <t>SEAA8</t>
+        </is>
+      </c>
+      <c r="B5064" t="inlineStr">
+        <is>
+          <t>Braas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" t="inlineStr">
+        <is>
+          <t>SEAAR</t>
+        </is>
+      </c>
+      <c r="B5065" t="inlineStr">
+        <is>
+          <t>Ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" t="inlineStr">
+        <is>
+          <t>SEABS</t>
+        </is>
+      </c>
+      <c r="B5066" t="inlineStr">
+        <is>
+          <t>Abisko</t>
+        </is>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" t="inlineStr">
+        <is>
+          <t>SEADA</t>
+        </is>
+      </c>
+      <c r="B5067" t="inlineStr">
+        <is>
+          <t>Aseda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5068">
+      <c r="A5068" t="inlineStr">
+        <is>
+          <t>SEADG</t>
+        </is>
+      </c>
+      <c r="B5068" t="inlineStr">
+        <is>
+          <t>Arildslage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" t="inlineStr">
+        <is>
+          <t>SEADK</t>
+        </is>
+      </c>
+      <c r="B5069" t="inlineStr">
+        <is>
+          <t>Adak</t>
+        </is>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" t="inlineStr">
+        <is>
+          <t>SEADO</t>
+        </is>
+      </c>
+      <c r="B5070" t="inlineStr">
+        <is>
+          <t>Adelso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" t="inlineStr">
+        <is>
+          <t>SEAEL</t>
+        </is>
+      </c>
+      <c r="B5071" t="inlineStr">
+        <is>
+          <t>Aelvsered</t>
+        </is>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" t="inlineStr">
+        <is>
+          <t>SEAGB</t>
+        </is>
+      </c>
+      <c r="B5072" t="inlineStr">
+        <is>
+          <t>Agnesberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5073">
+      <c r="A5073" t="inlineStr">
+        <is>
+          <t>SEAGE</t>
+        </is>
+      </c>
+      <c r="B5073" t="inlineStr">
+        <is>
+          <t>Ange</t>
+        </is>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" t="inlineStr">
+        <is>
+          <t>SEAHR</t>
+        </is>
+      </c>
+      <c r="B5074" t="inlineStr">
+        <is>
+          <t>Aha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5075">
+      <c r="A5075" t="inlineStr">
+        <is>
+          <t>SEAHT</t>
+        </is>
+      </c>
+      <c r="B5075" t="inlineStr">
+        <is>
+          <t>Alghult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5076">
+      <c r="A5076" t="inlineStr">
+        <is>
+          <t>SEAJG</t>
+        </is>
+      </c>
+      <c r="B5076" t="inlineStr">
+        <is>
+          <t>Emmaljunga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5077">
+      <c r="A5077" t="inlineStr">
+        <is>
+          <t>SEAJR</t>
+        </is>
+      </c>
+      <c r="B5077" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+    </row>
+    <row r="5078">
+      <c r="A5078" t="inlineStr">
+        <is>
+          <t>SEAKP</t>
+        </is>
+      </c>
+      <c r="B5078" t="inlineStr">
+        <is>
+          <t>Akarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5079">
+      <c r="A5079" t="inlineStr">
+        <is>
+          <t>SEAKR</t>
+        </is>
+      </c>
+      <c r="B5079" t="inlineStr">
+        <is>
+          <t>Ankarsrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5080">
+      <c r="A5080" t="inlineStr">
+        <is>
+          <t>SEALA</t>
+        </is>
+      </c>
+      <c r="B5080" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" t="inlineStr">
+        <is>
+          <t>SEALB</t>
+        </is>
+      </c>
+      <c r="B5081" t="inlineStr">
+        <is>
+          <t>Alby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" t="inlineStr">
+        <is>
+          <t>SEALE</t>
+        </is>
+      </c>
+      <c r="B5082" t="inlineStr">
+        <is>
+          <t>Asele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="inlineStr">
+        <is>
+          <t>SEALF</t>
+        </is>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>Alfredshem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" t="inlineStr">
+        <is>
+          <t>SEALG</t>
+        </is>
+      </c>
+      <c r="B5084" t="inlineStr">
+        <is>
+          <t>Alberga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="inlineStr">
+        <is>
+          <t>SEALN</t>
+        </is>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>Alvenas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" t="inlineStr">
+        <is>
+          <t>SEANA</t>
+        </is>
+      </c>
+      <c r="B5086" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="inlineStr">
+        <is>
+          <t>SEANK</t>
+        </is>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>Ankarsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" t="inlineStr">
+        <is>
+          <t>SEANN</t>
+        </is>
+      </c>
+      <c r="B5088" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="inlineStr">
+        <is>
+          <t>SEAQ2</t>
+        </is>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" t="inlineStr">
+        <is>
+          <t>SEARD</t>
+        </is>
+      </c>
+      <c r="B5090" t="inlineStr">
+        <is>
+          <t>Arstadal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5091">
+      <c r="A5091" t="inlineStr">
+        <is>
+          <t>SEARG</t>
+        </is>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" t="inlineStr">
+        <is>
+          <t>SEARK</t>
+        </is>
+      </c>
+      <c r="B5092" t="inlineStr">
+        <is>
+          <t>Arnoviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="inlineStr">
+        <is>
+          <t>SEASK</t>
+        </is>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>Askloster</t>
+        </is>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" t="inlineStr">
+        <is>
+          <t>SEASL</t>
+        </is>
+      </c>
+      <c r="B5094" t="inlineStr">
+        <is>
+          <t>Anderslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="inlineStr">
+        <is>
+          <t>SEASM</t>
+        </is>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>Alstermo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" t="inlineStr">
+        <is>
+          <t>SEATV</t>
+        </is>
+      </c>
+      <c r="B5096" t="inlineStr">
+        <is>
+          <t>Atvidaberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="inlineStr">
+        <is>
+          <t>SEAUD</t>
+        </is>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>Arsunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" t="inlineStr">
+        <is>
+          <t>SEASH</t>
+        </is>
+      </c>
+      <c r="B5098" t="inlineStr">
+        <is>
+          <t>Ashammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="inlineStr">
+        <is>
+          <t>SEAVK</t>
+        </is>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>Almvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5100">
+      <c r="A5100" t="inlineStr">
+        <is>
+          <t>SEB5P</t>
+        </is>
+      </c>
+      <c r="B5100" t="inlineStr">
+        <is>
+          <t>Blentarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5101">
+      <c r="A5101" t="inlineStr">
+        <is>
+          <t>SEBAC</t>
+        </is>
+      </c>
+      <c r="B5101" t="inlineStr">
+        <is>
+          <t>Backviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5102">
+      <c r="A5102" t="inlineStr">
+        <is>
+          <t>SEBAL</t>
+        </is>
+      </c>
+      <c r="B5102" t="inlineStr">
+        <is>
+          <t>Ballingslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5103">
+      <c r="A5103" t="inlineStr">
+        <is>
+          <t>SEBAT</t>
+        </is>
+      </c>
+      <c r="B5103" t="inlineStr">
+        <is>
+          <t>Batskarsnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5104">
+      <c r="A5104" t="inlineStr">
+        <is>
+          <t>SEBBE</t>
+        </is>
+      </c>
+      <c r="B5104" t="inlineStr">
+        <is>
+          <t>Baberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5105">
+      <c r="A5105" t="inlineStr">
+        <is>
+          <t>SEBBH</t>
+        </is>
+      </c>
+      <c r="B5105" t="inlineStr">
+        <is>
+          <t>Barsebackshamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5106">
+      <c r="A5106" t="inlineStr">
+        <is>
+          <t>SEBCD</t>
+        </is>
+      </c>
+      <c r="B5106" t="inlineStr">
+        <is>
+          <t>Backaryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5107">
+      <c r="A5107" t="inlineStr">
+        <is>
+          <t>SEBCS</t>
+        </is>
+      </c>
+      <c r="B5107" t="inlineStr">
+        <is>
+          <t>Blattnicksele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5108">
+      <c r="A5108" t="inlineStr">
+        <is>
+          <t>SEBDQ</t>
+        </is>
+      </c>
+      <c r="B5108" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5109">
+      <c r="A5109" t="inlineStr">
+        <is>
+          <t>SEBER</t>
+        </is>
+      </c>
+      <c r="B5109" t="inlineStr">
+        <is>
+          <t>Bergs oljehamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5110">
+      <c r="A5110" t="inlineStr">
+        <is>
+          <t>SEBFS</t>
+        </is>
+      </c>
+      <c r="B5110" t="inlineStr">
+        <is>
+          <t>Backfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5111">
+      <c r="A5111" t="inlineStr">
+        <is>
+          <t>SEBGA</t>
+        </is>
+      </c>
+      <c r="B5111" t="inlineStr">
+        <is>
+          <t>Berga Orlogsskolor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5112">
+      <c r="A5112" t="inlineStr">
+        <is>
+          <t>SEBGB</t>
+        </is>
+      </c>
+      <c r="B5112" t="inlineStr">
+        <is>
+          <t>Bjuraker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5113">
+      <c r="A5113" t="inlineStr">
+        <is>
+          <t>SEBGF</t>
+        </is>
+      </c>
+      <c r="B5113" t="inlineStr">
+        <is>
+          <t>Bergeforsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5114">
+      <c r="A5114" t="inlineStr">
+        <is>
+          <t>SEBGO</t>
+        </is>
+      </c>
+      <c r="B5114" t="inlineStr">
+        <is>
+          <t>Bagarmossen/Stockholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5115">
+      <c r="A5115" t="inlineStr">
+        <is>
+          <t>SEBHM</t>
+        </is>
+      </c>
+      <c r="B5115" t="inlineStr">
+        <is>
+          <t>Bergshamra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5116">
+      <c r="A5116" t="inlineStr">
+        <is>
+          <t>SEBJA</t>
+        </is>
+      </c>
+      <c r="B5116" t="inlineStr">
+        <is>
+          <t>Bjarnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5117">
+      <c r="A5117" t="inlineStr">
+        <is>
+          <t>SEBJN</t>
+        </is>
+      </c>
+      <c r="B5117" t="inlineStr">
+        <is>
+          <t>Bjorneborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5118">
+      <c r="A5118" t="inlineStr">
+        <is>
+          <t>SEBJR</t>
+        </is>
+      </c>
+      <c r="B5118" t="inlineStr">
+        <is>
+          <t>Bjarred</t>
+        </is>
+      </c>
+    </row>
+    <row r="5119">
+      <c r="A5119" t="inlineStr">
+        <is>
+          <t>SEBJV</t>
+        </is>
+      </c>
+      <c r="B5119" t="inlineStr">
+        <is>
+          <t>Bjorkvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5120">
+      <c r="A5120" t="inlineStr">
+        <is>
+          <t>SEBKS</t>
+        </is>
+      </c>
+      <c r="B5120" t="inlineStr">
+        <is>
+          <t>Backefors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5121">
+      <c r="A5121" t="inlineStr">
+        <is>
+          <t>SEBKU</t>
+        </is>
+      </c>
+      <c r="B5121" t="inlineStr">
+        <is>
+          <t>Broakulla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5122">
+      <c r="A5122" t="inlineStr">
+        <is>
+          <t>SEBLV</t>
+        </is>
+      </c>
+      <c r="B5122" t="inlineStr">
+        <is>
+          <t>Ballstaviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5123">
+      <c r="A5123" t="inlineStr">
+        <is>
+          <t>SEBMK</t>
+        </is>
+      </c>
+      <c r="B5123" t="inlineStr">
+        <is>
+          <t>Botsmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5124">
+      <c r="A5124" t="inlineStr">
+        <is>
+          <t>SEBKY</t>
+        </is>
+      </c>
+      <c r="B5124" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+    </row>
+    <row r="5125">
+      <c r="A5125" t="inlineStr">
+        <is>
+          <t>SEBLA</t>
+        </is>
+      </c>
+      <c r="B5125" t="inlineStr">
+        <is>
+          <t>Blankaholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5126">
+      <c r="A5126" t="inlineStr">
+        <is>
+          <t>SEBNF</t>
+        </is>
+      </c>
+      <c r="B5126" t="inlineStr">
+        <is>
+          <t>Brannfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5127">
+      <c r="A5127" t="inlineStr">
+        <is>
+          <t>SEBOG</t>
+        </is>
+      </c>
+      <c r="B5127" t="inlineStr">
+        <is>
+          <t>Borensberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5128">
+      <c r="A5128" t="inlineStr">
+        <is>
+          <t>SEBOH</t>
+        </is>
+      </c>
+      <c r="B5128" t="inlineStr">
+        <is>
+          <t>Bohus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5129">
+      <c r="A5129" t="inlineStr">
+        <is>
+          <t>SEBOM</t>
+        </is>
+      </c>
+      <c r="B5129" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5130">
+      <c r="A5130" t="inlineStr">
+        <is>
+          <t>SEBON</t>
+        </is>
+      </c>
+      <c r="B5130" t="inlineStr">
+        <is>
+          <t>Borghamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5131">
+      <c r="A5131" t="inlineStr">
+        <is>
+          <t>SEBPG</t>
+        </is>
+      </c>
+      <c r="B5131" t="inlineStr">
+        <is>
+          <t>Bispgarden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5132">
+      <c r="A5132" t="inlineStr">
+        <is>
+          <t>SEBRA</t>
+        </is>
+      </c>
+      <c r="B5132" t="inlineStr">
+        <is>
+          <t>Bralanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5133">
+      <c r="A5133" t="inlineStr">
+        <is>
+          <t>SEBRE</t>
+        </is>
+      </c>
+      <c r="B5133" t="inlineStr">
+        <is>
+          <t>Bredviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5134">
+      <c r="A5134" t="inlineStr">
+        <is>
+          <t>SEBRG</t>
+        </is>
+      </c>
+      <c r="B5134" t="inlineStr">
+        <is>
+          <t>Bergsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5135">
+      <c r="A5135" t="inlineStr">
+        <is>
+          <t>SEBRH</t>
+        </is>
+      </c>
+      <c r="B5135" t="inlineStr">
+        <is>
+          <t>Brakne-Hoby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5136">
+      <c r="A5136" t="inlineStr">
+        <is>
+          <t>SEBRO</t>
+        </is>
+      </c>
+      <c r="B5136" t="inlineStr">
+        <is>
+          <t>Brofjorden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5137">
+      <c r="A5137" t="inlineStr">
+        <is>
+          <t>SEBRS</t>
+        </is>
+      </c>
+      <c r="B5137" t="inlineStr">
+        <is>
+          <t>Braas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5138">
+      <c r="A5138" t="inlineStr">
+        <is>
+          <t>SEBRT</t>
+        </is>
+      </c>
+      <c r="B5138" t="inlineStr">
+        <is>
+          <t>Brottby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5139">
+      <c r="A5139" t="inlineStr">
+        <is>
+          <t>SEBSI</t>
+        </is>
+      </c>
+      <c r="B5139" t="inlineStr">
+        <is>
+          <t>Bunkeflostrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5140">
+      <c r="A5140" t="inlineStr">
+        <is>
+          <t>SEBSP</t>
+        </is>
+      </c>
+      <c r="B5140" t="inlineStr">
+        <is>
+          <t>Brosarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5141">
+      <c r="A5141" t="inlineStr">
+        <is>
+          <t>SEBSR</t>
+        </is>
+      </c>
+      <c r="B5141" t="inlineStr">
+        <is>
+          <t>Burseryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5142">
+      <c r="A5142" t="inlineStr">
+        <is>
+          <t>SEBTS</t>
+        </is>
+      </c>
+      <c r="B5142" t="inlineStr">
+        <is>
+          <t>Bastutrask</t>
+        </is>
+      </c>
+    </row>
+    <row r="5143">
+      <c r="A5143" t="inlineStr">
+        <is>
+          <t>SEBUN</t>
+        </is>
+      </c>
+      <c r="B5143" t="inlineStr">
+        <is>
+          <t>Brunna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5144">
+      <c r="A5144" t="inlineStr">
+        <is>
+          <t>SEBUR</t>
+        </is>
+      </c>
+      <c r="B5144" t="inlineStr">
+        <is>
+          <t>Burea</t>
+        </is>
+      </c>
+    </row>
+    <row r="5145">
+      <c r="A5145" t="inlineStr">
+        <is>
+          <t>SEBUV</t>
+        </is>
+      </c>
+      <c r="B5145" t="inlineStr">
+        <is>
+          <t>Burgsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5146">
+      <c r="A5146" t="inlineStr">
+        <is>
+          <t>SEBVK</t>
+        </is>
+      </c>
+      <c r="B5146" t="inlineStr">
+        <is>
+          <t>Braviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5147">
+      <c r="A5147" t="inlineStr">
+        <is>
+          <t>SEBVN</t>
+        </is>
+      </c>
+      <c r="B5147" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5148">
+      <c r="A5148" t="inlineStr">
+        <is>
+          <t>SEBYS</t>
+        </is>
+      </c>
+      <c r="B5148" t="inlineStr">
+        <is>
+          <t>Byske (Brannfors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5149">
+      <c r="A5149" t="inlineStr">
+        <is>
+          <t>SEBYX</t>
+        </is>
+      </c>
+      <c r="B5149" t="inlineStr">
+        <is>
+          <t>Byxelkrok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5150">
+      <c r="A5150" t="inlineStr">
+        <is>
+          <t>SECSA</t>
+        </is>
+      </c>
+      <c r="B5150" t="inlineStr">
+        <is>
+          <t>Soderkulla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="inlineStr">
+        <is>
+          <t>SEDAL</t>
+        </is>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>Dals-Langed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" t="inlineStr">
+        <is>
+          <t>SEDAN</t>
+        </is>
+      </c>
+      <c r="B5152" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="inlineStr">
+        <is>
+          <t>SEDD7</t>
+        </is>
+      </c>
+      <c r="B5153" t="inlineStr">
+        <is>
+          <t>Djuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" t="inlineStr">
+        <is>
+          <t>SEDEJ</t>
+        </is>
+      </c>
+      <c r="B5154" t="inlineStr">
+        <is>
+          <t>Deje</t>
+        </is>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="inlineStr">
+        <is>
+          <t>SEDEL</t>
+        </is>
+      </c>
+      <c r="B5155" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" t="inlineStr">
+        <is>
+          <t>SEDFO</t>
+        </is>
+      </c>
+      <c r="B5156" t="inlineStr">
+        <is>
+          <t>Dalsjofors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5157">
+      <c r="A5157" t="inlineStr">
+        <is>
+          <t>SEDHN</t>
+        </is>
+      </c>
+      <c r="B5157" t="inlineStr">
+        <is>
+          <t>Djurhamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" t="inlineStr">
+        <is>
+          <t>SEDJB</t>
+        </is>
+      </c>
+      <c r="B5158" t="inlineStr">
+        <is>
+          <t>Dosjebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="inlineStr">
+        <is>
+          <t>SEDJM</t>
+        </is>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>Dala-Jarna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" t="inlineStr">
+        <is>
+          <t>SEDJN</t>
+        </is>
+      </c>
+      <c r="B5160" t="inlineStr">
+        <is>
+          <t>Djuron</t>
+        </is>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="inlineStr">
+        <is>
+          <t>SEDJP</t>
+        </is>
+      </c>
+      <c r="B5161" t="inlineStr">
+        <is>
+          <t>Djupvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" t="inlineStr">
+        <is>
+          <t>SEDJU</t>
+        </is>
+      </c>
+      <c r="B5162" t="inlineStr">
+        <is>
+          <t>Djurmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="inlineStr">
+        <is>
+          <t>SEDLB</t>
+        </is>
+      </c>
+      <c r="B5163" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" t="inlineStr">
+        <is>
+          <t>SEDNG</t>
+        </is>
+      </c>
+      <c r="B5164" t="inlineStr">
+        <is>
+          <t>Dingle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="inlineStr">
+        <is>
+          <t>SEDNK</t>
+        </is>
+      </c>
+      <c r="B5165" t="inlineStr">
+        <is>
+          <t>Dannike</t>
+        </is>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" t="inlineStr">
+        <is>
+          <t>SEDON</t>
+        </is>
+      </c>
+      <c r="B5166" t="inlineStr">
+        <is>
+          <t>Donso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="inlineStr">
+        <is>
+          <t>SEDRE</t>
+        </is>
+      </c>
+      <c r="B5167" t="inlineStr">
+        <is>
+          <t>Sexdrega</t>
+        </is>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" t="inlineStr">
+        <is>
+          <t>SEDRT</t>
+        </is>
+      </c>
+      <c r="B5168" t="inlineStr">
+        <is>
+          <t>Drottningholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="inlineStr">
+        <is>
+          <t>SEDSE</t>
+        </is>
+      </c>
+      <c r="B5169" t="inlineStr">
+        <is>
+          <t>Dvaersaett</t>
+        </is>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" t="inlineStr">
+        <is>
+          <t>SEDSM</t>
+        </is>
+      </c>
+      <c r="B5170" t="inlineStr">
+        <is>
+          <t>Djursholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="inlineStr">
+        <is>
+          <t>SEDYN</t>
+        </is>
+      </c>
+      <c r="B5171" t="inlineStr">
+        <is>
+          <t>Dynas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" t="inlineStr">
+        <is>
+          <t>SEECK</t>
+        </is>
+      </c>
+      <c r="B5172" t="inlineStr">
+        <is>
+          <t>Lackeby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="inlineStr">
+        <is>
+          <t>SEEDA</t>
+        </is>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" t="inlineStr">
+        <is>
+          <t>SEEDE</t>
+        </is>
+      </c>
+      <c r="B5174" t="inlineStr">
+        <is>
+          <t>Edane</t>
+        </is>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="inlineStr">
+        <is>
+          <t>SEEDV</t>
+        </is>
+      </c>
+      <c r="B5175" t="inlineStr">
+        <is>
+          <t>Edsvalla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" t="inlineStr">
+        <is>
+          <t>SEEDZ</t>
+        </is>
+      </c>
+      <c r="B5176" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="inlineStr">
+        <is>
+          <t>SEEEN</t>
+        </is>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>Ekenassjon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" t="inlineStr">
+        <is>
+          <t>SEEHR</t>
+        </is>
+      </c>
+      <c r="B5178" t="inlineStr">
+        <is>
+          <t>Enhorna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="inlineStr">
+        <is>
+          <t>SEEKH</t>
+        </is>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>Eksharad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" t="inlineStr">
+        <is>
+          <t>SEELL</t>
+        </is>
+      </c>
+      <c r="B5180" t="inlineStr">
+        <is>
+          <t>Elleholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="inlineStr">
+        <is>
+          <t>SEELO</t>
+        </is>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>Ellos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" t="inlineStr">
+        <is>
+          <t>SEENE</t>
+        </is>
+      </c>
+      <c r="B5182" t="inlineStr">
+        <is>
+          <t>Enebyberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="inlineStr">
+        <is>
+          <t>SEERI</t>
+        </is>
+      </c>
+      <c r="B5183" t="inlineStr">
+        <is>
+          <t>Erikslund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" t="inlineStr">
+        <is>
+          <t>SEERK</t>
+        </is>
+      </c>
+      <c r="B5184" t="inlineStr">
+        <is>
+          <t>Eriksmala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="inlineStr">
+        <is>
+          <t>SEERS</t>
+        </is>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>Ersmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" t="inlineStr">
+        <is>
+          <t>SEESS</t>
+        </is>
+      </c>
+      <c r="B5186" t="inlineStr">
+        <is>
+          <t>Essvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="inlineStr">
+        <is>
+          <t>SEEVL</t>
+        </is>
+      </c>
+      <c r="B5187" t="inlineStr">
+        <is>
+          <t>Ervalla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" t="inlineStr">
+        <is>
+          <t>SEFAD</t>
+        </is>
+      </c>
+      <c r="B5188" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="inlineStr">
+        <is>
+          <t>SEFAE</t>
+        </is>
+      </c>
+      <c r="B5189" t="inlineStr">
+        <is>
+          <t>Fargelanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" t="inlineStr">
+        <is>
+          <t>SEFAK</t>
+        </is>
+      </c>
+      <c r="B5190" t="inlineStr">
+        <is>
+          <t>Fagervik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="inlineStr">
+        <is>
+          <t>SEFAS</t>
+        </is>
+      </c>
+      <c r="B5191" t="inlineStr">
+        <is>
+          <t>Fagersanna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" t="inlineStr">
+        <is>
+          <t>SEFAV</t>
+        </is>
+      </c>
+      <c r="B5192" t="inlineStr">
+        <is>
+          <t>Farlov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="inlineStr">
+        <is>
+          <t>SEFBK</t>
+        </is>
+      </c>
+      <c r="B5193" t="inlineStr">
+        <is>
+          <t>Fiskebackskil</t>
+        </is>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" t="inlineStr">
+        <is>
+          <t>SEFBO</t>
+        </is>
+      </c>
+      <c r="B5194" t="inlineStr">
+        <is>
+          <t>Farbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="inlineStr">
+        <is>
+          <t>SEFBY</t>
+        </is>
+      </c>
+      <c r="B5195" t="inlineStr">
+        <is>
+          <t>Floby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" t="inlineStr">
+        <is>
+          <t>SEFDL</t>
+        </is>
+      </c>
+      <c r="B5196" t="inlineStr">
+        <is>
+          <t>Fredriksdal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="inlineStr">
+        <is>
+          <t>SEFDS</t>
+        </is>
+      </c>
+      <c r="B5197" t="inlineStr">
+        <is>
+          <t>Frandefors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" t="inlineStr">
+        <is>
+          <t>SEFGN</t>
+        </is>
+      </c>
+      <c r="B5198" t="inlineStr">
+        <is>
+          <t>Flyinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="inlineStr">
+        <is>
+          <t>SEFGS</t>
+        </is>
+      </c>
+      <c r="B5199" t="inlineStr">
+        <is>
+          <t>Fagelfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" t="inlineStr">
+        <is>
+          <t>SEFIK</t>
+        </is>
+      </c>
+      <c r="B5200" t="inlineStr">
+        <is>
+          <t>Fiskeby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="inlineStr">
+        <is>
+          <t>SEFIS</t>
+        </is>
+      </c>
+      <c r="B5201" t="inlineStr">
+        <is>
+          <t>Fiskeback</t>
+        </is>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" t="inlineStr">
+        <is>
+          <t>SEFJA</t>
+        </is>
+      </c>
+      <c r="B5202" t="inlineStr">
+        <is>
+          <t>Fjallbacka</t>
+        </is>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="inlineStr">
+        <is>
+          <t>SEFLD</t>
+        </is>
+      </c>
+      <c r="B5203" t="inlineStr">
+        <is>
+          <t>Furulund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" t="inlineStr">
+        <is>
+          <t>SEFLI</t>
+        </is>
+      </c>
+      <c r="B5204" t="inlineStr">
+        <is>
+          <t>Flivik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="inlineStr">
+        <is>
+          <t>SEFLM</t>
+        </is>
+      </c>
+      <c r="B5205" t="inlineStr">
+        <is>
+          <t>Flemingsberg/Stockholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" t="inlineStr">
+        <is>
+          <t>SEFLX</t>
+        </is>
+      </c>
+      <c r="B5206" t="inlineStr">
+        <is>
+          <t>Flaxenvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="inlineStr">
+        <is>
+          <t>SEFNA</t>
+        </is>
+      </c>
+      <c r="B5207" t="inlineStr">
+        <is>
+          <t>Finja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" t="inlineStr">
+        <is>
+          <t>SEFOA</t>
+        </is>
+      </c>
+      <c r="B5208" t="inlineStr">
+        <is>
+          <t>Forsbacka</t>
+        </is>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="inlineStr">
+        <is>
+          <t>SEFOM</t>
+        </is>
+      </c>
+      <c r="B5209" t="inlineStr">
+        <is>
+          <t>Forserum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" t="inlineStr">
+        <is>
+          <t>SEFON</t>
+        </is>
+      </c>
+      <c r="B5210" t="inlineStr">
+        <is>
+          <t>Fornasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="inlineStr">
+        <is>
+          <t>SEFOR</t>
+        </is>
+      </c>
+      <c r="B5211" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" t="inlineStr">
+        <is>
+          <t>SEFRA</t>
+        </is>
+      </c>
+      <c r="B5212" t="inlineStr">
+        <is>
+          <t>Frano</t>
+        </is>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="inlineStr">
+        <is>
+          <t>SEFRK</t>
+        </is>
+      </c>
+      <c r="B5213" t="inlineStr">
+        <is>
+          <t>Flarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" t="inlineStr">
+        <is>
+          <t>SEFRN</t>
+        </is>
+      </c>
+      <c r="B5214" t="inlineStr">
+        <is>
+          <t>Froson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="inlineStr">
+        <is>
+          <t>SEFSA</t>
+        </is>
+      </c>
+      <c r="B5215" t="inlineStr">
+        <is>
+          <t>Frillesas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" t="inlineStr">
+        <is>
+          <t>SEFSB</t>
+        </is>
+      </c>
+      <c r="B5216" t="inlineStr">
+        <is>
+          <t>Falsterbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="inlineStr">
+        <is>
+          <t>SEFTY</t>
+        </is>
+      </c>
+      <c r="B5217" t="inlineStr">
+        <is>
+          <t>Fritsla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" t="inlineStr">
+        <is>
+          <t>SEFVK</t>
+        </is>
+      </c>
+      <c r="B5218" t="inlineStr">
+        <is>
+          <t>Forsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="inlineStr">
+        <is>
+          <t>SEGAA</t>
+        </is>
+      </c>
+      <c r="B5219" t="inlineStr">
+        <is>
+          <t>Granna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="inlineStr">
+        <is>
+          <t>SEGAD</t>
+        </is>
+      </c>
+      <c r="B5220" t="inlineStr">
+        <is>
+          <t>Gaddviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="inlineStr">
+        <is>
+          <t>SEGAL</t>
+        </is>
+      </c>
+      <c r="B5221" t="inlineStr">
+        <is>
+          <t>Gallo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="inlineStr">
+        <is>
+          <t>SEGAR</t>
+        </is>
+      </c>
+      <c r="B5222" t="inlineStr">
+        <is>
+          <t>Garphyttan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="inlineStr">
+        <is>
+          <t>SEGAS</t>
+        </is>
+      </c>
+      <c r="B5223" t="inlineStr">
+        <is>
+          <t>Garsnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="inlineStr">
+        <is>
+          <t>SEGDE</t>
+        </is>
+      </c>
+      <c r="B5224" t="inlineStr">
+        <is>
+          <t>Gaddede</t>
+        </is>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="inlineStr">
+        <is>
+          <t>SEGDG</t>
+        </is>
+      </c>
+      <c r="B5225" t="inlineStr">
+        <is>
+          <t>Grodinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="inlineStr">
+        <is>
+          <t>SEGGE</t>
+        </is>
+      </c>
+      <c r="B5226" t="inlineStr">
+        <is>
+          <t>Grangarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="inlineStr">
+        <is>
+          <t>SEGHT</t>
+        </is>
+      </c>
+      <c r="B5227" t="inlineStr">
+        <is>
+          <t>Guldsmedshyttan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="inlineStr">
+        <is>
+          <t>SEGKA</t>
+        </is>
+      </c>
+      <c r="B5228" t="inlineStr">
+        <is>
+          <t>Gronskara</t>
+        </is>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="inlineStr">
+        <is>
+          <t>SEGKG</t>
+        </is>
+      </c>
+      <c r="B5229" t="inlineStr">
+        <is>
+          <t>Gards Kopinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="inlineStr">
+        <is>
+          <t>SEGKS</t>
+        </is>
+      </c>
+      <c r="B5230" t="inlineStr">
+        <is>
+          <t>Gustavsvik/Stockholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="inlineStr">
+        <is>
+          <t>SEGKV</t>
+        </is>
+      </c>
+      <c r="B5231" t="inlineStr">
+        <is>
+          <t>Grankullavik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="inlineStr">
+        <is>
+          <t>SEGLA</t>
+        </is>
+      </c>
+      <c r="B5232" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="inlineStr">
+        <is>
+          <t>SEGLB</t>
+        </is>
+      </c>
+      <c r="B5233" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="inlineStr">
+        <is>
+          <t>SEGLM</t>
+        </is>
+      </c>
+      <c r="B5234" t="inlineStr">
+        <is>
+          <t>Glommen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="inlineStr">
+        <is>
+          <t>SEGML</t>
+        </is>
+      </c>
+      <c r="B5235" t="inlineStr">
+        <is>
+          <t>Gemla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="inlineStr">
+        <is>
+          <t>SEGNA</t>
+        </is>
+      </c>
+      <c r="B5236" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="inlineStr">
+        <is>
+          <t>SEGOA</t>
+        </is>
+      </c>
+      <c r="B5237" t="inlineStr">
+        <is>
+          <t>Gota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="inlineStr">
+        <is>
+          <t>SEGOR</t>
+        </is>
+      </c>
+      <c r="B5238" t="inlineStr">
+        <is>
+          <t>Gorsingeholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="inlineStr">
+        <is>
+          <t>SEGR5</t>
+        </is>
+      </c>
+      <c r="B5239" t="inlineStr">
+        <is>
+          <t>Grillby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="inlineStr">
+        <is>
+          <t>SEGR9</t>
+        </is>
+      </c>
+      <c r="B5240" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="inlineStr">
+        <is>
+          <t>SEGRD</t>
+        </is>
+      </c>
+      <c r="B5241" t="inlineStr">
+        <is>
+          <t>Grundsund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="inlineStr">
+        <is>
+          <t>SEGRE</t>
+        </is>
+      </c>
+      <c r="B5242" t="inlineStr">
+        <is>
+          <t>Grebbestad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="inlineStr">
+        <is>
+          <t>SEGRH</t>
+        </is>
+      </c>
+      <c r="B5243" t="inlineStr">
+        <is>
+          <t>Grisslehamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="inlineStr">
+        <is>
+          <t>SEGRK</t>
+        </is>
+      </c>
+      <c r="B5244" t="inlineStr">
+        <is>
+          <t>Grundvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="inlineStr">
+        <is>
+          <t>SEGRM</t>
+        </is>
+      </c>
+      <c r="B5245" t="inlineStr">
+        <is>
+          <t>Grimslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="inlineStr">
+        <is>
+          <t>SEGRN</t>
+        </is>
+      </c>
+      <c r="B5246" t="inlineStr">
+        <is>
+          <t>Grangesberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="inlineStr">
+        <is>
+          <t>SEGRP</t>
+        </is>
+      </c>
+      <c r="B5247" t="inlineStr">
+        <is>
+          <t>Grastorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="inlineStr">
+        <is>
+          <t>SEGRT</t>
+        </is>
+      </c>
+      <c r="B5248" t="inlineStr">
+        <is>
+          <t>Grytgol</t>
+        </is>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="inlineStr">
+        <is>
+          <t>SEGRV</t>
+        </is>
+      </c>
+      <c r="B5249" t="inlineStr">
+        <is>
+          <t>Grevie</t>
+        </is>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="inlineStr">
+        <is>
+          <t>SEGSP</t>
+        </is>
+      </c>
+      <c r="B5250" t="inlineStr">
+        <is>
+          <t>Gullspang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="inlineStr">
+        <is>
+          <t>SEGUM</t>
+        </is>
+      </c>
+      <c r="B5251" t="inlineStr">
+        <is>
+          <t>Gusum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="inlineStr">
+        <is>
+          <t>SEGUN</t>
+        </is>
+      </c>
+      <c r="B5252" t="inlineStr">
+        <is>
+          <t>Gunnebo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="inlineStr">
+        <is>
+          <t>SEGUO</t>
+        </is>
+      </c>
+      <c r="B5253" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="inlineStr">
+        <is>
+          <t>SEGVA</t>
+        </is>
+      </c>
+      <c r="B5254" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="inlineStr">
+        <is>
+          <t>SEGVN</t>
+        </is>
+      </c>
+      <c r="B5255" t="inlineStr">
+        <is>
+          <t>Gravarne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="inlineStr">
+        <is>
+          <t>SEGYT</t>
+        </is>
+      </c>
+      <c r="B5256" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="inlineStr">
+        <is>
+          <t>SEHAC</t>
+        </is>
+      </c>
+      <c r="B5257" t="inlineStr">
+        <is>
+          <t>Hackas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="inlineStr">
+        <is>
+          <t>SEHAG</t>
+        </is>
+      </c>
+      <c r="B5258" t="inlineStr">
+        <is>
+          <t>Hagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="inlineStr">
+        <is>
+          <t>SEHAJ</t>
+        </is>
+      </c>
+      <c r="B5259" t="inlineStr">
+        <is>
+          <t>Haljarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="inlineStr">
+        <is>
+          <t>SEHAR</t>
+        </is>
+      </c>
+      <c r="B5260" t="inlineStr">
+        <is>
+          <t>Harspranget</t>
+        </is>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="inlineStr">
+        <is>
+          <t>SEHAS</t>
+        </is>
+      </c>
+      <c r="B5261" t="inlineStr">
+        <is>
+          <t>Hallstanas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="inlineStr">
+        <is>
+          <t>SEHAV</t>
+        </is>
+      </c>
+      <c r="B5262" t="inlineStr">
+        <is>
+          <t>Havdhem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="inlineStr">
+        <is>
+          <t>SEHBY</t>
+        </is>
+      </c>
+      <c r="B5263" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="inlineStr">
+        <is>
+          <t>SEHEE</t>
+        </is>
+      </c>
+      <c r="B5264" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="inlineStr">
+        <is>
+          <t>SEHEG</t>
+        </is>
+      </c>
+      <c r="B5265" t="inlineStr">
+        <is>
+          <t>Heberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="inlineStr">
+        <is>
+          <t>SEHEM</t>
+        </is>
+      </c>
+      <c r="B5266" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="inlineStr">
+        <is>
+          <t>SEHER</t>
+        </is>
+      </c>
+      <c r="B5267" t="inlineStr">
+        <is>
+          <t>Herrang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="inlineStr">
+        <is>
+          <t>SEHGJ</t>
+        </is>
+      </c>
+      <c r="B5268" t="inlineStr">
+        <is>
+          <t>Hogsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="inlineStr">
+        <is>
+          <t>SEHGS</t>
+        </is>
+      </c>
+      <c r="B5269" t="inlineStr">
+        <is>
+          <t>Hogsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="inlineStr">
+        <is>
+          <t>SEHIT</t>
+        </is>
+      </c>
+      <c r="B5270" t="inlineStr">
+        <is>
+          <t>Hittarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="inlineStr">
+        <is>
+          <t>SEHJD</t>
+        </is>
+      </c>
+      <c r="B5271" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="inlineStr">
+        <is>
+          <t>SEHJS</t>
+        </is>
+      </c>
+      <c r="B5272" t="inlineStr">
+        <is>
+          <t>Holjes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="inlineStr">
+        <is>
+          <t>SEHLG</t>
+        </is>
+      </c>
+      <c r="B5273" t="inlineStr">
+        <is>
+          <t>Hallingsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="inlineStr">
+        <is>
+          <t>SEHLN</t>
+        </is>
+      </c>
+      <c r="B5274" t="inlineStr">
+        <is>
+          <t>Helgenas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="inlineStr">
+        <is>
+          <t>SEHLS</t>
+        </is>
+      </c>
+      <c r="B5275" t="inlineStr">
+        <is>
+          <t>Hallekis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="inlineStr">
+        <is>
+          <t>SEHMD</t>
+        </is>
+      </c>
+      <c r="B5276" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="inlineStr">
+        <is>
+          <t>SEHJB</t>
+        </is>
+      </c>
+      <c r="B5277" t="inlineStr">
+        <is>
+          <t>Hjalteby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="inlineStr">
+        <is>
+          <t>SEHMR</t>
+        </is>
+      </c>
+      <c r="B5278" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="inlineStr">
+        <is>
+          <t>SEHMV</t>
+        </is>
+      </c>
+      <c r="B5279" t="inlineStr">
+        <is>
+          <t>Hemavan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="inlineStr">
+        <is>
+          <t>SEHNB</t>
+        </is>
+      </c>
+      <c r="B5280" t="inlineStr">
+        <is>
+          <t>Horneborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="inlineStr">
+        <is>
+          <t>SEHNF</t>
+        </is>
+      </c>
+      <c r="B5281" t="inlineStr">
+        <is>
+          <t>Hornefors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="inlineStr">
+        <is>
+          <t>SEHOD</t>
+        </is>
+      </c>
+      <c r="B5282" t="inlineStr">
+        <is>
+          <t>Horred</t>
+        </is>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="inlineStr">
+        <is>
+          <t>SEHOK</t>
+        </is>
+      </c>
+      <c r="B5283" t="inlineStr">
+        <is>
+          <t>Hok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="inlineStr">
+        <is>
+          <t>SEHOL</t>
+        </is>
+      </c>
+      <c r="B5284" t="inlineStr">
+        <is>
+          <t>Holmsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="inlineStr">
+        <is>
+          <t>SEHON</t>
+        </is>
+      </c>
+      <c r="B5285" t="inlineStr">
+        <is>
+          <t>Honsater</t>
+        </is>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="inlineStr">
+        <is>
+          <t>SEHOO</t>
+        </is>
+      </c>
+      <c r="B5286" t="inlineStr">
+        <is>
+          <t>Hoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="inlineStr">
+        <is>
+          <t>SEHRA</t>
+        </is>
+      </c>
+      <c r="B5287" t="inlineStr">
+        <is>
+          <t>Horda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" t="inlineStr">
+        <is>
+          <t>SEHRD</t>
+        </is>
+      </c>
+      <c r="B5288" t="inlineStr">
+        <is>
+          <t>Harestad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="inlineStr">
+        <is>
+          <t>SEHRN</t>
+        </is>
+      </c>
+      <c r="B5289" t="inlineStr">
+        <is>
+          <t>Horndal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="inlineStr">
+        <is>
+          <t>SEHRS</t>
+        </is>
+      </c>
+      <c r="B5290" t="inlineStr">
+        <is>
+          <t>Halleforsnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="inlineStr">
+        <is>
+          <t>SEHRV</t>
+        </is>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>Harslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="inlineStr">
+        <is>
+          <t>SEHSD</t>
+        </is>
+      </c>
+      <c r="B5292" t="inlineStr">
+        <is>
+          <t>Hillared</t>
+        </is>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="inlineStr">
+        <is>
+          <t>SEHST</t>
+        </is>
+      </c>
+      <c r="B5293" t="inlineStr">
+        <is>
+          <t>Heestrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="inlineStr">
+        <is>
+          <t>SEHTM</t>
+        </is>
+      </c>
+      <c r="B5294" t="inlineStr">
+        <is>
+          <t>Hjartum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="inlineStr">
+        <is>
+          <t>SEHUN</t>
+        </is>
+      </c>
+      <c r="B5295" t="inlineStr">
+        <is>
+          <t>Hunnebostrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="inlineStr">
+        <is>
+          <t>SEHUR</t>
+        </is>
+      </c>
+      <c r="B5296" t="inlineStr">
+        <is>
+          <t>Hurva</t>
+        </is>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="inlineStr">
+        <is>
+          <t>SEHUY</t>
+        </is>
+      </c>
+      <c r="B5297" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="inlineStr">
+        <is>
+          <t>SEHVR</t>
+        </is>
+      </c>
+      <c r="B5298" t="inlineStr">
+        <is>
+          <t>Haverud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="inlineStr">
+        <is>
+          <t>SEHXN</t>
+        </is>
+      </c>
+      <c r="B5299" t="inlineStr">
+        <is>
+          <t>Henan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="inlineStr">
+        <is>
+          <t>SEHYD</t>
+        </is>
+      </c>
+      <c r="B5300" t="inlineStr">
+        <is>
+          <t>Hallaryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="inlineStr">
+        <is>
+          <t>SEHYP</t>
+        </is>
+      </c>
+      <c r="B5301" t="inlineStr">
+        <is>
+          <t>Hyppeln</t>
+        </is>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="inlineStr">
+        <is>
+          <t>SEHYS</t>
+        </is>
+      </c>
+      <c r="B5302" t="inlineStr">
+        <is>
+          <t>Hyssna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="inlineStr">
+        <is>
+          <t>SEHZS</t>
+        </is>
+      </c>
+      <c r="B5303" t="inlineStr">
+        <is>
+          <t>Hovslatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="inlineStr">
+        <is>
+          <t>SEIDB</t>
+        </is>
+      </c>
+      <c r="B5304" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="inlineStr">
+        <is>
+          <t>SEIGP</t>
+        </is>
+      </c>
+      <c r="B5305" t="inlineStr">
+        <is>
+          <t>Igelstorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="inlineStr">
+        <is>
+          <t>SEJAO</t>
+        </is>
+      </c>
+      <c r="B5306" t="inlineStr">
+        <is>
+          <t>Jarbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="inlineStr">
+        <is>
+          <t>SEJAT</t>
+        </is>
+      </c>
+      <c r="B5307" t="inlineStr">
+        <is>
+          <t>Jatterson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="inlineStr">
+        <is>
+          <t>SEJNA</t>
+        </is>
+      </c>
+      <c r="B5308" t="inlineStr">
+        <is>
+          <t>Jorlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="inlineStr">
+        <is>
+          <t>SEJOH</t>
+        </is>
+      </c>
+      <c r="B5309" t="inlineStr">
+        <is>
+          <t>Johannedal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="inlineStr">
+        <is>
+          <t>SEJOK</t>
+        </is>
+      </c>
+      <c r="B5310" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="inlineStr">
+        <is>
+          <t>SEJOP</t>
+        </is>
+      </c>
+      <c r="B5311" t="inlineStr">
+        <is>
+          <t>Jonstorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="inlineStr">
+        <is>
+          <t>SEJPS</t>
+        </is>
+      </c>
+      <c r="B5312" t="inlineStr">
+        <is>
+          <t>Jarpas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="inlineStr">
+        <is>
+          <t>SEJUN</t>
+        </is>
+      </c>
+      <c r="B5313" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="inlineStr">
+        <is>
+          <t>SEKAE</t>
+        </is>
+      </c>
+      <c r="B5314" t="inlineStr">
+        <is>
+          <t>Kattilstorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="inlineStr">
+        <is>
+          <t>SEKAK</t>
+        </is>
+      </c>
+      <c r="B5315" t="inlineStr">
+        <is>
+          <t>Karlsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="inlineStr">
+        <is>
+          <t>SEKAO</t>
+        </is>
+      </c>
+      <c r="B5316" t="inlineStr">
+        <is>
+          <t>Karo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="inlineStr">
+        <is>
+          <t>SEKAS</t>
+        </is>
+      </c>
+      <c r="B5317" t="inlineStr">
+        <is>
+          <t>Karskar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="inlineStr">
+        <is>
+          <t>SEKAT</t>
+        </is>
+      </c>
+      <c r="B5318" t="inlineStr">
+        <is>
+          <t>Katthammarsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="inlineStr">
+        <is>
+          <t>SEKAX</t>
+        </is>
+      </c>
+      <c r="B5319" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" t="inlineStr">
+        <is>
+          <t>SEKDG</t>
+        </is>
+      </c>
+      <c r="B5320" t="inlineStr">
+        <is>
+          <t>Kvidinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="inlineStr">
+        <is>
+          <t>SEKGG</t>
+        </is>
+      </c>
+      <c r="B5321" t="inlineStr">
+        <is>
+          <t>Kagghamra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" t="inlineStr">
+        <is>
+          <t>SEKGM</t>
+        </is>
+      </c>
+      <c r="B5322" t="inlineStr">
+        <is>
+          <t>Klagshamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="inlineStr">
+        <is>
+          <t>SEKHL</t>
+        </is>
+      </c>
+      <c r="B5323" t="inlineStr">
+        <is>
+          <t>Kallhall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" t="inlineStr">
+        <is>
+          <t>SEKIM</t>
+        </is>
+      </c>
+      <c r="B5324" t="inlineStr">
+        <is>
+          <t>Kilsmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="inlineStr">
+        <is>
+          <t>SEKIN</t>
+        </is>
+      </c>
+      <c r="B5325" t="inlineStr">
+        <is>
+          <t>Kinnarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" t="inlineStr">
+        <is>
+          <t>SEKIR</t>
+        </is>
+      </c>
+      <c r="B5326" t="inlineStr">
+        <is>
+          <t>Kinnared</t>
+        </is>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="inlineStr">
+        <is>
+          <t>SEKK9</t>
+        </is>
+      </c>
+      <c r="B5327" t="inlineStr">
+        <is>
+          <t>Klockrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" t="inlineStr">
+        <is>
+          <t>SEKKS</t>
+        </is>
+      </c>
+      <c r="B5328" t="inlineStr">
+        <is>
+          <t>Kyrkesund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="inlineStr">
+        <is>
+          <t>SEKLA</t>
+        </is>
+      </c>
+      <c r="B5329" t="inlineStr">
+        <is>
+          <t>Klavrestrom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" t="inlineStr">
+        <is>
+          <t>SEKLD</t>
+        </is>
+      </c>
+      <c r="B5330" t="inlineStr">
+        <is>
+          <t>Kladesholmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="inlineStr">
+        <is>
+          <t>SEKLE</t>
+        </is>
+      </c>
+      <c r="B5331" t="inlineStr">
+        <is>
+          <t>Kalarne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" t="inlineStr">
+        <is>
+          <t>SEKLI</t>
+        </is>
+      </c>
+      <c r="B5332" t="inlineStr">
+        <is>
+          <t>Klintehamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="inlineStr">
+        <is>
+          <t>SEKLO</t>
+        </is>
+      </c>
+      <c r="B5333" t="inlineStr">
+        <is>
+          <t>Kallandso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" t="inlineStr">
+        <is>
+          <t>SEKLV</t>
+        </is>
+      </c>
+      <c r="B5334" t="inlineStr">
+        <is>
+          <t>Kullavik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="inlineStr">
+        <is>
+          <t>SEKLX</t>
+        </is>
+      </c>
+      <c r="B5335" t="inlineStr">
+        <is>
+          <t>Kalv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" t="inlineStr">
+        <is>
+          <t>SEKNL</t>
+        </is>
+      </c>
+      <c r="B5336" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="inlineStr">
+        <is>
+          <t>SEKOA</t>
+        </is>
+      </c>
+      <c r="B5337" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" t="inlineStr">
+        <is>
+          <t>SEKOP</t>
+        </is>
+      </c>
+      <c r="B5338" t="inlineStr">
+        <is>
+          <t>Kopingebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="inlineStr">
+        <is>
+          <t>SEKOR</t>
+        </is>
+      </c>
+      <c r="B5339" t="inlineStr">
+        <is>
+          <t>Korsberga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5340">
+      <c r="A5340" t="inlineStr">
+        <is>
+          <t>SEKOS</t>
+        </is>
+      </c>
+      <c r="B5340" t="inlineStr">
+        <is>
+          <t>Korsnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="inlineStr">
+        <is>
+          <t>SEKPA</t>
+        </is>
+      </c>
+      <c r="B5341" t="inlineStr">
+        <is>
+          <t>Karpalund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" t="inlineStr">
+        <is>
+          <t>SEKRH</t>
+        </is>
+      </c>
+      <c r="B5342" t="inlineStr">
+        <is>
+          <t>Karehamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="inlineStr">
+        <is>
+          <t>SEKRI</t>
+        </is>
+      </c>
+      <c r="B5343" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" t="inlineStr">
+        <is>
+          <t>SEKRK</t>
+        </is>
+      </c>
+      <c r="B5344" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="inlineStr">
+        <is>
+          <t>SEKRO</t>
+        </is>
+      </c>
+      <c r="B5345" t="inlineStr">
+        <is>
+          <t>Krokvag</t>
+        </is>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" t="inlineStr">
+        <is>
+          <t>SEKRR</t>
+        </is>
+      </c>
+      <c r="B5346" t="inlineStr">
+        <is>
+          <t>Kallekarr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="inlineStr">
+        <is>
+          <t>SEKSL</t>
+        </is>
+      </c>
+      <c r="B5347" t="inlineStr">
+        <is>
+          <t>Koskullskulle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" t="inlineStr">
+        <is>
+          <t>SEKSP</t>
+        </is>
+      </c>
+      <c r="B5348" t="inlineStr">
+        <is>
+          <t>Klagstorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="inlineStr">
+        <is>
+          <t>SEKUB</t>
+        </is>
+      </c>
+      <c r="B5349" t="inlineStr">
+        <is>
+          <t>Kubikenborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" t="inlineStr">
+        <is>
+          <t>SEKUK</t>
+        </is>
+      </c>
+      <c r="B5350" t="inlineStr">
+        <is>
+          <t>Skebobruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="inlineStr">
+        <is>
+          <t>SEKVA</t>
+        </is>
+      </c>
+      <c r="B5351" t="inlineStr">
+        <is>
+          <t>Kvarnholmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" t="inlineStr">
+        <is>
+          <t>SEKVK</t>
+        </is>
+      </c>
+      <c r="B5352" t="inlineStr">
+        <is>
+          <t>Kalvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5353">
+      <c r="A5353" t="inlineStr">
+        <is>
+          <t>SEKVN</t>
+        </is>
+      </c>
+      <c r="B5353" t="inlineStr">
+        <is>
+          <t>Kvarnsveden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" t="inlineStr">
+        <is>
+          <t>SEKVY</t>
+        </is>
+      </c>
+      <c r="B5354" t="inlineStr">
+        <is>
+          <t>Kvissleby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="inlineStr">
+        <is>
+          <t>SEKXH</t>
+        </is>
+      </c>
+      <c r="B5355" t="inlineStr">
+        <is>
+          <t>Kaxholmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="inlineStr">
+        <is>
+          <t>SEKYK</t>
+        </is>
+      </c>
+      <c r="B5356" t="inlineStr">
+        <is>
+          <t>Kyrkas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="inlineStr">
+        <is>
+          <t>SELA9</t>
+        </is>
+      </c>
+      <c r="B5357" t="inlineStr">
+        <is>
+          <t>Langas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="inlineStr">
+        <is>
+          <t>SELAL</t>
+        </is>
+      </c>
+      <c r="B5358" t="inlineStr">
+        <is>
+          <t>Laisvall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="inlineStr">
+        <is>
+          <t>SEKVC</t>
+        </is>
+      </c>
+      <c r="B5359" t="inlineStr">
+        <is>
+          <t>Kvicksund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="inlineStr">
+        <is>
+          <t>SEKVH</t>
+        </is>
+      </c>
+      <c r="B5360" t="inlineStr">
+        <is>
+          <t>Kopparverkshamnen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="inlineStr">
+        <is>
+          <t>SELAO</t>
+        </is>
+      </c>
+      <c r="B5361" t="inlineStr">
+        <is>
+          <t>Landsbro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="inlineStr">
+        <is>
+          <t>SELAR</t>
+        </is>
+      </c>
+      <c r="B5362" t="inlineStr">
+        <is>
+          <t>Larv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="inlineStr">
+        <is>
+          <t>SELAY</t>
+        </is>
+      </c>
+      <c r="B5363" t="inlineStr">
+        <is>
+          <t>Langaryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="inlineStr">
+        <is>
+          <t>SELDN</t>
+        </is>
+      </c>
+      <c r="B5364" t="inlineStr">
+        <is>
+          <t>Lofsdalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="inlineStr">
+        <is>
+          <t>SELDO</t>
+        </is>
+      </c>
+      <c r="B5365" t="inlineStr">
+        <is>
+          <t>Lodose</t>
+        </is>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" t="inlineStr">
+        <is>
+          <t>SELDV</t>
+        </is>
+      </c>
+      <c r="B5366" t="inlineStr">
+        <is>
+          <t>Lenhovda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="inlineStr">
+        <is>
+          <t>SELER</t>
+        </is>
+      </c>
+      <c r="B5367" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" t="inlineStr">
+        <is>
+          <t>SELES</t>
+        </is>
+      </c>
+      <c r="B5368" t="inlineStr">
+        <is>
+          <t>Lesjofors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="inlineStr">
+        <is>
+          <t>SELGL</t>
+        </is>
+      </c>
+      <c r="B5369" t="inlineStr">
+        <is>
+          <t>Langsele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" t="inlineStr">
+        <is>
+          <t>SELGO</t>
+        </is>
+      </c>
+      <c r="B5370" t="inlineStr">
+        <is>
+          <t>Lingbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="inlineStr">
+        <is>
+          <t>SELGR</t>
+        </is>
+      </c>
+      <c r="B5371" t="inlineStr">
+        <is>
+          <t>Algaras, Toreboda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" t="inlineStr">
+        <is>
+          <t>SELIA</t>
+        </is>
+      </c>
+      <c r="B5372" t="inlineStr">
+        <is>
+          <t>Lindas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="inlineStr">
+        <is>
+          <t>SELID</t>
+        </is>
+      </c>
+      <c r="B5373" t="inlineStr">
+        <is>
+          <t>Lindarva</t>
+        </is>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" t="inlineStr">
+        <is>
+          <t>SELIL</t>
+        </is>
+      </c>
+      <c r="B5374" t="inlineStr">
+        <is>
+          <t>Liljendal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5375">
+      <c r="A5375" t="inlineStr">
+        <is>
+          <t>SELIT</t>
+        </is>
+      </c>
+      <c r="B5375" t="inlineStr">
+        <is>
+          <t>Lidhult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" t="inlineStr">
+        <is>
+          <t>SELJB</t>
+        </is>
+      </c>
+      <c r="B5376" t="inlineStr">
+        <is>
+          <t>Ljungsbro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5377">
+      <c r="A5377" t="inlineStr">
+        <is>
+          <t>SELJO</t>
+        </is>
+      </c>
+      <c r="B5377" t="inlineStr">
+        <is>
+          <t>Ljustero</t>
+        </is>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" t="inlineStr">
+        <is>
+          <t>SELJP</t>
+        </is>
+      </c>
+      <c r="B5378" t="inlineStr">
+        <is>
+          <t>Ljungsarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="inlineStr">
+        <is>
+          <t>SELJU</t>
+        </is>
+      </c>
+      <c r="B5379" t="inlineStr">
+        <is>
+          <t>Ljusne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" t="inlineStr">
+        <is>
+          <t>SELNA</t>
+        </is>
+      </c>
+      <c r="B5380" t="inlineStr">
+        <is>
+          <t>Lanna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="inlineStr">
+        <is>
+          <t>SELOB</t>
+        </is>
+      </c>
+      <c r="B5381" t="inlineStr">
+        <is>
+          <t>Loberod</t>
+        </is>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" t="inlineStr">
+        <is>
+          <t>SELOF</t>
+        </is>
+      </c>
+      <c r="B5382" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="inlineStr">
+        <is>
+          <t>SELON</t>
+        </is>
+      </c>
+      <c r="B5383" t="inlineStr">
+        <is>
+          <t>Lonsboda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" t="inlineStr">
+        <is>
+          <t>SELOT</t>
+        </is>
+      </c>
+      <c r="B5384" t="inlineStr">
+        <is>
+          <t>Loten</t>
+        </is>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="inlineStr">
+        <is>
+          <t>SELOU</t>
+        </is>
+      </c>
+      <c r="B5385" t="inlineStr">
+        <is>
+          <t>Loudden/Stockholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" t="inlineStr">
+        <is>
+          <t>SELJJ</t>
+        </is>
+      </c>
+      <c r="B5386" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="inlineStr">
+        <is>
+          <t>SELTP</t>
+        </is>
+      </c>
+      <c r="B5387" t="inlineStr">
+        <is>
+          <t>Liatorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" t="inlineStr">
+        <is>
+          <t>SELUG</t>
+        </is>
+      </c>
+      <c r="B5388" t="inlineStr">
+        <is>
+          <t>Lugnvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="inlineStr">
+        <is>
+          <t>SELUN</t>
+        </is>
+      </c>
+      <c r="B5389" t="inlineStr">
+        <is>
+          <t>Lovholmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" t="inlineStr">
+        <is>
+          <t>SELVR</t>
+        </is>
+      </c>
+      <c r="B5390" t="inlineStr">
+        <is>
+          <t>Lovanger</t>
+        </is>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="inlineStr">
+        <is>
+          <t>SELVS</t>
+        </is>
+      </c>
+      <c r="B5391" t="inlineStr">
+        <is>
+          <t>Lovestad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5392">
+      <c r="A5392" t="inlineStr">
+        <is>
+          <t>SEMAN</t>
+        </is>
+      </c>
+      <c r="B5392" t="inlineStr">
+        <is>
+          <t>Marsviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="inlineStr">
+        <is>
+          <t>SEMAP</t>
+        </is>
+      </c>
+      <c r="B5393" t="inlineStr">
+        <is>
+          <t>Mantorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" t="inlineStr">
+        <is>
+          <t>SEMAR</t>
+        </is>
+      </c>
+      <c r="B5394" t="inlineStr">
+        <is>
+          <t>Marieberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="inlineStr">
+        <is>
+          <t>SEMAT</t>
+        </is>
+      </c>
+      <c r="B5395" t="inlineStr">
+        <is>
+          <t>Matfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" t="inlineStr">
+        <is>
+          <t>SEMAV</t>
+        </is>
+      </c>
+      <c r="B5396" t="inlineStr">
+        <is>
+          <t>Marviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="inlineStr">
+        <is>
+          <t>SEMBS</t>
+        </is>
+      </c>
+      <c r="B5397" t="inlineStr">
+        <is>
+          <t>Mellbystrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" t="inlineStr">
+        <is>
+          <t>SEMEM</t>
+        </is>
+      </c>
+      <c r="B5398" t="inlineStr">
+        <is>
+          <t>Mem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="inlineStr">
+        <is>
+          <t>SEMGG</t>
+        </is>
+      </c>
+      <c r="B5399" t="inlineStr">
+        <is>
+          <t>Morgongava</t>
+        </is>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" t="inlineStr">
+        <is>
+          <t>SEMHA</t>
+        </is>
+      </c>
+      <c r="B5400" t="inlineStr">
+        <is>
+          <t>Moheda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="inlineStr">
+        <is>
+          <t>SEMHM</t>
+        </is>
+      </c>
+      <c r="B5401" t="inlineStr">
+        <is>
+          <t>Moholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" t="inlineStr">
+        <is>
+          <t>SEMKP</t>
+        </is>
+      </c>
+      <c r="B5402" t="inlineStr">
+        <is>
+          <t>Malmkoping</t>
+        </is>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="inlineStr">
+        <is>
+          <t>SEMLB</t>
+        </is>
+      </c>
+      <c r="B5403" t="inlineStr">
+        <is>
+          <t>Molnbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" t="inlineStr">
+        <is>
+          <t>SEMLE</t>
+        </is>
+      </c>
+      <c r="B5404" t="inlineStr">
+        <is>
+          <t>Molle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="inlineStr">
+        <is>
+          <t>SEMLO</t>
+        </is>
+      </c>
+      <c r="B5405" t="inlineStr">
+        <is>
+          <t>Mollosund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" t="inlineStr">
+        <is>
+          <t>SEMLR</t>
+        </is>
+      </c>
+      <c r="B5406" t="inlineStr">
+        <is>
+          <t>Maleras</t>
+        </is>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="inlineStr">
+        <is>
+          <t>SEMLS</t>
+        </is>
+      </c>
+      <c r="B5407" t="inlineStr">
+        <is>
+          <t>Mellansel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" t="inlineStr">
+        <is>
+          <t>SEMLU</t>
+        </is>
+      </c>
+      <c r="B5408" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="inlineStr">
+        <is>
+          <t>SEMNO</t>
+        </is>
+      </c>
+      <c r="B5409" t="inlineStr">
+        <is>
+          <t>Munso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" t="inlineStr">
+        <is>
+          <t>SEMOF</t>
+        </is>
+      </c>
+      <c r="B5410" t="inlineStr">
+        <is>
+          <t>Mortfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5411">
+      <c r="A5411" t="inlineStr">
+        <is>
+          <t>SEMOI</t>
+        </is>
+      </c>
+      <c r="B5411" t="inlineStr">
+        <is>
+          <t>Mellosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5412">
+      <c r="A5412" t="inlineStr">
+        <is>
+          <t>SEMOJ</t>
+        </is>
+      </c>
+      <c r="B5412" t="inlineStr">
+        <is>
+          <t>Moja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="inlineStr">
+        <is>
+          <t>SEMOO</t>
+        </is>
+      </c>
+      <c r="B5413" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" t="inlineStr">
+        <is>
+          <t>SEMOP</t>
+        </is>
+      </c>
+      <c r="B5414" t="inlineStr">
+        <is>
+          <t>Morarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="inlineStr">
+        <is>
+          <t>SEMOR</t>
+        </is>
+      </c>
+      <c r="B5415" t="inlineStr">
+        <is>
+          <t>Morbylanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5416">
+      <c r="A5416" t="inlineStr">
+        <is>
+          <t>SEMRH</t>
+        </is>
+      </c>
+      <c r="B5416" t="inlineStr">
+        <is>
+          <t>Marieholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5417">
+      <c r="A5417" t="inlineStr">
+        <is>
+          <t>SEMRL</t>
+        </is>
+      </c>
+      <c r="B5417" t="inlineStr">
+        <is>
+          <t>Mariannelund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" t="inlineStr">
+        <is>
+          <t>SEMSK</t>
+        </is>
+      </c>
+      <c r="B5418" t="inlineStr">
+        <is>
+          <t>Musko</t>
+        </is>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="inlineStr">
+        <is>
+          <t>SEMTM</t>
+        </is>
+      </c>
+      <c r="B5419" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="inlineStr">
+        <is>
+          <t>SEMTP</t>
+        </is>
+      </c>
+      <c r="B5420" t="inlineStr">
+        <is>
+          <t>Molltorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="inlineStr">
+        <is>
+          <t>SEMVK</t>
+        </is>
+      </c>
+      <c r="B5421" t="inlineStr">
+        <is>
+          <t>Maryvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="inlineStr">
+        <is>
+          <t>SEN8P</t>
+        </is>
+      </c>
+      <c r="B5422" t="inlineStr">
+        <is>
+          <t>Alnarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="inlineStr">
+        <is>
+          <t>SENAS</t>
+        </is>
+      </c>
+      <c r="B5423" t="inlineStr">
+        <is>
+          <t>Nas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5424">
+      <c r="A5424" t="inlineStr">
+        <is>
+          <t>SENAV</t>
+        </is>
+      </c>
+      <c r="B5424" t="inlineStr">
+        <is>
+          <t>Navekvarn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="inlineStr">
+        <is>
+          <t>SENCS</t>
+        </is>
+      </c>
+      <c r="B5425" t="inlineStr">
+        <is>
+          <t>Nacka Strand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5426">
+      <c r="A5426" t="inlineStr">
+        <is>
+          <t>SENFD</t>
+        </is>
+      </c>
+      <c r="B5426" t="inlineStr">
+        <is>
+          <t>Norrfjarden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="inlineStr">
+        <is>
+          <t>SENHN</t>
+        </is>
+      </c>
+      <c r="B5427" t="inlineStr">
+        <is>
+          <t>Nyhamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5428">
+      <c r="A5428" t="inlineStr">
+        <is>
+          <t>SENHR</t>
+        </is>
+      </c>
+      <c r="B5428" t="inlineStr">
+        <is>
+          <t>Norrahammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="inlineStr">
+        <is>
+          <t>SENJA</t>
+        </is>
+      </c>
+      <c r="B5429" t="inlineStr">
+        <is>
+          <t>Norrbottens Jarnverk-SSAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5430">
+      <c r="A5430" t="inlineStr">
+        <is>
+          <t>SENML</t>
+        </is>
+      </c>
+      <c r="B5430" t="inlineStr">
+        <is>
+          <t>Nymala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="inlineStr">
+        <is>
+          <t>SENOR</t>
+        </is>
+      </c>
+      <c r="B5431" t="inlineStr">
+        <is>
+          <t>Norrbyskar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5432">
+      <c r="A5432" t="inlineStr">
+        <is>
+          <t>SENOS</t>
+        </is>
+      </c>
+      <c r="B5432" t="inlineStr">
+        <is>
+          <t>Onsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="inlineStr">
+        <is>
+          <t>SENRH</t>
+        </is>
+      </c>
+      <c r="B5433" t="inlineStr">
+        <is>
+          <t>Norrhult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5434">
+      <c r="A5434" t="inlineStr">
+        <is>
+          <t>SENSG</t>
+        </is>
+      </c>
+      <c r="B5434" t="inlineStr">
+        <is>
+          <t>Norsborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="inlineStr">
+        <is>
+          <t>SENSM</t>
+        </is>
+      </c>
+      <c r="B5435" t="inlineStr">
+        <is>
+          <t>Nasum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5436">
+      <c r="A5436" t="inlineStr">
+        <is>
+          <t>SENST</t>
+        </is>
+      </c>
+      <c r="B5436" t="inlineStr">
+        <is>
+          <t>Norastrom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="inlineStr">
+        <is>
+          <t>SENTY</t>
+        </is>
+      </c>
+      <c r="B5437" t="inlineStr">
+        <is>
+          <t>Nattraby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5438">
+      <c r="A5438" t="inlineStr">
+        <is>
+          <t>SENVE</t>
+        </is>
+      </c>
+      <c r="B5438" t="inlineStr">
+        <is>
+          <t>Navlinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5439">
+      <c r="A5439" t="inlineStr">
+        <is>
+          <t>SENYL</t>
+        </is>
+      </c>
+      <c r="B5439" t="inlineStr">
+        <is>
+          <t>Nyland</t>
+        </is>
+      </c>
+    </row>
+    <row r="5440">
+      <c r="A5440" t="inlineStr">
+        <is>
+          <t>SENYP</t>
+        </is>
+      </c>
+      <c r="B5440" t="inlineStr">
+        <is>
+          <t>Nyvarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="inlineStr">
+        <is>
+          <t>SENYV</t>
+        </is>
+      </c>
+      <c r="B5441" t="inlineStr">
+        <is>
+          <t>Nyvang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5442">
+      <c r="A5442" t="inlineStr">
+        <is>
+          <t>SEOAB</t>
+        </is>
+      </c>
+      <c r="B5442" t="inlineStr">
+        <is>
+          <t>Osterhaninge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="inlineStr">
+        <is>
+          <t>SEOAX</t>
+        </is>
+      </c>
+      <c r="B5443" t="inlineStr">
+        <is>
+          <t>Oaxen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5444">
+      <c r="A5444" t="inlineStr">
+        <is>
+          <t>SEOBB</t>
+        </is>
+      </c>
+      <c r="B5444" t="inlineStr">
+        <is>
+          <t>Obbola</t>
+        </is>
+      </c>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="inlineStr">
+        <is>
+          <t>SEODA</t>
+        </is>
+      </c>
+      <c r="B5445" t="inlineStr">
+        <is>
+          <t>Odakra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5446">
+      <c r="A5446" t="inlineStr">
+        <is>
+          <t>SEODB</t>
+        </is>
+      </c>
+      <c r="B5446" t="inlineStr">
+        <is>
+          <t>Odensbacken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5447">
+      <c r="A5447" t="inlineStr">
+        <is>
+          <t>SEODO</t>
+        </is>
+      </c>
+      <c r="B5447" t="inlineStr">
+        <is>
+          <t>Orsundsbro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5448">
+      <c r="A5448" t="inlineStr">
+        <is>
+          <t>SEOEN</t>
+        </is>
+      </c>
+      <c r="B5448" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+    </row>
+    <row r="5449">
+      <c r="A5449" t="inlineStr">
+        <is>
+          <t>SEOEV</t>
+        </is>
+      </c>
+      <c r="B5449" t="inlineStr">
+        <is>
+          <t>Overkalix</t>
+        </is>
+      </c>
+    </row>
+    <row r="5450">
+      <c r="A5450" t="inlineStr">
+        <is>
+          <t>SEOGR</t>
+        </is>
+      </c>
+      <c r="B5450" t="inlineStr">
+        <is>
+          <t>Oregrund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5451">
+      <c r="A5451" t="inlineStr">
+        <is>
+          <t>SEOJS</t>
+        </is>
+      </c>
+      <c r="B5451" t="inlineStr">
+        <is>
+          <t>Ojersjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5452">
+      <c r="A5452" t="inlineStr">
+        <is>
+          <t>SEOLM</t>
+        </is>
+      </c>
+      <c r="B5452" t="inlineStr">
+        <is>
+          <t>Olsremma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5453">
+      <c r="A5453" t="inlineStr">
+        <is>
+          <t>SEORJ</t>
+        </is>
+      </c>
+      <c r="B5453" t="inlineStr">
+        <is>
+          <t>Orsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5454">
+      <c r="A5454" t="inlineStr">
+        <is>
+          <t>SEORS</t>
+        </is>
+      </c>
+      <c r="B5454" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5455">
+      <c r="A5455" t="inlineStr">
+        <is>
+          <t>SEORT</t>
+        </is>
+      </c>
+      <c r="B5455" t="inlineStr">
+        <is>
+          <t>Ortviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5456">
+      <c r="A5456" t="inlineStr">
+        <is>
+          <t>SEORV</t>
+        </is>
+      </c>
+      <c r="B5456" t="inlineStr">
+        <is>
+          <t>Orviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5457">
+      <c r="A5457" t="inlineStr">
+        <is>
+          <t>SEOLS</t>
+        </is>
+      </c>
+      <c r="B5457" t="inlineStr">
+        <is>
+          <t>Olsfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5458">
+      <c r="A5458" t="inlineStr">
+        <is>
+          <t>SEOST</t>
+        </is>
+      </c>
+      <c r="B5458" t="inlineStr">
+        <is>
+          <t>Ostrand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5459">
+      <c r="A5459" t="inlineStr">
+        <is>
+          <t>SEOSV</t>
+        </is>
+      </c>
+      <c r="B5459" t="inlineStr">
+        <is>
+          <t>Ostra Sonnarslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5460">
+      <c r="A5460" t="inlineStr">
+        <is>
+          <t>SEOTD</t>
+        </is>
+      </c>
+      <c r="B5460" t="inlineStr">
+        <is>
+          <t>Onnestad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5461">
+      <c r="A5461" t="inlineStr">
+        <is>
+          <t>SEOTT</t>
+        </is>
+      </c>
+      <c r="B5461" t="inlineStr">
+        <is>
+          <t>Otterbacken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5462">
+      <c r="A5462" t="inlineStr">
+        <is>
+          <t>SEOTV</t>
+        </is>
+      </c>
+      <c r="B5462" t="inlineStr">
+        <is>
+          <t>Ostervala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="inlineStr">
+        <is>
+          <t>SEOVE</t>
+        </is>
+      </c>
+      <c r="B5463" t="inlineStr">
+        <is>
+          <t>Overtornea</t>
+        </is>
+      </c>
+    </row>
+    <row r="5464">
+      <c r="A5464" t="inlineStr">
+        <is>
+          <t>SEOVN</t>
+        </is>
+      </c>
+      <c r="B5464" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5465">
+      <c r="A5465" t="inlineStr">
+        <is>
+          <t>SEOYS</t>
+        </is>
+      </c>
+      <c r="B5465" t="inlineStr">
+        <is>
+          <t>Orbyhus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5466">
+      <c r="A5466" t="inlineStr">
+        <is>
+          <t>SEPAS</t>
+        </is>
+      </c>
+      <c r="B5466" t="inlineStr">
+        <is>
+          <t>Paskallavik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="inlineStr">
+        <is>
+          <t>SEPHM</t>
+        </is>
+      </c>
+      <c r="B5467" t="inlineStr">
+        <is>
+          <t>Pataholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5468">
+      <c r="A5468" t="inlineStr">
+        <is>
+          <t>SEPIX</t>
+        </is>
+      </c>
+      <c r="B5468" t="inlineStr">
+        <is>
+          <t>Pixbo/Harryda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="inlineStr">
+        <is>
+          <t>SEPRP</t>
+        </is>
+      </c>
+      <c r="B5469" t="inlineStr">
+        <is>
+          <t>Paarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5470">
+      <c r="A5470" t="inlineStr">
+        <is>
+          <t>SERAG</t>
+        </is>
+      </c>
+      <c r="B5470" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="inlineStr">
+        <is>
+          <t>SERAM</t>
+        </is>
+      </c>
+      <c r="B5471" t="inlineStr">
+        <is>
+          <t>Ramvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5472">
+      <c r="A5472" t="inlineStr">
+        <is>
+          <t>SERAQ</t>
+        </is>
+      </c>
+      <c r="B5472" t="inlineStr">
+        <is>
+          <t>Ranas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="inlineStr">
+        <is>
+          <t>SERBY</t>
+        </is>
+      </c>
+      <c r="B5473" t="inlineStr">
+        <is>
+          <t>Ronnebyhamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5474">
+      <c r="A5474" t="inlineStr">
+        <is>
+          <t>SERDB</t>
+        </is>
+      </c>
+      <c r="B5474" t="inlineStr">
+        <is>
+          <t>Rydobruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="inlineStr">
+        <is>
+          <t>SERDD</t>
+        </is>
+      </c>
+      <c r="B5475" t="inlineStr">
+        <is>
+          <t>Riddarhyttan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5476">
+      <c r="A5476" t="inlineStr">
+        <is>
+          <t>SEREP</t>
+        </is>
+      </c>
+      <c r="B5476" t="inlineStr">
+        <is>
+          <t>Reftele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="inlineStr">
+        <is>
+          <t>SERJM</t>
+        </is>
+      </c>
+      <c r="B5477" t="inlineStr">
+        <is>
+          <t>Rejmyre</t>
+        </is>
+      </c>
+    </row>
+    <row r="5478">
+      <c r="A5478" t="inlineStr">
+        <is>
+          <t>SERMF</t>
+        </is>
+      </c>
+      <c r="B5478" t="inlineStr">
+        <is>
+          <t>Rimforsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>SERNG</t>
+        </is>
+      </c>
+      <c r="B5479" t="inlineStr">
+        <is>
+          <t>Ronnang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="inlineStr">
+        <is>
+          <t>SERNH</t>
+        </is>
+      </c>
+      <c r="B5480" t="inlineStr">
+        <is>
+          <t>Ronehamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>SERNX</t>
+        </is>
+      </c>
+      <c r="B5481" t="inlineStr">
+        <is>
+          <t>Rosson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5482">
+      <c r="A5482" t="inlineStr">
+        <is>
+          <t>SEROE</t>
+        </is>
+      </c>
+      <c r="B5482" t="inlineStr">
+        <is>
+          <t>Rone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>SEROF</t>
+        </is>
+      </c>
+      <c r="B5483" t="inlineStr">
+        <is>
+          <t>Rosenfors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5484">
+      <c r="A5484" t="inlineStr">
+        <is>
+          <t>SEROR</t>
+        </is>
+      </c>
+      <c r="B5484" t="inlineStr">
+        <is>
+          <t>Ronnskar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>SEROT</t>
+        </is>
+      </c>
+      <c r="B5485" t="inlineStr">
+        <is>
+          <t>Rotebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5486">
+      <c r="A5486" t="inlineStr">
+        <is>
+          <t>SEROV</t>
+        </is>
+      </c>
+      <c r="B5486" t="inlineStr">
+        <is>
+          <t>Ronnskarsverken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>SERQT</t>
+        </is>
+      </c>
+      <c r="B5487" t="inlineStr">
+        <is>
+          <t>Stora Levene</t>
+        </is>
+      </c>
+    </row>
+    <row r="5488">
+      <c r="A5488" t="inlineStr">
+        <is>
+          <t>SERS8</t>
+        </is>
+      </c>
+      <c r="B5488" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>SERST</t>
+        </is>
+      </c>
+      <c r="B5489" t="inlineStr">
+        <is>
+          <t>Ransta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5490">
+      <c r="A5490" t="inlineStr">
+        <is>
+          <t>SERUK</t>
+        </is>
+      </c>
+      <c r="B5490" t="inlineStr">
+        <is>
+          <t>Torpsbruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>SERUN</t>
+        </is>
+      </c>
+      <c r="B5491" t="inlineStr">
+        <is>
+          <t>Runsten</t>
+        </is>
+      </c>
+    </row>
+    <row r="5492">
+      <c r="A5492" t="inlineStr">
+        <is>
+          <t>SERUR</t>
+        </is>
+      </c>
+      <c r="B5492" t="inlineStr">
+        <is>
+          <t>Runmaro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>SERUV</t>
+        </is>
+      </c>
+      <c r="B5493" t="inlineStr">
+        <is>
+          <t>Rundvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5494">
+      <c r="A5494" t="inlineStr">
+        <is>
+          <t>SERVD</t>
+        </is>
+      </c>
+      <c r="B5494" t="inlineStr">
+        <is>
+          <t>Ravlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>SERYD</t>
+        </is>
+      </c>
+      <c r="B5495" t="inlineStr">
+        <is>
+          <t>Rydsgard</t>
+        </is>
+      </c>
+    </row>
+    <row r="5496">
+      <c r="A5496" t="inlineStr">
+        <is>
+          <t>SERYZ</t>
+        </is>
+      </c>
+      <c r="B5496" t="inlineStr">
+        <is>
+          <t>Ryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>SES2N</t>
+        </is>
+      </c>
+      <c r="B5497" t="inlineStr">
+        <is>
+          <t>Svanon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5498">
+      <c r="A5498" t="inlineStr">
+        <is>
+          <t>SESAA</t>
+        </is>
+      </c>
+      <c r="B5498" t="inlineStr">
+        <is>
+          <t>Storaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>SESAS</t>
+        </is>
+      </c>
+      <c r="B5499" t="inlineStr">
+        <is>
+          <t>Satenas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5500">
+      <c r="A5500" t="inlineStr">
+        <is>
+          <t>SESBH</t>
+        </is>
+      </c>
+      <c r="B5500" t="inlineStr">
+        <is>
+          <t>Sibbhult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>SESBV</t>
+        </is>
+      </c>
+      <c r="B5501" t="inlineStr">
+        <is>
+          <t>Satra Brunn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5502">
+      <c r="A5502" t="inlineStr">
+        <is>
+          <t>SESCM</t>
+        </is>
+      </c>
+      <c r="B5502" t="inlineStr">
+        <is>
+          <t>Stockamollan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>SESDB</t>
+        </is>
+      </c>
+      <c r="B5503" t="inlineStr">
+        <is>
+          <t>Soderbarke</t>
+        </is>
+      </c>
+    </row>
+    <row r="5504">
+      <c r="A5504" t="inlineStr">
+        <is>
+          <t>SESDE</t>
+        </is>
+      </c>
+      <c r="B5504" t="inlineStr">
+        <is>
+          <t>Stode</t>
+        </is>
+      </c>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>SESDJ</t>
+        </is>
+      </c>
+      <c r="B5505" t="inlineStr">
+        <is>
+          <t>Sandsjofors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5506">
+      <c r="A5506" t="inlineStr">
+        <is>
+          <t>SESDS</t>
+        </is>
+      </c>
+      <c r="B5506" t="inlineStr">
+        <is>
+          <t>Studsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>SESEF</t>
+        </is>
+      </c>
+      <c r="B5507" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+    </row>
+    <row r="5508">
+      <c r="A5508" t="inlineStr">
+        <is>
+          <t>SESES</t>
+        </is>
+      </c>
+      <c r="B5508" t="inlineStr">
+        <is>
+          <t>Seskaro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>SESGB</t>
+        </is>
+      </c>
+      <c r="B5509" t="inlineStr">
+        <is>
+          <t>Stegeborg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5510">
+      <c r="A5510" t="inlineStr">
+        <is>
+          <t>SESGM</t>
+        </is>
+      </c>
+      <c r="B5510" t="inlineStr">
+        <is>
+          <t>Skagshamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>SESHT</t>
+        </is>
+      </c>
+      <c r="B5511" t="inlineStr">
+        <is>
+          <t>Sandhult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5512">
+      <c r="A5512" t="inlineStr">
+        <is>
+          <t>SESIB</t>
+        </is>
+      </c>
+      <c r="B5512" t="inlineStr">
+        <is>
+          <t>Sankt Ibb</t>
+        </is>
+      </c>
+    </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>SESIG</t>
+        </is>
+      </c>
+      <c r="B5513" t="inlineStr">
+        <is>
+          <t>Stigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5514">
+      <c r="A5514" t="inlineStr">
+        <is>
+          <t>SESJD</t>
+        </is>
+      </c>
+      <c r="B5514" t="inlineStr">
+        <is>
+          <t>Stjarnsund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>SESJL</t>
+        </is>
+      </c>
+      <c r="B5515" t="inlineStr">
+        <is>
+          <t>Skogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5516">
+      <c r="A5516" t="inlineStr">
+        <is>
+          <t>SESJO</t>
+        </is>
+      </c>
+      <c r="B5516" t="inlineStr">
+        <is>
+          <t>Sjoviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>SESJP</t>
+        </is>
+      </c>
+      <c r="B5517" t="inlineStr">
+        <is>
+          <t>Sjuntorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5518">
+      <c r="A5518" t="inlineStr">
+        <is>
+          <t>SESJV</t>
+        </is>
+      </c>
+      <c r="B5518" t="inlineStr">
+        <is>
+          <t>Sjalevad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5519">
+      <c r="A5519" t="inlineStr">
+        <is>
+          <t>SESK8</t>
+        </is>
+      </c>
+      <c r="B5519" t="inlineStr">
+        <is>
+          <t>Sickla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" t="inlineStr">
+        <is>
+          <t>SESKA</t>
+        </is>
+      </c>
+      <c r="B5520" t="inlineStr">
+        <is>
+          <t>Skapafors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5521">
+      <c r="A5521" t="inlineStr">
+        <is>
+          <t>SESKH</t>
+        </is>
+      </c>
+      <c r="B5521" t="inlineStr">
+        <is>
+          <t>Skarholmen/Stockholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5522">
+      <c r="A5522" t="inlineStr">
+        <is>
+          <t>SESKK</t>
+        </is>
+      </c>
+      <c r="B5522" t="inlineStr">
+        <is>
+          <t>Skonvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5523">
+      <c r="A5523" t="inlineStr">
+        <is>
+          <t>SESKL</t>
+        </is>
+      </c>
+      <c r="B5523" t="inlineStr">
+        <is>
+          <t>Skalhamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" t="inlineStr">
+        <is>
+          <t>SESKM</t>
+        </is>
+      </c>
+      <c r="B5524" t="inlineStr">
+        <is>
+          <t>Skarhamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" t="inlineStr">
+        <is>
+          <t>SESKN</t>
+        </is>
+      </c>
+      <c r="B5525" t="inlineStr">
+        <is>
+          <t>Skuthamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" t="inlineStr">
+        <is>
+          <t>SESKR</t>
+        </is>
+      </c>
+      <c r="B5526" t="inlineStr">
+        <is>
+          <t>Skredsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5527">
+      <c r="A5527" t="inlineStr">
+        <is>
+          <t>SESKT</t>
+        </is>
+      </c>
+      <c r="B5527" t="inlineStr">
+        <is>
+          <t>Skattkarr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" t="inlineStr">
+        <is>
+          <t>SESKY</t>
+        </is>
+      </c>
+      <c r="B5528" t="inlineStr">
+        <is>
+          <t>Skyllberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" t="inlineStr">
+        <is>
+          <t>SESL3</t>
+        </is>
+      </c>
+      <c r="B5529" t="inlineStr">
+        <is>
+          <t>Simlangsdalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5530">
+      <c r="A5530" t="inlineStr">
+        <is>
+          <t>SESLG</t>
+        </is>
+      </c>
+      <c r="B5530" t="inlineStr">
+        <is>
+          <t>Sloinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5531">
+      <c r="A5531" t="inlineStr">
+        <is>
+          <t>SESLI</t>
+        </is>
+      </c>
+      <c r="B5531" t="inlineStr">
+        <is>
+          <t>Slite</t>
+        </is>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" t="inlineStr">
+        <is>
+          <t>SESLL</t>
+        </is>
+      </c>
+      <c r="B5532" t="inlineStr">
+        <is>
+          <t>Skollersta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" t="inlineStr">
+        <is>
+          <t>SESMN</t>
+        </is>
+      </c>
+      <c r="B5533" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+    </row>
+    <row r="5534">
+      <c r="A5534" t="inlineStr">
+        <is>
+          <t>SESMO</t>
+        </is>
+      </c>
+      <c r="B5534" t="inlineStr">
+        <is>
+          <t>Smogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" t="inlineStr">
+        <is>
+          <t>SESMS</t>
+        </is>
+      </c>
+      <c r="B5535" t="inlineStr">
+        <is>
+          <t>Salmis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5536">
+      <c r="A5536" t="inlineStr">
+        <is>
+          <t>SESMT</t>
+        </is>
+      </c>
+      <c r="B5536" t="inlineStr">
+        <is>
+          <t>Asmundtorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5537">
+      <c r="A5537" t="inlineStr">
+        <is>
+          <t>SESNA</t>
+        </is>
+      </c>
+      <c r="B5537" t="inlineStr">
+        <is>
+          <t>Svangsta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5538">
+      <c r="A5538" t="inlineStr">
+        <is>
+          <t>SESND</t>
+        </is>
+      </c>
+      <c r="B5538" t="inlineStr">
+        <is>
+          <t>Svanesund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5539">
+      <c r="A5539" t="inlineStr">
+        <is>
+          <t>SESNN</t>
+        </is>
+      </c>
+      <c r="B5539" t="inlineStr">
+        <is>
+          <t>Sennan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5540">
+      <c r="A5540" t="inlineStr">
+        <is>
+          <t>SESNY</t>
+        </is>
+      </c>
+      <c r="B5540" t="inlineStr">
+        <is>
+          <t>Sundby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5541">
+      <c r="A5541" t="inlineStr">
+        <is>
+          <t>SESO3</t>
+        </is>
+      </c>
+      <c r="B5541" t="inlineStr">
+        <is>
+          <t>Soderakra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5542">
+      <c r="A5542" t="inlineStr">
+        <is>
+          <t>SESOD</t>
+        </is>
+      </c>
+      <c r="B5542" t="inlineStr">
+        <is>
+          <t>Sodra Vika</t>
+        </is>
+      </c>
+    </row>
+    <row r="5543">
+      <c r="A5543" t="inlineStr">
+        <is>
+          <t>SESOJ</t>
+        </is>
+      </c>
+      <c r="B5543" t="inlineStr">
+        <is>
+          <t>Sjomarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5544">
+      <c r="A5544" t="inlineStr">
+        <is>
+          <t>SESOM</t>
+        </is>
+      </c>
+      <c r="B5544" t="inlineStr">
+        <is>
+          <t>Sommen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5545">
+      <c r="A5545" t="inlineStr">
+        <is>
+          <t>SESPG</t>
+        </is>
+      </c>
+      <c r="B5545" t="inlineStr">
+        <is>
+          <t>Skarplinge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5546">
+      <c r="A5546" t="inlineStr">
+        <is>
+          <t>SESPH</t>
+        </is>
+      </c>
+      <c r="B5546" t="inlineStr">
+        <is>
+          <t>Sparreholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5547">
+      <c r="A5547" t="inlineStr">
+        <is>
+          <t>SESPL</t>
+        </is>
+      </c>
+      <c r="B5547" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" t="inlineStr">
+        <is>
+          <t>SESPP</t>
+        </is>
+      </c>
+      <c r="B5548" t="inlineStr">
+        <is>
+          <t>Simpevarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" t="inlineStr">
+        <is>
+          <t>SESPR</t>
+        </is>
+      </c>
+      <c r="B5549" t="inlineStr">
+        <is>
+          <t>Sprangsviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5550">
+      <c r="A5550" t="inlineStr">
+        <is>
+          <t>SESRB</t>
+        </is>
+      </c>
+      <c r="B5550" t="inlineStr">
+        <is>
+          <t>Stora Raby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5551">
+      <c r="A5551" t="inlineStr">
+        <is>
+          <t>SESRW</t>
+        </is>
+      </c>
+      <c r="B5551" t="inlineStr">
+        <is>
+          <t>Storebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="5552">
+      <c r="A5552" t="inlineStr">
+        <is>
+          <t>SESSA</t>
+        </is>
+      </c>
+      <c r="B5552" t="inlineStr">
+        <is>
+          <t>Sodra Sandby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5553">
+      <c r="A5553" t="inlineStr">
+        <is>
+          <t>SESSI</t>
+        </is>
+      </c>
+      <c r="B5553" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5554">
+      <c r="A5554" t="inlineStr">
+        <is>
+          <t>SESSO</t>
+        </is>
+      </c>
+      <c r="B5554" t="inlineStr">
+        <is>
+          <t>Stensjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5555">
+      <c r="A5555" t="inlineStr">
+        <is>
+          <t>SEST2</t>
+        </is>
+      </c>
+      <c r="B5555" t="inlineStr">
+        <is>
+          <t>Sjotorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5556">
+      <c r="A5556" t="inlineStr">
+        <is>
+          <t>SESTG</t>
+        </is>
+      </c>
+      <c r="B5556" t="inlineStr">
+        <is>
+          <t>Stigtomta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5557">
+      <c r="A5557" t="inlineStr">
+        <is>
+          <t>SESTI</t>
+        </is>
+      </c>
+      <c r="B5557" t="inlineStr">
+        <is>
+          <t>Stillingson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5558">
+      <c r="A5558" t="inlineStr">
+        <is>
+          <t>SESTK</t>
+        </is>
+      </c>
+      <c r="B5558" t="inlineStr">
+        <is>
+          <t>Stockviksverken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5559">
+      <c r="A5559" t="inlineStr">
+        <is>
+          <t>SESTL</t>
+        </is>
+      </c>
+      <c r="B5559" t="inlineStr">
+        <is>
+          <t>Saltkallan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5560">
+      <c r="A5560" t="inlineStr">
+        <is>
+          <t>SESTN</t>
+        </is>
+      </c>
+      <c r="B5560" t="inlineStr">
+        <is>
+          <t>Storlien</t>
+        </is>
+      </c>
+    </row>
+    <row r="5561">
+      <c r="A5561" t="inlineStr">
+        <is>
+          <t>SESTR</t>
+        </is>
+      </c>
+      <c r="B5561" t="inlineStr">
+        <is>
+          <t>Sandvik, Styrso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5562">
+      <c r="A5562" t="inlineStr">
+        <is>
+          <t>SESTS</t>
+        </is>
+      </c>
+      <c r="B5562" t="inlineStr">
+        <is>
+          <t>Stromsnasbruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5563">
+      <c r="A5563" t="inlineStr">
+        <is>
+          <t>SESTU</t>
+        </is>
+      </c>
+      <c r="B5563" t="inlineStr">
+        <is>
+          <t>Stugsund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5564">
+      <c r="A5564" t="inlineStr">
+        <is>
+          <t>SESTV</t>
+        </is>
+      </c>
+      <c r="B5564" t="inlineStr">
+        <is>
+          <t>Stora Vika</t>
+        </is>
+      </c>
+    </row>
+    <row r="5565">
+      <c r="A5565" t="inlineStr">
+        <is>
+          <t>SESUD</t>
+        </is>
+      </c>
+      <c r="B5565" t="inlineStr">
+        <is>
+          <t>Stocksund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5566">
+      <c r="A5566" t="inlineStr">
+        <is>
+          <t>SESUN</t>
+        </is>
+      </c>
+      <c r="B5566" t="inlineStr">
+        <is>
+          <t>Sund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5567">
+      <c r="A5567" t="inlineStr">
+        <is>
+          <t>SESUP</t>
+        </is>
+      </c>
+      <c r="B5567" t="inlineStr">
+        <is>
+          <t>Slutarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5568">
+      <c r="A5568" t="inlineStr">
+        <is>
+          <t>SESUS</t>
+        </is>
+      </c>
+      <c r="B5568" t="inlineStr">
+        <is>
+          <t>Storugns</t>
+        </is>
+      </c>
+    </row>
+    <row r="5569">
+      <c r="A5569" t="inlineStr">
+        <is>
+          <t>SESVD</t>
+        </is>
+      </c>
+      <c r="B5569" t="inlineStr">
+        <is>
+          <t>Silverdalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5570">
+      <c r="A5570" t="inlineStr">
+        <is>
+          <t>SESVK</t>
+        </is>
+      </c>
+      <c r="B5570" t="inlineStr">
+        <is>
+          <t>Svartvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5571">
+      <c r="A5571" t="inlineStr">
+        <is>
+          <t>SESVP</t>
+        </is>
+      </c>
+      <c r="B5571" t="inlineStr">
+        <is>
+          <t>Svappavaara</t>
+        </is>
+      </c>
+    </row>
+    <row r="5572">
+      <c r="A5572" t="inlineStr">
+        <is>
+          <t>SESVS</t>
+        </is>
+      </c>
+      <c r="B5572" t="inlineStr">
+        <is>
+          <t>Saivisnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5573">
+      <c r="A5573" t="inlineStr">
+        <is>
+          <t>SESZC</t>
+        </is>
+      </c>
+      <c r="B5573" t="inlineStr">
+        <is>
+          <t>Alvkarleby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5574">
+      <c r="A5574" t="inlineStr">
+        <is>
+          <t>SESZD</t>
+        </is>
+      </c>
+      <c r="B5574" t="inlineStr">
+        <is>
+          <t>Borrby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5575">
+      <c r="A5575" t="inlineStr">
+        <is>
+          <t>SESZG</t>
+        </is>
+      </c>
+      <c r="B5575" t="inlineStr">
+        <is>
+          <t>Flisby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5576">
+      <c r="A5576" t="inlineStr">
+        <is>
+          <t>SESZH</t>
+        </is>
+      </c>
+      <c r="B5576" t="inlineStr">
+        <is>
+          <t>Gyttorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5577">
+      <c r="A5577" t="inlineStr">
+        <is>
+          <t>SESZL</t>
+        </is>
+      </c>
+      <c r="B5577" t="inlineStr">
+        <is>
+          <t>Malilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5578">
+      <c r="A5578" t="inlineStr">
+        <is>
+          <t>SESZM</t>
+        </is>
+      </c>
+      <c r="B5578" t="inlineStr">
+        <is>
+          <t>Moklinta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5579">
+      <c r="A5579" t="inlineStr">
+        <is>
+          <t>SESZO</t>
+        </is>
+      </c>
+      <c r="B5579" t="inlineStr">
+        <is>
+          <t>Rumskulla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5580">
+      <c r="A5580" t="inlineStr">
+        <is>
+          <t>SESZP</t>
+        </is>
+      </c>
+      <c r="B5580" t="inlineStr">
+        <is>
+          <t>Rorvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5581">
+      <c r="A5581" t="inlineStr">
+        <is>
+          <t>SESZU</t>
+        </is>
+      </c>
+      <c r="B5581" t="inlineStr">
+        <is>
+          <t>Trekanten</t>
+        </is>
+      </c>
+    </row>
+    <row r="5582">
+      <c r="A5582" t="inlineStr">
+        <is>
+          <t>SESZX</t>
+        </is>
+      </c>
+      <c r="B5582" t="inlineStr">
+        <is>
+          <t>Tofta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5583">
+      <c r="A5583" t="inlineStr">
+        <is>
+          <t>SESZY</t>
+        </is>
+      </c>
+      <c r="B5583" t="inlineStr">
+        <is>
+          <t>Timmele</t>
+        </is>
+      </c>
+    </row>
+    <row r="5584">
+      <c r="A5584" t="inlineStr">
+        <is>
+          <t>SETAB</t>
+        </is>
+      </c>
+      <c r="B5584" t="inlineStr">
+        <is>
+          <t>Tandsbyn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5585">
+      <c r="A5585" t="inlineStr">
+        <is>
+          <t>SETAE</t>
+        </is>
+      </c>
+      <c r="B5585" t="inlineStr">
+        <is>
+          <t>Tarnaby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5586">
+      <c r="A5586" t="inlineStr">
+        <is>
+          <t>SETAG</t>
+        </is>
+      </c>
+      <c r="B5586" t="inlineStr">
+        <is>
+          <t>Tangaberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5587">
+      <c r="A5587" t="inlineStr">
+        <is>
+          <t>SETAN</t>
+        </is>
+      </c>
+      <c r="B5587" t="inlineStr">
+        <is>
+          <t>Tanumshede</t>
+        </is>
+      </c>
+    </row>
+    <row r="5588">
+      <c r="A5588" t="inlineStr">
+        <is>
+          <t>SETBA</t>
+        </is>
+      </c>
+      <c r="B5588" t="inlineStr">
+        <is>
+          <t>Tomteboda/Solna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5589">
+      <c r="A5589" t="inlineStr">
+        <is>
+          <t>SETEG</t>
+        </is>
+      </c>
+      <c r="B5589" t="inlineStr">
+        <is>
+          <t>Taberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5590">
+      <c r="A5590" t="inlineStr">
+        <is>
+          <t>SETEO</t>
+        </is>
+      </c>
+      <c r="B5590" t="inlineStr">
+        <is>
+          <t>Tarendo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5591">
+      <c r="A5591" t="inlineStr">
+        <is>
+          <t>SETGA</t>
+        </is>
+      </c>
+      <c r="B5591" t="inlineStr">
+        <is>
+          <t>Tagarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5592">
+      <c r="A5592" t="inlineStr">
+        <is>
+          <t>SETGS</t>
+        </is>
+      </c>
+      <c r="B5592" t="inlineStr">
+        <is>
+          <t>Trangsund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5593">
+      <c r="A5593" t="inlineStr">
+        <is>
+          <t>SETHR</t>
+        </is>
+      </c>
+      <c r="B5593" t="inlineStr">
+        <is>
+          <t>Torpshammar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5594">
+      <c r="A5594" t="inlineStr">
+        <is>
+          <t>SETJP</t>
+        </is>
+      </c>
+      <c r="B5594" t="inlineStr">
+        <is>
+          <t>Tjornarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5595">
+      <c r="A5595" t="inlineStr">
+        <is>
+          <t>SETK2</t>
+        </is>
+      </c>
+      <c r="B5595" t="inlineStr">
+        <is>
+          <t>Tving</t>
+        </is>
+      </c>
+    </row>
+    <row r="5596">
+      <c r="A5596" t="inlineStr">
+        <is>
+          <t>SETLL</t>
+        </is>
+      </c>
+      <c r="B5596" t="inlineStr">
+        <is>
+          <t>Tollarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5597">
+      <c r="A5597" t="inlineStr">
+        <is>
+          <t>SETNH</t>
+        </is>
+      </c>
+      <c r="B5597" t="inlineStr">
+        <is>
+          <t>Tenhult</t>
+        </is>
+      </c>
+    </row>
+    <row r="5598">
+      <c r="A5598" t="inlineStr">
+        <is>
+          <t>SETNJ</t>
+        </is>
+      </c>
+      <c r="B5598" t="inlineStr">
+        <is>
+          <t>Tarnsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5599">
+      <c r="A5599" t="inlineStr">
+        <is>
+          <t>SETOE</t>
+        </is>
+      </c>
+      <c r="B5599" t="inlineStr">
+        <is>
+          <t>Tore</t>
+        </is>
+      </c>
+    </row>
+    <row r="5600">
+      <c r="A5600" t="inlineStr">
+        <is>
+          <t>SETOP</t>
+        </is>
+      </c>
+      <c r="B5600" t="inlineStr">
+        <is>
+          <t>Torup</t>
+        </is>
+      </c>
+    </row>
+    <row r="5601">
+      <c r="A5601" t="inlineStr">
+        <is>
+          <t>SETOT</t>
+        </is>
+      </c>
+      <c r="B5601" t="inlineStr">
+        <is>
+          <t>Totebo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5602">
+      <c r="A5602" t="inlineStr">
+        <is>
+          <t>SETRP</t>
+        </is>
+      </c>
+      <c r="B5602" t="inlineStr">
+        <is>
+          <t>Ostra Tommarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5603">
+      <c r="A5603" t="inlineStr">
+        <is>
+          <t>SETRR</t>
+        </is>
+      </c>
+      <c r="B5603" t="inlineStr">
+        <is>
+          <t>Travad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5604">
+      <c r="A5604" t="inlineStr">
+        <is>
+          <t>SETSB</t>
+        </is>
+      </c>
+      <c r="B5604" t="inlineStr">
+        <is>
+          <t>Tagsjoberg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5605">
+      <c r="A5605" t="inlineStr">
+        <is>
+          <t>SETSL</t>
+        </is>
+      </c>
+      <c r="B5605" t="inlineStr">
+        <is>
+          <t>Traslovslage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5606">
+      <c r="A5606" t="inlineStr">
+        <is>
+          <t>SETSO</t>
+        </is>
+      </c>
+      <c r="B5606" t="inlineStr">
+        <is>
+          <t>Torso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5607">
+      <c r="A5607" t="inlineStr">
+        <is>
+          <t>SETSR</t>
+        </is>
+      </c>
+      <c r="B5607" t="inlineStr">
+        <is>
+          <t>Torsaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5608">
+      <c r="A5608" t="inlineStr">
+        <is>
+          <t>SETTD</t>
+        </is>
+      </c>
+      <c r="B5608" t="inlineStr">
+        <is>
+          <t>Tomtbod</t>
+        </is>
+      </c>
+    </row>
+    <row r="5609">
+      <c r="A5609" t="inlineStr">
+        <is>
+          <t>SETTN</t>
+        </is>
+      </c>
+      <c r="B5609" t="inlineStr">
+        <is>
+          <t>Rottne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5610">
+      <c r="A5610" t="inlineStr">
+        <is>
+          <t>SETUN</t>
+        </is>
+      </c>
+      <c r="B5610" t="inlineStr">
+        <is>
+          <t>Tunadal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5611">
+      <c r="A5611" t="inlineStr">
+        <is>
+          <t>SETVD</t>
+        </is>
+      </c>
+      <c r="B5611" t="inlineStr">
+        <is>
+          <t>Tvaeraalund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5612">
+      <c r="A5612" t="inlineStr">
+        <is>
+          <t>SETVK</t>
+        </is>
+      </c>
+      <c r="B5612" t="inlineStr">
+        <is>
+          <t>Torsvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5613">
+      <c r="A5613" t="inlineStr">
+        <is>
+          <t>SETYG</t>
+        </is>
+      </c>
+      <c r="B5613" t="inlineStr">
+        <is>
+          <t>Tygelsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5614">
+      <c r="A5614" t="inlineStr">
+        <is>
+          <t>SETYN</t>
+        </is>
+      </c>
+      <c r="B5614" t="inlineStr">
+        <is>
+          <t>Tyngsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5615">
+      <c r="A5615" t="inlineStr">
+        <is>
+          <t>SETYS</t>
+        </is>
+      </c>
+      <c r="B5615" t="inlineStr">
+        <is>
+          <t>Tyreso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5616">
+      <c r="A5616" t="inlineStr">
+        <is>
+          <t>SEUGG</t>
+        </is>
+      </c>
+      <c r="B5616" t="inlineStr">
+        <is>
+          <t>Ugglarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5617">
+      <c r="A5617" t="inlineStr">
+        <is>
+          <t>SEUGN</t>
+        </is>
+      </c>
+      <c r="B5617" t="inlineStr">
+        <is>
+          <t>Ulebergshamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5618">
+      <c r="A5618" t="inlineStr">
+        <is>
+          <t>SEUKM</t>
+        </is>
+      </c>
+      <c r="B5618" t="inlineStr">
+        <is>
+          <t>Ucklum</t>
+        </is>
+      </c>
+    </row>
+    <row r="5619">
+      <c r="A5619" t="inlineStr">
+        <is>
+          <t>SEULF</t>
+        </is>
+      </c>
+      <c r="B5619" t="inlineStr">
+        <is>
+          <t>Ulfvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="5620">
+      <c r="A5620" t="inlineStr">
+        <is>
+          <t>SEVAC</t>
+        </is>
+      </c>
+      <c r="B5620" t="inlineStr">
+        <is>
+          <t>Vackelsang</t>
+        </is>
+      </c>
+    </row>
+    <row r="5621">
+      <c r="A5621" t="inlineStr">
+        <is>
+          <t>SEVAT</t>
+        </is>
+      </c>
+      <c r="B5621" t="inlineStr">
+        <is>
+          <t>Vattholma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5622">
+      <c r="A5622" t="inlineStr">
+        <is>
+          <t>SEVBE</t>
+        </is>
+      </c>
+      <c r="B5622" t="inlineStr">
+        <is>
+          <t>Veberod</t>
+        </is>
+      </c>
+    </row>
+    <row r="5623">
+      <c r="A5623" t="inlineStr">
+        <is>
+          <t>SEVDL</t>
+        </is>
+      </c>
+      <c r="B5623" t="inlineStr">
+        <is>
+          <t>Vendelso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5624">
+      <c r="A5624" t="inlineStr">
+        <is>
+          <t>SEVDS</t>
+        </is>
+      </c>
+      <c r="B5624" t="inlineStr">
+        <is>
+          <t>Vaderstad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5625">
+      <c r="A5625" t="inlineStr">
+        <is>
+          <t>SEVED</t>
+        </is>
+      </c>
+      <c r="B5625" t="inlineStr">
+        <is>
+          <t>Veddesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5626">
+      <c r="A5626" t="inlineStr">
+        <is>
+          <t>SEVER</t>
+        </is>
+      </c>
+      <c r="B5626" t="inlineStr">
+        <is>
+          <t>Verkeback</t>
+        </is>
+      </c>
+    </row>
+    <row r="5627">
+      <c r="A5627" t="inlineStr">
+        <is>
+          <t>SEVGO</t>
+        </is>
+      </c>
+      <c r="B5627" t="inlineStr">
+        <is>
+          <t>Vrango</t>
+        </is>
+      </c>
+    </row>
+    <row r="5628">
+      <c r="A5628" t="inlineStr">
+        <is>
+          <t>SEVHD</t>
+        </is>
+      </c>
+      <c r="B5628" t="inlineStr">
+        <is>
+          <t>Vagnharad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5629">
+      <c r="A5629" t="inlineStr">
+        <is>
+          <t>SEVHE</t>
+        </is>
+      </c>
+      <c r="B5629" t="inlineStr">
+        <is>
+          <t>Vasterhaninge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5630">
+      <c r="A5630" t="inlineStr">
+        <is>
+          <t>SEVHM</t>
+        </is>
+      </c>
+      <c r="B5630" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5631">
+      <c r="A5631" t="inlineStr">
+        <is>
+          <t>SEVII</t>
+        </is>
+      </c>
+      <c r="B5631" t="inlineStr">
+        <is>
+          <t>Vintrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="5632">
+      <c r="A5632" t="inlineStr">
+        <is>
+          <t>SEVIN</t>
+        </is>
+      </c>
+      <c r="B5632" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+    </row>
+    <row r="5633">
+      <c r="A5633" t="inlineStr">
+        <is>
+          <t>SEVIS</t>
+        </is>
+      </c>
+      <c r="B5633" t="inlineStr">
+        <is>
+          <t>Vinslov</t>
+        </is>
+      </c>
+    </row>
+    <row r="5634">
+      <c r="A5634" t="inlineStr">
+        <is>
+          <t>SEVIT</t>
+        </is>
+      </c>
+      <c r="B5634" t="inlineStr">
+        <is>
+          <t>Vittaryd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5635">
+      <c r="A5635" t="inlineStr">
+        <is>
+          <t>SEVIV</t>
+        </is>
+      </c>
+      <c r="B5635" t="inlineStr">
+        <is>
+          <t>Vivstavarv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5636">
+      <c r="A5636" t="inlineStr">
+        <is>
+          <t>SEVKB</t>
+        </is>
+      </c>
+      <c r="B5636" t="inlineStr">
+        <is>
+          <t>Vikarbyn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5637">
+      <c r="A5637" t="inlineStr">
+        <is>
+          <t>SEVKF</t>
+        </is>
+      </c>
+      <c r="B5637" t="inlineStr">
+        <is>
+          <t>Viskafors</t>
+        </is>
+      </c>
+    </row>
+    <row r="5638">
+      <c r="A5638" t="inlineStr">
+        <is>
+          <t>SEVKO</t>
+        </is>
+      </c>
+      <c r="B5638" t="inlineStr">
+        <is>
+          <t>Vikbolandet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5639">
+      <c r="A5639" t="inlineStr">
+        <is>
+          <t>SEVKR</t>
+        </is>
+      </c>
+      <c r="B5639" t="inlineStr">
+        <is>
+          <t>Vreta Kloster</t>
+        </is>
+      </c>
+    </row>
+    <row r="5640">
+      <c r="A5640" t="inlineStr">
+        <is>
+          <t>SEVKT</t>
+        </is>
+      </c>
+      <c r="B5640" t="inlineStr">
+        <is>
+          <t>Vikingstad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5641">
+      <c r="A5641" t="inlineStr">
+        <is>
+          <t>SEVLA</t>
+        </is>
+      </c>
+      <c r="B5641" t="inlineStr">
+        <is>
+          <t>Vasterlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5642">
+      <c r="A5642" t="inlineStr">
+        <is>
+          <t>SEVLD</t>
+        </is>
+      </c>
+      <c r="B5642" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5643">
+      <c r="A5643" t="inlineStr">
+        <is>
+          <t>SEVLK</t>
+        </is>
+      </c>
+      <c r="B5643" t="inlineStr">
+        <is>
+          <t>Valla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5644">
+      <c r="A5644" t="inlineStr">
+        <is>
+          <t>SEVNG</t>
+        </is>
+      </c>
+      <c r="B5644" t="inlineStr">
+        <is>
+          <t>Vinninga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>SEVRI</t>
+        </is>
+      </c>
+      <c r="B5645" t="inlineStr">
+        <is>
+          <t>Vrigstad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" t="inlineStr">
+        <is>
+          <t>SEVRT</t>
+        </is>
+      </c>
+      <c r="B5646" t="inlineStr">
+        <is>
+          <t>Virestad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>SEVS8</t>
+        </is>
+      </c>
+      <c r="B5647" t="inlineStr">
+        <is>
+          <t>Svaneholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" t="inlineStr">
+        <is>
+          <t>SEVSE</t>
+        </is>
+      </c>
+      <c r="B5648" t="inlineStr">
+        <is>
+          <t>Vase</t>
+        </is>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>SEVSJ</t>
+        </is>
+      </c>
+      <c r="B5649" t="inlineStr">
+        <is>
+          <t>Vittsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" t="inlineStr">
+        <is>
+          <t>SEVSP</t>
+        </is>
+      </c>
+      <c r="B5650" t="inlineStr">
+        <is>
+          <t>Vretstorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>SEVTH</t>
+        </is>
+      </c>
+      <c r="B5651" t="inlineStr">
+        <is>
+          <t>Vastra Tunhem</t>
+        </is>
+      </c>
+    </row>
+    <row r="5652">
+      <c r="A5652" t="inlineStr">
+        <is>
+          <t>SEVTK</t>
+        </is>
+      </c>
+      <c r="B5652" t="inlineStr">
+        <is>
+          <t>Visttrask</t>
+        </is>
+      </c>
+    </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>SEVTR</t>
+        </is>
+      </c>
+      <c r="B5653" t="inlineStr">
+        <is>
+          <t>Vintrosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5654">
+      <c r="A5654" t="inlineStr">
+        <is>
+          <t>SEVXT</t>
+        </is>
+      </c>
+      <c r="B5654" t="inlineStr">
+        <is>
+          <t>Vaxtorp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>SEXMN</t>
+        </is>
+      </c>
+      <c r="B5655" t="inlineStr">
+        <is>
+          <t>Skivarp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" t="inlineStr">
+        <is>
+          <t>SEYBY</t>
+        </is>
+      </c>
+      <c r="B5656" t="inlineStr">
+        <is>
+          <t>Kareby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>SEYNG</t>
+        </is>
+      </c>
+      <c r="B5657" t="inlineStr">
+        <is>
+          <t>Yngsjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5658">
+      <c r="A5658" t="inlineStr">
+        <is>
+          <t>SEYTT</t>
+        </is>
+      </c>
+      <c r="B5658" t="inlineStr">
+        <is>
+          <t>Ytterfalle/Harnosand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>SEZGV</t>
+        </is>
+      </c>
+      <c r="B5659" t="inlineStr">
+        <is>
+          <t>Zinkgruvan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B5061"/>
+  <autoFilter ref="A1:B5659"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>